--- a/Excel/SkillSuitConfig.xlsx
+++ b/Excel/SkillSuitConfig.xlsx
@@ -4,11 +4,10 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="17680" activeTab="1"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
-    <sheet name="批量配置" sheetId="1" r:id="rId1"/>
-    <sheet name="手动配置" sheetId="2" r:id="rId2"/>
+    <sheet name="手动配置" sheetId="2" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,134 +27,6 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>admin</author>
-  </authors>
-  <commentList>
-    <comment ref="C3" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>admin:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-ID* 10 + level
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="K3" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>admin:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-1 主动
-2 被动
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="L3" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>admin:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-0 以自己为圆心
-1 距离1格</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="M3" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>admin:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-FrontRow 直线
-FullBox 十字
-Square 矩形
-Diamond 菱形
-FullBox 全图</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="R3" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>admin:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">
-攻击力系数（百分比），额外附加固定伤害值</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>admin</author>
@@ -234,18 +105,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1137" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="75">
   <si>
     <t>_ID</t>
   </si>
   <si>
-    <t>Type</t>
-  </si>
-  <si>
-    <t>EquipRate</t>
-  </si>
-  <si>
-    <t>ExclusiveRate</t>
+    <t>Role</t>
   </si>
   <si>
     <t>技能ID</t>
@@ -260,18 +125,12 @@
     <t>减少冷却时间</t>
   </si>
   <si>
-    <t>修改施法类型</t>
+    <t>持续时间</t>
   </si>
   <si>
     <t>增加攻击距离</t>
   </si>
   <si>
-    <t>修改攻击区域</t>
-  </si>
-  <si>
-    <t>持续时间</t>
-  </si>
-  <si>
     <t>增加最大敌人数量</t>
   </si>
   <si>
@@ -281,33 +140,30 @@
     <t>列</t>
   </si>
   <si>
+    <t>固定伤害</t>
+  </si>
+  <si>
     <t>增加伤害比例</t>
   </si>
   <si>
-    <t>固定伤害</t>
+    <t>致命率</t>
+  </si>
+  <si>
+    <t>致命伤害</t>
+  </si>
+  <si>
+    <t>攻击加成</t>
+  </si>
+  <si>
+    <t>最终加成</t>
   </si>
   <si>
     <t>无视防御</t>
   </si>
   <si>
-    <t>暴击率</t>
-  </si>
-  <si>
-    <t>暴击倍率</t>
-  </si>
-  <si>
     <t>伤害加成</t>
   </si>
   <si>
-    <t>攻击加成</t>
-  </si>
-  <si>
-    <t>最终加成</t>
-  </si>
-  <si>
-    <t>继承加成</t>
-  </si>
-  <si>
     <t>附带效果</t>
   </si>
   <si>
@@ -326,18 +182,12 @@
     <t>CD</t>
   </si>
   <si>
-    <t>CastType</t>
+    <t>Duration</t>
   </si>
   <si>
     <t>Dis</t>
   </si>
   <si>
-    <t>Area</t>
-  </si>
-  <si>
-    <t>Duration</t>
-  </si>
-  <si>
     <t>EnemyMax</t>
   </si>
   <si>
@@ -347,33 +197,30 @@
     <t>Column</t>
   </si>
   <si>
+    <t>Damage</t>
+  </si>
+  <si>
     <t>Percent</t>
   </si>
   <si>
-    <t>Damage</t>
+    <t>DeadlyRate</t>
+  </si>
+  <si>
+    <t>DeadlyDamage</t>
+  </si>
+  <si>
+    <t>AttrIncrea</t>
+  </si>
+  <si>
+    <t>FinalIncrea</t>
   </si>
   <si>
     <t>IgnoreDef</t>
   </si>
   <si>
-    <t>CritRate</t>
-  </si>
-  <si>
-    <t>CritDamage</t>
-  </si>
-  <si>
     <t>DamageIncrea</t>
   </si>
   <si>
-    <t>AttrIncrea</t>
-  </si>
-  <si>
-    <t>FinalIncrea</t>
-  </si>
-  <si>
-    <t>InheritIncrea</t>
-  </si>
-  <si>
     <t>EffectId</t>
   </si>
   <si>
@@ -381,336 +228,6 @@
   </si>
   <si>
     <t>string</t>
-  </si>
-  <si>
-    <t>10001</t>
-  </si>
-  <si>
-    <t>1001</t>
-  </si>
-  <si>
-    <t>基础剑术·祝福</t>
-  </si>
-  <si>
-    <t>技能提高50%攻击</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>50</t>
-  </si>
-  <si>
-    <t>10002</t>
-  </si>
-  <si>
-    <t>基础剑术·致命</t>
-  </si>
-  <si>
-    <t>技能提高50%最终伤害</t>
-  </si>
-  <si>
-    <t>10003</t>
-  </si>
-  <si>
-    <t>1002</t>
-  </si>
-  <si>
-    <t>流光剑法·祝福</t>
-  </si>
-  <si>
-    <t>10004</t>
-  </si>
-  <si>
-    <t>流光剑法·致命</t>
-  </si>
-  <si>
-    <t>10005</t>
-  </si>
-  <si>
-    <t>1003</t>
-  </si>
-  <si>
-    <t>旋风斩·祝福</t>
-  </si>
-  <si>
-    <t>10006</t>
-  </si>
-  <si>
-    <t>旋风斩·致命</t>
-  </si>
-  <si>
-    <t>10007</t>
-  </si>
-  <si>
-    <t>1004</t>
-  </si>
-  <si>
-    <t>蛮力撞击·祝福</t>
-  </si>
-  <si>
-    <t>10008</t>
-  </si>
-  <si>
-    <t>蛮力撞击·致命</t>
-  </si>
-  <si>
-    <t>10009</t>
-  </si>
-  <si>
-    <t>1005</t>
-  </si>
-  <si>
-    <t>武神盾·生命</t>
-  </si>
-  <si>
-    <t>技能提高50%生命加成</t>
-  </si>
-  <si>
-    <t>武神盾·防御</t>
-  </si>
-  <si>
-    <t>技能提高50%防御加成</t>
-  </si>
-  <si>
-    <t>10011</t>
-  </si>
-  <si>
-    <t>道力精通·配重复了</t>
-  </si>
-  <si>
-    <t>配重复了</t>
-  </si>
-  <si>
-    <t>10012</t>
-  </si>
-  <si>
-    <t>10013</t>
-  </si>
-  <si>
-    <t>1007</t>
-  </si>
-  <si>
-    <t>烈焰斩·祝福</t>
-  </si>
-  <si>
-    <t>10014</t>
-  </si>
-  <si>
-    <t>烈焰斩·致命</t>
-  </si>
-  <si>
-    <t>10015</t>
-  </si>
-  <si>
-    <t>2001</t>
-  </si>
-  <si>
-    <t>火球术·祝福</t>
-  </si>
-  <si>
-    <t>10016</t>
-  </si>
-  <si>
-    <t>火球术·致命</t>
-  </si>
-  <si>
-    <t>10017</t>
-  </si>
-  <si>
-    <t>2002</t>
-  </si>
-  <si>
-    <t>落雷术·祝福</t>
-  </si>
-  <si>
-    <t>10018</t>
-  </si>
-  <si>
-    <t>落雷术·致命</t>
-  </si>
-  <si>
-    <t>10019</t>
-  </si>
-  <si>
-    <t>2003</t>
-  </si>
-  <si>
-    <t>火焰墙·祝福</t>
-  </si>
-  <si>
-    <t>10020</t>
-  </si>
-  <si>
-    <t>火焰墙·致命</t>
-  </si>
-  <si>
-    <t>10021</t>
-  </si>
-  <si>
-    <t>2004</t>
-  </si>
-  <si>
-    <t>烈焰环·祝福</t>
-  </si>
-  <si>
-    <t>10022</t>
-  </si>
-  <si>
-    <t>烈焰环·致命</t>
-  </si>
-  <si>
-    <t>10023</t>
-  </si>
-  <si>
-    <t>2005</t>
-  </si>
-  <si>
-    <t>法力盾·生命</t>
-  </si>
-  <si>
-    <t>10024</t>
-  </si>
-  <si>
-    <t>法力盾·防御</t>
-  </si>
-  <si>
-    <t>10025</t>
-  </si>
-  <si>
-    <t>10026</t>
-  </si>
-  <si>
-    <t>10027</t>
-  </si>
-  <si>
-    <t>2007</t>
-  </si>
-  <si>
-    <t>冰爆术·祝福</t>
-  </si>
-  <si>
-    <t>10028</t>
-  </si>
-  <si>
-    <t>冰爆术·致命</t>
-  </si>
-  <si>
-    <t>10029</t>
-  </si>
-  <si>
-    <t>3001</t>
-  </si>
-  <si>
-    <t>疗伤术·祝福</t>
-  </si>
-  <si>
-    <t>10030</t>
-  </si>
-  <si>
-    <t>疗伤术·强化</t>
-  </si>
-  <si>
-    <t>技能提高50%技能系数</t>
-  </si>
-  <si>
-    <t>3002</t>
-  </si>
-  <si>
-    <t>驱魔符·祝福</t>
-  </si>
-  <si>
-    <t>驱魔符·致命</t>
-  </si>
-  <si>
-    <t>10033</t>
-  </si>
-  <si>
-    <t>3003</t>
-  </si>
-  <si>
-    <t>毒咒道法·祝福</t>
-  </si>
-  <si>
-    <t>10034</t>
-  </si>
-  <si>
-    <t>毒咒道法·致命</t>
-  </si>
-  <si>
-    <t>10035</t>
-  </si>
-  <si>
-    <t>3004</t>
-  </si>
-  <si>
-    <t>召唤小兵·祝福</t>
-  </si>
-  <si>
-    <t>10036</t>
-  </si>
-  <si>
-    <t>召唤小兵·传承</t>
-  </si>
-  <si>
-    <t>骷髅增加20%高级属性继承</t>
-  </si>
-  <si>
-    <t>10037</t>
-  </si>
-  <si>
-    <t>3005</t>
-  </si>
-  <si>
-    <t>道力盾·生命</t>
-  </si>
-  <si>
-    <t>10038</t>
-  </si>
-  <si>
-    <t>道力盾·防御</t>
-  </si>
-  <si>
-    <t>10039</t>
-  </si>
-  <si>
-    <t>10040</t>
-  </si>
-  <si>
-    <t>10041</t>
-  </si>
-  <si>
-    <t>3007</t>
-  </si>
-  <si>
-    <t>召唤魔兽·祝福</t>
-  </si>
-  <si>
-    <t>10042</t>
-  </si>
-  <si>
-    <t>召唤魔兽·传承</t>
-  </si>
-  <si>
-    <t>神兽增加20%高级属性继承</t>
-  </si>
-  <si>
-    <t>Role</t>
-  </si>
-  <si>
-    <t>致命率</t>
-  </si>
-  <si>
-    <t>致命伤害</t>
-  </si>
-  <si>
-    <t>DeadlyRate</t>
-  </si>
-  <si>
-    <t>DeadlyDamage</t>
   </si>
   <si>
     <t>基础心法</t>
@@ -1789,3511 +1306,6 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:AC47"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
-  <cols>
-    <col min="1" max="7" width="9" style="1"/>
-    <col min="8" max="8" width="21.25" style="1" customWidth="1"/>
-    <col min="9" max="9" width="25.875" style="1" customWidth="1"/>
-    <col min="10" max="10" width="9" style="1"/>
-    <col min="11" max="11" width="14.625" style="1" customWidth="1"/>
-    <col min="12" max="14" width="10.375" style="1" customWidth="1"/>
-    <col min="15" max="17" width="13.75" style="1" customWidth="1"/>
-    <col min="18" max="18" width="10.375" style="1" customWidth="1"/>
-    <col min="19" max="26" width="13" style="1" customWidth="1"/>
-    <col min="27" max="27" width="7.875" style="1" customWidth="1"/>
-    <col min="28" max="33" width="9" style="1"/>
-    <col min="34" max="34" width="19.25" style="1" customWidth="1"/>
-    <col min="35" max="16384" width="9" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="3" customHeight="1" spans="3:29">
-      <c r="C3" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="G3" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="K3" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="L3" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="M3" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="N3" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="O3" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="P3" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q3" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="R3" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="S3" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="T3" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="U3" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="V3" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="W3" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="X3" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="Y3" s="4" t="s">
-        <v>22</v>
-      </c>
-      <c r="Z3" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="AA3" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="AB3" s="4"/>
-      <c r="AC3" s="4"/>
-    </row>
-    <row r="4" customHeight="1" spans="3:29">
-      <c r="C4" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>1</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>2</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="H4" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="K4" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="L4" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="M4" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="N4" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="O4" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="P4" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q4" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="R4" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="S4" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="T4" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="U4" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="V4" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="W4" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="X4" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y4" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="Z4" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="AA4" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="AB4" s="4"/>
-      <c r="AC4" s="4"/>
-    </row>
-    <row r="5" customHeight="1" spans="3:29">
-      <c r="C5" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="H5" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="I5" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="K5" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="L5" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="M5" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="N5" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="O5" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="P5" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="Q5" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="R5" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="S5" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="T5" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="U5" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="V5" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="W5" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="X5" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="Y5" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="Z5" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="AA5" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="AB5" s="4"/>
-      <c r="AC5" s="4"/>
-    </row>
-    <row r="6" s="2" customFormat="1" customHeight="1" spans="3:29">
-      <c r="C6" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="D6" s="1">
-        <v>1</v>
-      </c>
-      <c r="E6" s="1">
-        <v>1</v>
-      </c>
-      <c r="F6" s="1">
-        <v>1</v>
-      </c>
-      <c r="G6" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="L6" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="M6" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="N6" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="O6" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="P6" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q6" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="R6" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="S6" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="T6" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="U6" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="V6" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="W6" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="X6" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="Y6" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="Z6" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA6" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" s="2" customFormat="1" customHeight="1" spans="3:29">
-      <c r="C7" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="D7" s="1">
-        <v>1</v>
-      </c>
-      <c r="E7" s="1">
-        <v>1</v>
-      </c>
-      <c r="F7" s="1">
-        <v>1</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="L7" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="M7" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="N7" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="O7" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="P7" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q7" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="R7" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="S7" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="T7" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="U7" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="V7" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="W7" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="X7" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="Y7" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="Z7" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA7" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" s="2" customFormat="1" customHeight="1" spans="3:29">
-      <c r="C8" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="D8" s="1">
-        <v>1</v>
-      </c>
-      <c r="E8" s="1">
-        <v>1</v>
-      </c>
-      <c r="F8" s="1">
-        <v>1</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="J8" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="L8" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="M8" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="N8" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="O8" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="P8" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q8" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="R8" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="S8" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="T8" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="U8" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="V8" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="W8" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="X8" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="Y8" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="Z8" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA8" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" s="2" customFormat="1" customHeight="1" spans="3:29">
-      <c r="C9" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="D9" s="1">
-        <v>1</v>
-      </c>
-      <c r="E9" s="1">
-        <v>1</v>
-      </c>
-      <c r="F9" s="1">
-        <v>1</v>
-      </c>
-      <c r="G9" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="J9" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="K9" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="L9" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="M9" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="N9" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="O9" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="P9" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q9" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="R9" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="S9" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="T9" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="U9" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="V9" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="W9" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="X9" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="Y9" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="Z9" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA9" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" customHeight="1" spans="3:29">
-      <c r="C10" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="D10" s="1">
-        <v>1</v>
-      </c>
-      <c r="E10" s="1">
-        <v>1</v>
-      </c>
-      <c r="F10" s="1">
-        <v>1</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="J10" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="K10" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="L10" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="M10" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="N10" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="O10" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="P10" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q10" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="R10" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="S10" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="T10" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="U10" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="V10" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="W10" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="X10" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="Y10" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="Z10" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA10" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" customHeight="1" spans="3:29">
-      <c r="C11" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="D11" s="1">
-        <v>1</v>
-      </c>
-      <c r="E11" s="1">
-        <v>1</v>
-      </c>
-      <c r="F11" s="1">
-        <v>1</v>
-      </c>
-      <c r="G11" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="I11" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="J11" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="K11" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="L11" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="M11" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="N11" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="O11" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="P11" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q11" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="R11" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="S11" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="T11" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="U11" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="V11" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="W11" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="X11" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="Y11" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="Z11" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA11" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" customHeight="1" spans="3:29">
-      <c r="C12" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="D12" s="1">
-        <v>1</v>
-      </c>
-      <c r="E12" s="1">
-        <v>1</v>
-      </c>
-      <c r="F12" s="1">
-        <v>1</v>
-      </c>
-      <c r="G12" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="H12" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="I12" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="J12" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="K12" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="L12" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="M12" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="N12" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="O12" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="P12" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q12" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="R12" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="S12" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="T12" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="U12" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="V12" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="W12" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="X12" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="Y12" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="Z12" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA12" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" customHeight="1" spans="3:29">
-      <c r="C13" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="D13" s="1">
-        <v>1</v>
-      </c>
-      <c r="E13" s="1">
-        <v>1</v>
-      </c>
-      <c r="F13" s="1">
-        <v>1</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="H13" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="I13" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="J13" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="K13" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="L13" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="M13" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="N13" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="O13" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="P13" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q13" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="R13" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="S13" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="T13" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="U13" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="V13" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="W13" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="X13" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="Y13" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="Z13" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA13" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" customHeight="1" spans="3:29">
-      <c r="C14" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="D14" s="1">
-        <v>1</v>
-      </c>
-      <c r="E14" s="1">
-        <v>1</v>
-      </c>
-      <c r="F14" s="1">
-        <v>1</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="H14" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="I14" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="J14" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="K14" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="L14" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="M14" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="N14" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="O14" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="P14" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q14" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="R14" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="S14" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="T14" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="U14" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="V14" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="W14" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="X14" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="Y14" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="Z14" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA14" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" customHeight="1" spans="3:29">
-      <c r="C15" s="1">
-        <v>10010</v>
-      </c>
-      <c r="D15" s="1">
-        <v>1</v>
-      </c>
-      <c r="E15" s="1">
-        <v>1</v>
-      </c>
-      <c r="F15" s="1">
-        <v>1</v>
-      </c>
-      <c r="G15" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="H15" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="I15" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="J15" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="K15" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="L15" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="M15" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="N15" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="O15" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="P15" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q15" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="R15" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="S15" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="T15" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="U15" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="V15" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="W15" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="X15" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="Y15" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="Z15" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA15" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="16" customHeight="1" spans="3:29">
-      <c r="C16" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="D16" s="1">
-        <v>0</v>
-      </c>
-      <c r="E16" s="1">
-        <v>1</v>
-      </c>
-      <c r="F16" s="1">
-        <v>1</v>
-      </c>
-      <c r="G16" s="1">
-        <v>0</v>
-      </c>
-      <c r="H16" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="I16" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="J16" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="K16" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="L16" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="M16" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="N16" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="O16" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="P16" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q16" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="R16" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="S16" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="T16" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="U16" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="V16" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="W16" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="X16" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="Y16" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="Z16" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA16" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" customHeight="1" spans="3:27">
-      <c r="C17" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="D17" s="1">
-        <v>0</v>
-      </c>
-      <c r="E17" s="1">
-        <v>1</v>
-      </c>
-      <c r="F17" s="1">
-        <v>1</v>
-      </c>
-      <c r="G17" s="1">
-        <v>0</v>
-      </c>
-      <c r="H17" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="I17" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="J17" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="K17" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="L17" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="M17" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="N17" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="O17" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="P17" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q17" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="R17" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="S17" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="T17" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="U17" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="V17" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="W17" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="X17" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="Y17" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="Z17" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA17" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" customHeight="1" spans="3:27">
-      <c r="C18" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="D18" s="1">
-        <v>1</v>
-      </c>
-      <c r="E18" s="1">
-        <v>1</v>
-      </c>
-      <c r="F18" s="1">
-        <v>1</v>
-      </c>
-      <c r="G18" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="H18" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="I18" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="J18" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="K18" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="L18" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="M18" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="N18" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="O18" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="P18" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q18" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="R18" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="S18" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="T18" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="U18" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="V18" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="W18" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="X18" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="Y18" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="Z18" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA18" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" customHeight="1" spans="3:27">
-      <c r="C19" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="D19" s="1">
-        <v>1</v>
-      </c>
-      <c r="E19" s="1">
-        <v>1</v>
-      </c>
-      <c r="F19" s="1">
-        <v>1</v>
-      </c>
-      <c r="G19" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="H19" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="I19" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="J19" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="K19" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="L19" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="M19" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="N19" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="O19" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="P19" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q19" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="R19" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="S19" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="T19" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="U19" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="V19" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="W19" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="X19" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="Y19" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="Z19" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA19" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" customHeight="1" spans="3:27">
-      <c r="C20" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="D20" s="1">
-        <v>1</v>
-      </c>
-      <c r="E20" s="1">
-        <v>1</v>
-      </c>
-      <c r="F20" s="1">
-        <v>1</v>
-      </c>
-      <c r="G20" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="H20" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="I20" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="J20" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="K20" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="L20" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="M20" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="N20" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="O20" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="P20" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q20" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="R20" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="S20" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="T20" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="U20" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="V20" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="W20" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="X20" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="Y20" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="Z20" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA20" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" customHeight="1" spans="3:27">
-      <c r="C21" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="D21" s="1">
-        <v>1</v>
-      </c>
-      <c r="E21" s="1">
-        <v>1</v>
-      </c>
-      <c r="F21" s="1">
-        <v>1</v>
-      </c>
-      <c r="G21" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="H21" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="I21" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="J21" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="K21" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="L21" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="M21" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="N21" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="O21" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="P21" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q21" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="R21" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="S21" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="T21" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="U21" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="V21" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="W21" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="X21" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="Y21" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="Z21" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA21" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" customHeight="1" spans="3:27">
-      <c r="C22" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="D22" s="1">
-        <v>1</v>
-      </c>
-      <c r="E22" s="1">
-        <v>1</v>
-      </c>
-      <c r="F22" s="1">
-        <v>1</v>
-      </c>
-      <c r="G22" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="H22" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="I22" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="J22" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="K22" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="L22" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="M22" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="N22" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="O22" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="P22" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q22" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="R22" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="S22" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="T22" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="U22" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="V22" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="W22" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="X22" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="Y22" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="Z22" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA22" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" customHeight="1" spans="3:27">
-      <c r="C23" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="D23" s="1">
-        <v>1</v>
-      </c>
-      <c r="E23" s="1">
-        <v>1</v>
-      </c>
-      <c r="F23" s="1">
-        <v>1</v>
-      </c>
-      <c r="G23" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="H23" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="I23" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="J23" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="K23" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="L23" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="M23" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="N23" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="O23" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="P23" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q23" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="R23" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="S23" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="T23" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="U23" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="V23" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="W23" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="X23" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="Y23" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="Z23" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA23" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" customHeight="1" spans="3:27">
-      <c r="C24" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="D24" s="1">
-        <v>1</v>
-      </c>
-      <c r="E24" s="1">
-        <v>1</v>
-      </c>
-      <c r="F24" s="1">
-        <v>1</v>
-      </c>
-      <c r="G24" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="H24" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="I24" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="J24" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="K24" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="L24" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="M24" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="N24" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="O24" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="P24" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q24" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="R24" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="S24" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="T24" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="U24" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="V24" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="W24" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="X24" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="Y24" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="Z24" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA24" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" customHeight="1" spans="3:27">
-      <c r="C25" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="D25" s="1">
-        <v>1</v>
-      </c>
-      <c r="E25" s="1">
-        <v>1</v>
-      </c>
-      <c r="F25" s="1">
-        <v>1</v>
-      </c>
-      <c r="G25" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="H25" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="I25" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="J25" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="K25" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="L25" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="M25" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="N25" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="O25" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="P25" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q25" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="R25" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="S25" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="T25" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="U25" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="V25" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="W25" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="X25" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="Y25" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="Z25" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA25" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" customHeight="1" spans="3:27">
-      <c r="C26" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="D26" s="1">
-        <v>1</v>
-      </c>
-      <c r="E26" s="1">
-        <v>1</v>
-      </c>
-      <c r="F26" s="1">
-        <v>1</v>
-      </c>
-      <c r="G26" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="H26" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="I26" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="J26" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="K26" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="L26" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="M26" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="N26" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="O26" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="P26" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q26" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="R26" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="S26" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="T26" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="U26" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="V26" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="W26" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="X26" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="Y26" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="Z26" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA26" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" customHeight="1" spans="3:27">
-      <c r="C27" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="D27" s="1">
-        <v>1</v>
-      </c>
-      <c r="E27" s="1">
-        <v>1</v>
-      </c>
-      <c r="F27" s="1">
-        <v>1</v>
-      </c>
-      <c r="G27" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="H27" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="I27" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="J27" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="K27" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="L27" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="M27" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="N27" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="O27" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="P27" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q27" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="R27" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="S27" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="T27" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="U27" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="V27" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="W27" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="X27" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="Y27" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="Z27" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA27" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" customHeight="1" spans="3:27">
-      <c r="C28" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="D28" s="1">
-        <v>1</v>
-      </c>
-      <c r="E28" s="1">
-        <v>1</v>
-      </c>
-      <c r="F28" s="1">
-        <v>1</v>
-      </c>
-      <c r="G28" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="H28" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="I28" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="J28" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="K28" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="L28" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="M28" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="N28" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="O28" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="P28" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q28" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="R28" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="S28" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="T28" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="U28" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="V28" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="W28" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="X28" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="Y28" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="Z28" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA28" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="29" customHeight="1" spans="3:27">
-      <c r="C29" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="D29" s="1">
-        <v>1</v>
-      </c>
-      <c r="E29" s="1">
-        <v>1</v>
-      </c>
-      <c r="F29" s="1">
-        <v>1</v>
-      </c>
-      <c r="G29" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="H29" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="I29" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="J29" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="K29" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="L29" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="M29" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="N29" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="O29" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="P29" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q29" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="R29" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="S29" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="T29" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="U29" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="V29" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="W29" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="X29" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="Y29" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="Z29" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA29" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="30" customHeight="1" spans="3:27">
-      <c r="C30" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="D30" s="1">
-        <v>0</v>
-      </c>
-      <c r="E30" s="1">
-        <v>1</v>
-      </c>
-      <c r="F30" s="1">
-        <v>1</v>
-      </c>
-      <c r="G30" s="1">
-        <v>0</v>
-      </c>
-      <c r="H30" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="I30" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="J30" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="K30" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="L30" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="M30" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="N30" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="O30" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="P30" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q30" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="R30" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="S30" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="T30" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="U30" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="V30" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="W30" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="X30" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="Y30" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="Z30" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA30" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" customHeight="1" spans="3:27">
-      <c r="C31" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="D31" s="1">
-        <v>0</v>
-      </c>
-      <c r="E31" s="1">
-        <v>1</v>
-      </c>
-      <c r="F31" s="1">
-        <v>1</v>
-      </c>
-      <c r="G31" s="1">
-        <v>0</v>
-      </c>
-      <c r="H31" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="I31" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="J31" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="K31" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="L31" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="M31" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="N31" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="O31" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="P31" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q31" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="R31" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="S31" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="T31" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="U31" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="V31" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="W31" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="X31" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="Y31" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="Z31" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA31" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" customHeight="1" spans="3:27">
-      <c r="C32" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="D32" s="1">
-        <v>1</v>
-      </c>
-      <c r="E32" s="1">
-        <v>1</v>
-      </c>
-      <c r="F32" s="1">
-        <v>1</v>
-      </c>
-      <c r="G32" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="H32" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="I32" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="J32" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="K32" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="L32" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="M32" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="N32" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="O32" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="P32" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q32" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="R32" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="S32" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="T32" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="U32" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="V32" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="W32" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="X32" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="Y32" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="Z32" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA32" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" customHeight="1" spans="3:27">
-      <c r="C33" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="D33" s="1">
-        <v>1</v>
-      </c>
-      <c r="E33" s="1">
-        <v>1</v>
-      </c>
-      <c r="F33" s="1">
-        <v>1</v>
-      </c>
-      <c r="G33" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="H33" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="I33" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="J33" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="K33" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="L33" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="M33" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="N33" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="O33" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="P33" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q33" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="R33" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="S33" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="T33" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="U33" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="V33" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="W33" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="X33" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="Y33" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="Z33" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA33" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" customHeight="1" spans="3:27">
-      <c r="C34" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="D34" s="1">
-        <v>1</v>
-      </c>
-      <c r="E34" s="1">
-        <v>1</v>
-      </c>
-      <c r="F34" s="1">
-        <v>1</v>
-      </c>
-      <c r="G34" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="H34" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="I34" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="J34" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="K34" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="L34" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="M34" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="N34" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="O34" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="P34" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q34" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="R34" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="S34" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="T34" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="U34" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="V34" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="W34" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="X34" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="Y34" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="Z34" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA34" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" customHeight="1" spans="3:27">
-      <c r="C35" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="D35" s="1">
-        <v>1</v>
-      </c>
-      <c r="E35" s="1">
-        <v>1</v>
-      </c>
-      <c r="F35" s="1">
-        <v>1</v>
-      </c>
-      <c r="G35" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="H35" s="1" t="s">
-        <v>125</v>
-      </c>
-      <c r="I35" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="J35" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="K35" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="L35" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="M35" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="N35" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="O35" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="P35" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q35" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="R35" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="S35" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="T35" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="U35" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="V35" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="W35" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="X35" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="Y35" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="Z35" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA35" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" customHeight="1" spans="3:27">
-      <c r="C36" s="1">
-        <v>10031</v>
-      </c>
-      <c r="D36" s="1">
-        <v>1</v>
-      </c>
-      <c r="E36" s="1">
-        <v>1</v>
-      </c>
-      <c r="F36" s="1">
-        <v>1</v>
-      </c>
-      <c r="G36" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="H36" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="I36" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="J36" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="K36" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="L36" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="M36" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="N36" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="O36" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="P36" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q36" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="R36" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="S36" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="T36" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="U36" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="V36" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="W36" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="X36" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="Y36" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="Z36" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA36" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" customHeight="1" spans="3:27">
-      <c r="C37" s="1">
-        <v>10032</v>
-      </c>
-      <c r="D37" s="1">
-        <v>1</v>
-      </c>
-      <c r="E37" s="1">
-        <v>1</v>
-      </c>
-      <c r="F37" s="1">
-        <v>1</v>
-      </c>
-      <c r="G37" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="H37" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="I37" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="J37" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="K37" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="L37" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="M37" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="N37" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="O37" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="P37" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q37" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="R37" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="S37" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="T37" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="U37" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="V37" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="W37" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="X37" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="Y37" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="Z37" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA37" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" customHeight="1" spans="3:27">
-      <c r="C38" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="D38" s="1">
-        <v>1</v>
-      </c>
-      <c r="E38" s="1">
-        <v>1</v>
-      </c>
-      <c r="F38" s="1">
-        <v>1</v>
-      </c>
-      <c r="G38" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="H38" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="I38" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="J38" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="K38" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="L38" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="M38" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="N38" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="O38" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="P38" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q38" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="R38" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="S38" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="T38" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="U38" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="V38" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="W38" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="X38" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="Y38" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="Z38" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA38" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" customHeight="1" spans="3:27">
-      <c r="C39" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="D39" s="1">
-        <v>1</v>
-      </c>
-      <c r="E39" s="1">
-        <v>1</v>
-      </c>
-      <c r="F39" s="1">
-        <v>1</v>
-      </c>
-      <c r="G39" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="H39" s="1" t="s">
-        <v>134</v>
-      </c>
-      <c r="I39" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="J39" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="K39" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="L39" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="M39" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="N39" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="O39" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="P39" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q39" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="R39" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="S39" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="T39" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="U39" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="V39" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="W39" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="X39" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="Y39" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="Z39" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA39" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" customHeight="1" spans="3:27">
-      <c r="C40" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="D40" s="1">
-        <v>1</v>
-      </c>
-      <c r="E40" s="1">
-        <v>1</v>
-      </c>
-      <c r="F40" s="1">
-        <v>1</v>
-      </c>
-      <c r="G40" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="H40" s="1" t="s">
-        <v>137</v>
-      </c>
-      <c r="I40" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="J40" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="K40" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="L40" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="M40" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="N40" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="O40" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="P40" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q40" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="R40" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="S40" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="T40" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="U40" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="V40" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="W40" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="X40" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="Y40" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="Z40" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA40" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" customHeight="1" spans="3:27">
-      <c r="C41" s="1" t="s">
-        <v>138</v>
-      </c>
-      <c r="D41" s="1">
-        <v>1</v>
-      </c>
-      <c r="E41" s="1">
-        <v>1</v>
-      </c>
-      <c r="F41" s="1">
-        <v>1</v>
-      </c>
-      <c r="G41" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="H41" s="1" t="s">
-        <v>139</v>
-      </c>
-      <c r="I41" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="J41" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="K41" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="L41" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="M41" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="N41" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="O41" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="P41" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q41" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="R41" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="S41" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="T41" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="U41" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="V41" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="W41" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="X41" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="Y41" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="Z41" s="1">
-        <v>20</v>
-      </c>
-      <c r="AA41" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" customHeight="1" spans="3:27">
-      <c r="C42" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="D42" s="1">
-        <v>1</v>
-      </c>
-      <c r="E42" s="1">
-        <v>1</v>
-      </c>
-      <c r="F42" s="1">
-        <v>1</v>
-      </c>
-      <c r="G42" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="H42" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="I42" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="J42" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="K42" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="L42" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="M42" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="N42" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="O42" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="P42" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q42" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="R42" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="S42" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="T42" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="U42" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="V42" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="W42" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="X42" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="Y42" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="Z42" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA42" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="43" customHeight="1" spans="3:27">
-      <c r="C43" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="D43" s="1">
-        <v>1</v>
-      </c>
-      <c r="E43" s="1">
-        <v>1</v>
-      </c>
-      <c r="F43" s="1">
-        <v>1</v>
-      </c>
-      <c r="G43" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="H43" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="I43" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="J43" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="K43" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="L43" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="M43" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="N43" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="O43" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="P43" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q43" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="R43" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="S43" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="T43" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="U43" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="V43" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="W43" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="X43" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="Y43" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="Z43" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA43" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="44" customHeight="1" spans="3:27">
-      <c r="C44" s="1" t="s">
-        <v>146</v>
-      </c>
-      <c r="D44" s="1">
-        <v>0</v>
-      </c>
-      <c r="E44" s="1">
-        <v>1</v>
-      </c>
-      <c r="F44" s="1">
-        <v>1</v>
-      </c>
-      <c r="G44" s="1">
-        <v>0</v>
-      </c>
-      <c r="H44" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="I44" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="J44" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="K44" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="L44" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="M44" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="N44" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="O44" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="P44" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q44" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="R44" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="S44" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="T44" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="U44" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="V44" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="W44" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="X44" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="Y44" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="Z44" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA44" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" customHeight="1" spans="3:27">
-      <c r="C45" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="D45" s="1">
-        <v>0</v>
-      </c>
-      <c r="E45" s="1">
-        <v>1</v>
-      </c>
-      <c r="F45" s="1">
-        <v>1</v>
-      </c>
-      <c r="G45" s="1">
-        <v>0</v>
-      </c>
-      <c r="H45" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="I45" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="J45" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="K45" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="L45" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="M45" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="N45" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="O45" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="P45" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q45" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="R45" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="S45" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="T45" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="U45" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="V45" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="W45" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="X45" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="Y45" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="Z45" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA45" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" customHeight="1" spans="3:27">
-      <c r="C46" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="D46" s="1">
-        <v>1</v>
-      </c>
-      <c r="E46" s="1">
-        <v>1</v>
-      </c>
-      <c r="F46" s="1">
-        <v>1</v>
-      </c>
-      <c r="G46" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="H46" s="1" t="s">
-        <v>150</v>
-      </c>
-      <c r="I46" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="J46" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="K46" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="L46" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="M46" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="N46" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="O46" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="P46" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q46" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="R46" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="S46" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="T46" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="U46" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="V46" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="W46" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="X46" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="Y46" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="Z46" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA46" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" customHeight="1" spans="3:27">
-      <c r="C47" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="D47" s="1">
-        <v>1</v>
-      </c>
-      <c r="E47" s="1">
-        <v>1</v>
-      </c>
-      <c r="F47" s="1">
-        <v>1</v>
-      </c>
-      <c r="G47" s="1" t="s">
-        <v>149</v>
-      </c>
-      <c r="H47" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="I47" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="J47" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="K47" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="L47" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="M47" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="N47" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="O47" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="P47" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q47" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="R47" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="S47" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="T47" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="U47" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="V47" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="W47" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="X47" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="Y47" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="Z47" s="1">
-        <v>20</v>
-      </c>
-      <c r="AA47" s="1">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:J5" errorStyle="warning">
-      <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="360" verticalDpi="360"/>
-  <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
   <dimension ref="C3:W77"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
@@ -5322,188 +1334,188 @@
         <v>0</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>154</v>
+        <v>1</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F3" s="4"/>
       <c r="G3" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="I3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="J3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="K3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="J3" s="4" t="s">
+      <c r="L3" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="M3" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="N3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="O3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="K3" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="L3" s="4" t="s">
+      <c r="P3" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="M3" s="4" t="s">
+      <c r="Q3" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="N3" s="4" t="s">
+      <c r="R3" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="O3" s="4" t="s">
+      <c r="S3" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="T3" s="4" t="s">
         <v>16</v>
-      </c>
-      <c r="P3" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q3" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="R3" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="S3" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="T3" s="4" t="s">
-        <v>22</v>
       </c>
       <c r="U3" s="4" t="s">
         <v>17</v>
       </c>
       <c r="V3" s="4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="W3" s="4" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" s="1" customFormat="1" customHeight="1" spans="3:23">
       <c r="C4" s="4" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>154</v>
+        <v>1</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="F4" s="4"/>
       <c r="G4" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="L4" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="M4" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="I4" s="4" t="s">
+      <c r="N4" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="J4" s="4" t="s">
+      <c r="O4" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="P4" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q4" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="R4" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="K4" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="L4" s="4" t="s">
+      <c r="S4" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="M4" s="4" t="s">
+      <c r="T4" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="N4" s="4" t="s">
+      <c r="U4" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="O4" s="4" t="s">
+      <c r="V4" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="W4" s="4" t="s">
         <v>38</v>
-      </c>
-      <c r="P4" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q4" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="R4" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="S4" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="T4" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="U4" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="V4" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="W4" s="4" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" customHeight="1" spans="3:23">
       <c r="C5" s="4" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="F5" s="4"/>
       <c r="G5" s="4" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="L5" s="4" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="M5" s="4" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="N5" s="4" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="O5" s="4" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="P5" s="4" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="R5" s="4" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="S5" s="4" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="U5" s="4" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="V5" s="4" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="W5" s="4" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" customHeight="1" spans="3:23">
@@ -5517,13 +1529,13 @@
         <v>1001</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>159</v>
+        <v>41</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>160</v>
+        <v>42</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>161</v>
+        <v>43</v>
       </c>
       <c r="I6" s="1">
         <v>0</v>
@@ -5582,13 +1594,13 @@
         <v>1002</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>162</v>
+        <v>44</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>160</v>
+        <v>42</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>163</v>
+        <v>45</v>
       </c>
       <c r="I7" s="1">
         <v>0</v>
@@ -5647,13 +1659,13 @@
         <v>1003</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>164</v>
+        <v>46</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>160</v>
+        <v>42</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>163</v>
+        <v>45</v>
       </c>
       <c r="I8" s="1">
         <v>0</v>
@@ -5712,13 +1724,13 @@
         <v>1004</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>165</v>
+        <v>47</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>160</v>
+        <v>42</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>163</v>
+        <v>45</v>
       </c>
       <c r="I9" s="1">
         <v>0</v>
@@ -5777,13 +1789,13 @@
         <v>1005</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>166</v>
+        <v>48</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>160</v>
+        <v>42</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>163</v>
+        <v>45</v>
       </c>
       <c r="I10" s="1">
         <v>0</v>
@@ -5842,13 +1854,13 @@
         <v>1006</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>167</v>
+        <v>49</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>160</v>
+        <v>42</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>163</v>
+        <v>45</v>
       </c>
       <c r="I11" s="1">
         <v>0</v>
@@ -5907,13 +1919,13 @@
         <v>1007</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>168</v>
+        <v>50</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>160</v>
+        <v>42</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>163</v>
+        <v>45</v>
       </c>
       <c r="I12" s="1">
         <v>0</v>
@@ -5973,7 +1985,7 @@
     </row>
     <row r="14" s="1" customFormat="1" customHeight="1" spans="3:23">
       <c r="C14" s="1">
-        <v>10021</v>
+        <v>10022</v>
       </c>
       <c r="D14" s="1">
         <v>1</v>
@@ -5982,13 +1994,13 @@
         <v>1002</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>162</v>
+        <v>44</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>169</v>
+        <v>51</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>170</v>
+        <v>52</v>
       </c>
       <c r="I14" s="1">
         <v>0</v>
@@ -6038,7 +2050,7 @@
     </row>
     <row r="15" s="1" customFormat="1" customHeight="1" spans="3:23">
       <c r="C15" s="1">
-        <v>10031</v>
+        <v>10032</v>
       </c>
       <c r="D15" s="1">
         <v>1</v>
@@ -6047,13 +2059,13 @@
         <v>1003</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>164</v>
+        <v>46</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>169</v>
+        <v>51</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>170</v>
+        <v>52</v>
       </c>
       <c r="I15" s="1">
         <v>0</v>
@@ -6103,7 +2115,7 @@
     </row>
     <row r="16" s="1" customFormat="1" customHeight="1" spans="3:23">
       <c r="C16" s="1">
-        <v>10041</v>
+        <v>10042</v>
       </c>
       <c r="D16" s="1">
         <v>1</v>
@@ -6112,13 +2124,13 @@
         <v>1004</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>165</v>
+        <v>47</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>169</v>
+        <v>51</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>170</v>
+        <v>52</v>
       </c>
       <c r="I16" s="1">
         <v>0</v>
@@ -6168,7 +2180,7 @@
     </row>
     <row r="17" s="1" customFormat="1" customHeight="1" spans="3:23">
       <c r="C17" s="1">
-        <v>10071</v>
+        <v>10072</v>
       </c>
       <c r="D17" s="1">
         <v>1</v>
@@ -6177,13 +2189,13 @@
         <v>1007</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>168</v>
+        <v>50</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>169</v>
+        <v>51</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>170</v>
+        <v>52</v>
       </c>
       <c r="I17" s="1">
         <v>0</v>
@@ -6238,7 +2250,7 @@
     </row>
     <row r="19" s="2" customFormat="1" customHeight="1" spans="3:23">
       <c r="C19" s="1">
-        <v>10022</v>
+        <v>10023</v>
       </c>
       <c r="D19" s="1">
         <v>1</v>
@@ -6247,13 +2259,13 @@
         <v>1002</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>162</v>
+        <v>44</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>171</v>
+        <v>53</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>172</v>
+        <v>54</v>
       </c>
       <c r="I19" s="1">
         <v>0</v>
@@ -6303,7 +2315,7 @@
     </row>
     <row r="20" s="2" customFormat="1" customHeight="1" spans="3:23">
       <c r="C20" s="1">
-        <v>10032</v>
+        <v>10033</v>
       </c>
       <c r="D20" s="1">
         <v>1</v>
@@ -6312,13 +2324,13 @@
         <v>1003</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>164</v>
+        <v>46</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>171</v>
+        <v>53</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>172</v>
+        <v>54</v>
       </c>
       <c r="I20" s="1">
         <v>0</v>
@@ -6368,7 +2380,7 @@
     </row>
     <row r="21" s="2" customFormat="1" customHeight="1" spans="3:23">
       <c r="C21" s="1">
-        <v>10042</v>
+        <v>10043</v>
       </c>
       <c r="D21" s="1">
         <v>1</v>
@@ -6377,13 +2389,13 @@
         <v>1004</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>165</v>
+        <v>47</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>171</v>
+        <v>53</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>172</v>
+        <v>54</v>
       </c>
       <c r="I21" s="1">
         <v>0</v>
@@ -6433,7 +2445,7 @@
     </row>
     <row r="22" s="2" customFormat="1" customHeight="1" spans="3:23">
       <c r="C22" s="1">
-        <v>10072</v>
+        <v>10073</v>
       </c>
       <c r="D22" s="1">
         <v>1</v>
@@ -6442,13 +2454,13 @@
         <v>1007</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>168</v>
+        <v>50</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>171</v>
+        <v>53</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>172</v>
+        <v>54</v>
       </c>
       <c r="I22" s="1">
         <v>0</v>
@@ -6521,7 +2533,7 @@
     </row>
     <row r="24" s="2" customFormat="1" customHeight="1" spans="3:23">
       <c r="C24" s="1">
-        <v>10023</v>
+        <v>10024</v>
       </c>
       <c r="D24" s="1">
         <v>1</v>
@@ -6530,13 +2542,13 @@
         <v>1002</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>162</v>
+        <v>44</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>173</v>
+        <v>55</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>174</v>
+        <v>56</v>
       </c>
       <c r="I24" s="1">
         <v>0</v>
@@ -6586,7 +2598,7 @@
     </row>
     <row r="25" s="2" customFormat="1" customHeight="1" spans="3:23">
       <c r="C25" s="1">
-        <v>10033</v>
+        <v>10034</v>
       </c>
       <c r="D25" s="1">
         <v>1</v>
@@ -6595,13 +2607,13 @@
         <v>1003</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>164</v>
+        <v>46</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>173</v>
+        <v>55</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>174</v>
+        <v>56</v>
       </c>
       <c r="I25" s="1">
         <v>0</v>
@@ -6651,7 +2663,7 @@
     </row>
     <row r="26" s="2" customFormat="1" customHeight="1" spans="3:23">
       <c r="C26" s="1">
-        <v>10043</v>
+        <v>10044</v>
       </c>
       <c r="D26" s="1">
         <v>1</v>
@@ -6660,13 +2672,13 @@
         <v>1004</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>165</v>
+        <v>47</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>173</v>
+        <v>55</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>174</v>
+        <v>56</v>
       </c>
       <c r="I26" s="1">
         <v>0</v>
@@ -6716,7 +2728,7 @@
     </row>
     <row r="27" s="1" customFormat="1" customHeight="1" spans="3:23">
       <c r="C27" s="1">
-        <v>10073</v>
+        <v>10074</v>
       </c>
       <c r="D27" s="1">
         <v>1</v>
@@ -6725,13 +2737,13 @@
         <v>1007</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>168</v>
+        <v>50</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>173</v>
+        <v>55</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>174</v>
+        <v>56</v>
       </c>
       <c r="I27" s="1">
         <v>0</v>
@@ -6791,13 +2803,13 @@
         <v>2001</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>175</v>
+        <v>57</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>160</v>
+        <v>42</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>176</v>
+        <v>58</v>
       </c>
       <c r="I31" s="1">
         <v>0</v>
@@ -6856,13 +2868,13 @@
         <v>2002</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>177</v>
+        <v>59</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>160</v>
+        <v>42</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>163</v>
+        <v>45</v>
       </c>
       <c r="I32" s="1">
         <v>0</v>
@@ -6921,13 +2933,13 @@
         <v>2003</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>178</v>
+        <v>60</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>160</v>
+        <v>42</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>163</v>
+        <v>45</v>
       </c>
       <c r="I33" s="1">
         <v>0</v>
@@ -6986,13 +2998,13 @@
         <v>2004</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>179</v>
+        <v>61</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>160</v>
+        <v>42</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>163</v>
+        <v>45</v>
       </c>
       <c r="I34" s="1">
         <v>0</v>
@@ -7051,13 +3063,13 @@
         <v>2005</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>180</v>
+        <v>62</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>160</v>
+        <v>42</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>163</v>
+        <v>45</v>
       </c>
       <c r="I35" s="1">
         <v>0</v>
@@ -7116,13 +3128,13 @@
         <v>2006</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>181</v>
+        <v>63</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>160</v>
+        <v>42</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>163</v>
+        <v>45</v>
       </c>
       <c r="I36" s="1">
         <v>0</v>
@@ -7181,13 +3193,13 @@
         <v>2007</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>182</v>
+        <v>64</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>160</v>
+        <v>42</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>163</v>
+        <v>45</v>
       </c>
       <c r="I37" s="1">
         <v>0</v>
@@ -7241,7 +3253,7 @@
     </row>
     <row r="39" s="1" customFormat="1" customHeight="1" spans="3:23">
       <c r="C39" s="1">
-        <v>20021</v>
+        <v>20022</v>
       </c>
       <c r="D39" s="1">
         <v>1</v>
@@ -7250,13 +3262,13 @@
         <v>2002</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>177</v>
+        <v>59</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>169</v>
+        <v>51</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>170</v>
+        <v>52</v>
       </c>
       <c r="I39" s="1">
         <v>0</v>
@@ -7306,7 +3318,7 @@
     </row>
     <row r="40" s="1" customFormat="1" customHeight="1" spans="3:23">
       <c r="C40" s="1">
-        <v>20031</v>
+        <v>20032</v>
       </c>
       <c r="D40" s="1">
         <v>1</v>
@@ -7315,13 +3327,13 @@
         <v>2003</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>178</v>
+        <v>60</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>169</v>
+        <v>51</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>170</v>
+        <v>52</v>
       </c>
       <c r="I40" s="1">
         <v>0</v>
@@ -7371,7 +3383,7 @@
     </row>
     <row r="41" s="1" customFormat="1" customHeight="1" spans="3:23">
       <c r="C41" s="1">
-        <v>20041</v>
+        <v>20042</v>
       </c>
       <c r="D41" s="1">
         <v>1</v>
@@ -7380,13 +3392,13 @@
         <v>2004</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>179</v>
+        <v>61</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>169</v>
+        <v>51</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>170</v>
+        <v>52</v>
       </c>
       <c r="I41" s="1">
         <v>0</v>
@@ -7436,7 +3448,7 @@
     </row>
     <row r="42" s="1" customFormat="1" customHeight="1" spans="3:23">
       <c r="C42" s="1">
-        <v>20071</v>
+        <v>20072</v>
       </c>
       <c r="D42" s="1">
         <v>1</v>
@@ -7445,13 +3457,13 @@
         <v>2007</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>182</v>
+        <v>64</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>169</v>
+        <v>51</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>170</v>
+        <v>52</v>
       </c>
       <c r="I42" s="1">
         <v>0</v>
@@ -7506,7 +3518,7 @@
     </row>
     <row r="44" s="2" customFormat="1" customHeight="1" spans="3:23">
       <c r="C44" s="1">
-        <v>20022</v>
+        <v>20023</v>
       </c>
       <c r="D44" s="1">
         <v>1</v>
@@ -7515,13 +3527,13 @@
         <v>2002</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>177</v>
+        <v>59</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>171</v>
+        <v>53</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>172</v>
+        <v>54</v>
       </c>
       <c r="I44" s="1">
         <v>0</v>
@@ -7571,7 +3583,7 @@
     </row>
     <row r="45" s="2" customFormat="1" customHeight="1" spans="3:23">
       <c r="C45" s="1">
-        <v>20032</v>
+        <v>20033</v>
       </c>
       <c r="D45" s="1">
         <v>1</v>
@@ -7580,13 +3592,13 @@
         <v>2003</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>178</v>
+        <v>60</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>171</v>
+        <v>53</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>172</v>
+        <v>54</v>
       </c>
       <c r="I45" s="1">
         <v>0</v>
@@ -7636,7 +3648,7 @@
     </row>
     <row r="46" s="2" customFormat="1" customHeight="1" spans="3:23">
       <c r="C46" s="1">
-        <v>20042</v>
+        <v>20043</v>
       </c>
       <c r="D46" s="1">
         <v>1</v>
@@ -7645,13 +3657,13 @@
         <v>2004</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>179</v>
+        <v>61</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>171</v>
+        <v>53</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>172</v>
+        <v>54</v>
       </c>
       <c r="I46" s="1">
         <v>0</v>
@@ -7701,7 +3713,7 @@
     </row>
     <row r="47" s="2" customFormat="1" customHeight="1" spans="3:23">
       <c r="C47" s="1">
-        <v>20072</v>
+        <v>20073</v>
       </c>
       <c r="D47" s="1">
         <v>1</v>
@@ -7710,13 +3722,13 @@
         <v>2007</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>182</v>
+        <v>64</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>171</v>
+        <v>53</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>172</v>
+        <v>54</v>
       </c>
       <c r="I47" s="1">
         <v>0</v>
@@ -7787,7 +3799,7 @@
     </row>
     <row r="49" s="2" customFormat="1" customHeight="1" spans="3:23">
       <c r="C49" s="1">
-        <v>20023</v>
+        <v>20024</v>
       </c>
       <c r="D49" s="1">
         <v>1</v>
@@ -7796,13 +3808,13 @@
         <v>2002</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>177</v>
+        <v>59</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>173</v>
+        <v>55</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>174</v>
+        <v>56</v>
       </c>
       <c r="I49" s="1">
         <v>0</v>
@@ -7852,7 +3864,7 @@
     </row>
     <row r="50" s="2" customFormat="1" customHeight="1" spans="3:23">
       <c r="C50" s="1">
-        <v>20033</v>
+        <v>20034</v>
       </c>
       <c r="D50" s="1">
         <v>1</v>
@@ -7861,13 +3873,13 @@
         <v>2003</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>178</v>
+        <v>60</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>173</v>
+        <v>55</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>174</v>
+        <v>56</v>
       </c>
       <c r="I50" s="1">
         <v>0</v>
@@ -7917,7 +3929,7 @@
     </row>
     <row r="51" s="2" customFormat="1" customHeight="1" spans="3:23">
       <c r="C51" s="1">
-        <v>20043</v>
+        <v>20044</v>
       </c>
       <c r="D51" s="1">
         <v>1</v>
@@ -7926,13 +3938,13 @@
         <v>2004</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>179</v>
+        <v>61</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>173</v>
+        <v>55</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>174</v>
+        <v>56</v>
       </c>
       <c r="I51" s="1">
         <v>0</v>
@@ -7982,7 +3994,7 @@
     </row>
     <row r="52" s="1" customFormat="1" customHeight="1" spans="3:23">
       <c r="C52" s="1">
-        <v>20073</v>
+        <v>20074</v>
       </c>
       <c r="D52" s="1">
         <v>1</v>
@@ -7991,13 +4003,13 @@
         <v>2007</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>182</v>
+        <v>64</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>173</v>
+        <v>55</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>174</v>
+        <v>56</v>
       </c>
       <c r="I52" s="1">
         <v>0</v>
@@ -8057,13 +4069,13 @@
         <v>3001</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>183</v>
+        <v>65</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>160</v>
+        <v>42</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>184</v>
+        <v>66</v>
       </c>
       <c r="I56" s="1">
         <v>0</v>
@@ -8122,13 +4134,13 @@
         <v>3002</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>185</v>
+        <v>67</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>160</v>
+        <v>42</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>163</v>
+        <v>45</v>
       </c>
       <c r="I57" s="1">
         <v>0</v>
@@ -8187,13 +4199,13 @@
         <v>3003</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>186</v>
+        <v>68</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>160</v>
+        <v>42</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>163</v>
+        <v>45</v>
       </c>
       <c r="I58" s="1">
         <v>0</v>
@@ -8252,13 +4264,13 @@
         <v>3004</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>187</v>
+        <v>69</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>160</v>
+        <v>42</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>163</v>
+        <v>45</v>
       </c>
       <c r="I59" s="1">
         <v>0</v>
@@ -8317,13 +4329,13 @@
         <v>3005</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>188</v>
+        <v>70</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>160</v>
+        <v>42</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>163</v>
+        <v>45</v>
       </c>
       <c r="I60" s="1">
         <v>0</v>
@@ -8382,13 +4394,13 @@
         <v>3006</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>189</v>
+        <v>71</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>160</v>
+        <v>42</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>163</v>
+        <v>45</v>
       </c>
       <c r="I61" s="1">
         <v>0</v>
@@ -8447,13 +4459,13 @@
         <v>3007</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>190</v>
+        <v>72</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>160</v>
+        <v>42</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>163</v>
+        <v>45</v>
       </c>
       <c r="I62" s="1">
         <v>0</v>
@@ -8507,7 +4519,7 @@
     </row>
     <row r="64" s="1" customFormat="1" customHeight="1" spans="3:23">
       <c r="C64" s="1">
-        <v>30021</v>
+        <v>30022</v>
       </c>
       <c r="D64" s="1">
         <v>1</v>
@@ -8516,13 +4528,13 @@
         <v>3002</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>185</v>
+        <v>67</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>169</v>
+        <v>51</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>170</v>
+        <v>52</v>
       </c>
       <c r="I64" s="1">
         <v>0</v>
@@ -8572,7 +4584,7 @@
     </row>
     <row r="65" s="1" customFormat="1" customHeight="1" spans="3:23">
       <c r="C65" s="1">
-        <v>30031</v>
+        <v>30032</v>
       </c>
       <c r="D65" s="1">
         <v>1</v>
@@ -8581,13 +4593,13 @@
         <v>3003</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>186</v>
+        <v>68</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>169</v>
+        <v>51</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>170</v>
+        <v>52</v>
       </c>
       <c r="I65" s="1">
         <v>0</v>
@@ -8637,7 +4649,7 @@
     </row>
     <row r="66" s="1" customFormat="1" customHeight="1" spans="3:23">
       <c r="C66" s="1">
-        <v>30041</v>
+        <v>30042</v>
       </c>
       <c r="D66" s="1">
         <v>1</v>
@@ -8646,13 +4658,13 @@
         <v>3004</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>187</v>
+        <v>69</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>169</v>
+        <v>51</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>170</v>
+        <v>52</v>
       </c>
       <c r="I66" s="1">
         <v>0</v>
@@ -8702,7 +4714,7 @@
     </row>
     <row r="67" s="1" customFormat="1" customHeight="1" spans="3:23">
       <c r="C67" s="1">
-        <v>30071</v>
+        <v>30072</v>
       </c>
       <c r="D67" s="1">
         <v>1</v>
@@ -8711,13 +4723,13 @@
         <v>3007</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>190</v>
+        <v>72</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>169</v>
+        <v>51</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>170</v>
+        <v>52</v>
       </c>
       <c r="I67" s="1">
         <v>0</v>
@@ -8772,7 +4784,7 @@
     </row>
     <row r="69" s="2" customFormat="1" customHeight="1" spans="3:23">
       <c r="C69" s="1">
-        <v>30022</v>
+        <v>30023</v>
       </c>
       <c r="D69" s="1">
         <v>1</v>
@@ -8781,13 +4793,13 @@
         <v>3002</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>185</v>
+        <v>67</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>171</v>
+        <v>53</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>172</v>
+        <v>54</v>
       </c>
       <c r="I69" s="1">
         <v>0</v>
@@ -8837,7 +4849,7 @@
     </row>
     <row r="70" s="2" customFormat="1" customHeight="1" spans="3:23">
       <c r="C70" s="1">
-        <v>30032</v>
+        <v>30033</v>
       </c>
       <c r="D70" s="1">
         <v>1</v>
@@ -8846,13 +4858,13 @@
         <v>3003</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>186</v>
+        <v>68</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>171</v>
+        <v>53</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>172</v>
+        <v>54</v>
       </c>
       <c r="I70" s="1">
         <v>0</v>
@@ -8902,7 +4914,7 @@
     </row>
     <row r="71" s="2" customFormat="1" customHeight="1" spans="3:23">
       <c r="C71" s="1">
-        <v>30042</v>
+        <v>30043</v>
       </c>
       <c r="D71" s="1">
         <v>1</v>
@@ -8911,13 +4923,13 @@
         <v>3004</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>187</v>
+        <v>69</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>171</v>
+        <v>53</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>172</v>
+        <v>54</v>
       </c>
       <c r="I71" s="1">
         <v>0</v>
@@ -8967,7 +4979,7 @@
     </row>
     <row r="72" s="2" customFormat="1" customHeight="1" spans="3:23">
       <c r="C72" s="1">
-        <v>30072</v>
+        <v>30073</v>
       </c>
       <c r="D72" s="1">
         <v>1</v>
@@ -8976,13 +4988,13 @@
         <v>3007</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>190</v>
+        <v>72</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>171</v>
+        <v>53</v>
       </c>
       <c r="H72" s="1" t="s">
-        <v>191</v>
+        <v>73</v>
       </c>
       <c r="I72" s="1">
         <v>0</v>
@@ -9053,7 +5065,7 @@
     </row>
     <row r="74" s="2" customFormat="1" customHeight="1" spans="3:23">
       <c r="C74" s="1">
-        <v>30023</v>
+        <v>30024</v>
       </c>
       <c r="D74" s="1">
         <v>1</v>
@@ -9062,13 +5074,13 @@
         <v>3002</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>185</v>
+        <v>67</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>173</v>
+        <v>55</v>
       </c>
       <c r="H74" s="1" t="s">
-        <v>174</v>
+        <v>56</v>
       </c>
       <c r="I74" s="1">
         <v>0</v>
@@ -9118,7 +5130,7 @@
     </row>
     <row r="75" s="2" customFormat="1" customHeight="1" spans="3:23">
       <c r="C75" s="1">
-        <v>30033</v>
+        <v>30034</v>
       </c>
       <c r="D75" s="1">
         <v>1</v>
@@ -9127,13 +5139,13 @@
         <v>3003</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>186</v>
+        <v>68</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>173</v>
+        <v>55</v>
       </c>
       <c r="H75" s="1" t="s">
-        <v>174</v>
+        <v>56</v>
       </c>
       <c r="I75" s="1">
         <v>0</v>
@@ -9183,7 +5195,7 @@
     </row>
     <row r="76" s="2" customFormat="1" customHeight="1" spans="3:23">
       <c r="C76" s="1">
-        <v>30043</v>
+        <v>30044</v>
       </c>
       <c r="D76" s="1">
         <v>1</v>
@@ -9192,13 +5204,13 @@
         <v>3004</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>187</v>
+        <v>69</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>173</v>
+        <v>55</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>174</v>
+        <v>56</v>
       </c>
       <c r="I76" s="1">
         <v>0</v>
@@ -9248,7 +5260,7 @@
     </row>
     <row r="77" s="1" customFormat="1" customHeight="1" spans="3:23">
       <c r="C77" s="1">
-        <v>30073</v>
+        <v>30074</v>
       </c>
       <c r="D77" s="1">
         <v>1</v>
@@ -9257,13 +5269,13 @@
         <v>3007</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>190</v>
+        <v>72</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>173</v>
+        <v>55</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>192</v>
+        <v>74</v>
       </c>
       <c r="I77" s="1">
         <v>0</v>

--- a/Excel/SkillSuitConfig.xlsx
+++ b/Excel/SkillSuitConfig.xlsx
@@ -30,6 +30,7 @@
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>admin</author>
+    <author>Administrator</author>
   </authors>
   <commentList>
     <comment ref="C3" authorId="0">
@@ -100,12 +101,80 @@
         </r>
       </text>
     </comment>
+    <comment ref="AC4" authorId="1">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+特效ID</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="AD4" authorId="1">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+特效值</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="AE4" authorId="1">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+特效最大叠加层数
+0 无限次
+1 单次</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="88">
   <si>
     <t>_ID</t>
   </si>
@@ -146,22 +215,40 @@
     <t>增加伤害比例</t>
   </si>
   <si>
+    <t>无视防御</t>
+  </si>
+  <si>
+    <t>暴击率</t>
+  </si>
+  <si>
+    <t>暴击倍率</t>
+  </si>
+  <si>
     <t>致命率</t>
   </si>
   <si>
     <t>致命伤害</t>
   </si>
   <si>
+    <t>伤害加成</t>
+  </si>
+  <si>
     <t>攻击加成</t>
   </si>
   <si>
     <t>最终加成</t>
   </si>
   <si>
-    <t>无视防御</t>
-  </si>
-  <si>
-    <t>伤害加成</t>
+    <t>Accuracy</t>
+  </si>
+  <si>
+    <t>Speed</t>
+  </si>
+  <si>
+    <t>附加属性</t>
+  </si>
+  <si>
+    <t>属性值</t>
   </si>
   <si>
     <t>附带效果</t>
@@ -203,31 +290,52 @@
     <t>Percent</t>
   </si>
   <si>
+    <t>IgnoreDef</t>
+  </si>
+  <si>
+    <t>CritRate</t>
+  </si>
+  <si>
+    <t>CritDamage</t>
+  </si>
+  <si>
     <t>DeadlyRate</t>
   </si>
   <si>
     <t>DeadlyDamage</t>
   </si>
   <si>
+    <t>RateDamage</t>
+  </si>
+  <si>
     <t>AttrIncrea</t>
   </si>
   <si>
     <t>FinalIncrea</t>
   </si>
   <si>
-    <t>IgnoreDef</t>
-  </si>
-  <si>
-    <t>DamageIncrea</t>
+    <t>AttrId</t>
+  </si>
+  <si>
+    <t>AttrValue</t>
   </si>
   <si>
     <t>EffectId</t>
   </si>
   <si>
+    <t>EffectValue</t>
+  </si>
+  <si>
+    <t>EffectMax</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
     <t>string</t>
+  </si>
+  <si>
+    <t>double</t>
   </si>
   <si>
     <t>基础心法</t>
@@ -1306,30 +1414,30 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:W77"/>
+  <dimension ref="C3:AE77"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="6" width="9" style="1"/>
     <col min="7" max="7" width="13.75" style="1" customWidth="1"/>
-    <col min="8" max="8" width="29.125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="10.375" style="1" customWidth="1"/>
+    <col min="8" max="8" width="25.5833333333333" style="1" customWidth="1"/>
+    <col min="9" max="9" width="9.16666666666667" style="1" customWidth="1"/>
     <col min="10" max="10" width="9" style="1"/>
-    <col min="11" max="14" width="10.375" style="1" customWidth="1"/>
+    <col min="11" max="11" width="7.91666666666667" style="1" customWidth="1"/>
+    <col min="12" max="14" width="10.375" style="1" customWidth="1"/>
     <col min="15" max="15" width="10.875" style="1" customWidth="1"/>
-    <col min="16" max="16" width="13.75" style="1" customWidth="1"/>
-    <col min="17" max="17" width="13" style="1" customWidth="1"/>
-    <col min="18" max="18" width="9.08333333333333" style="1" customWidth="1"/>
-    <col min="19" max="19" width="12.625" style="1" customWidth="1"/>
-    <col min="20" max="20" width="9" style="1" customWidth="1"/>
-    <col min="21" max="21" width="13.75" style="1" customWidth="1"/>
+    <col min="16" max="19" width="8.83333333333333" style="1" customWidth="1"/>
+    <col min="20" max="20" width="13" style="1" customWidth="1"/>
+    <col min="21" max="21" width="9.08333333333333" style="1" customWidth="1"/>
     <col min="22" max="22" width="10.625" style="1" customWidth="1"/>
-    <col min="23" max="23" width="9.75" style="1" customWidth="1"/>
-    <col min="24" max="29" width="9" style="1"/>
-    <col min="30" max="30" width="19.25" style="1" customWidth="1"/>
-    <col min="31" max="16384" width="9" style="1"/>
+    <col min="23" max="23" width="12.625" style="1" customWidth="1"/>
+    <col min="24" max="24" width="9" style="1" customWidth="1"/>
+    <col min="26" max="26" width="9.75" style="1" customWidth="1"/>
+    <col min="27" max="32" width="9" style="1"/>
+    <col min="33" max="33" width="19.25" style="1" customWidth="1"/>
+    <col min="34" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:23">
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:31">
       <c r="C3" s="4" t="s">
         <v>0</v>
       </c>
@@ -1391,134 +1499,202 @@
       <c r="W3" s="4" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:23">
+      <c r="X3" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="Y3" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="Z3" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="AA3" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="AB3" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="AC3" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="AD3" s="4"/>
+      <c r="AE3" s="4"/>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:31">
       <c r="C4" s="4" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>1</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="F4" s="4"/>
       <c r="G4" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="L4" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="M4" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="N4" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="O4" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="P4" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q4" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="R4" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="S4" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="T4" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="U4" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="V4" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="W4" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="X4" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="Y4" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="Z4" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="H4" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="I4" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="J4" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="K4" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="L4" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="M4" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="N4" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="O4" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="P4" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q4" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="R4" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="S4" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="T4" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="U4" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="V4" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="W4" s="4" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:23">
+      <c r="AA4" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB4" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="AC4" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="AD4" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="AE4" s="4" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:31">
       <c r="C5" s="4" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="F5" s="4"/>
       <c r="G5" s="4" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="L5" s="4" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="M5" s="4" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="N5" s="4" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="O5" s="4" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="P5" s="4" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="R5" s="4" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="S5" s="4" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="U5" s="4" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="V5" s="4" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="W5" s="4" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:23">
+        <v>51</v>
+      </c>
+      <c r="X5" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="Y5" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="Z5" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="AA5" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="AB5" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="AC5" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="AD5" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="AE5" s="4" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:31">
       <c r="C6" s="1">
         <v>10011</v>
       </c>
@@ -1529,13 +1705,13 @@
         <v>1001</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>41</v>
+        <v>54</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="I6" s="1">
         <v>0</v>
@@ -1561,15 +1737,6 @@
       <c r="P6" s="1">
         <v>5</v>
       </c>
-      <c r="Q6" s="1">
-        <v>0</v>
-      </c>
-      <c r="R6" s="1">
-        <v>0</v>
-      </c>
-      <c r="S6" s="1">
-        <v>0</v>
-      </c>
       <c r="T6" s="1">
         <v>0</v>
       </c>
@@ -1582,8 +1749,11 @@
       <c r="W6" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:23">
+      <c r="X6" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:31">
       <c r="C7" s="1">
         <v>10021</v>
       </c>
@@ -1594,13 +1764,13 @@
         <v>1002</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="I7" s="1">
         <v>0</v>
@@ -1626,15 +1796,9 @@
       <c r="P7" s="2">
         <v>20</v>
       </c>
-      <c r="Q7" s="1">
-        <v>0</v>
-      </c>
-      <c r="R7" s="1">
-        <v>0</v>
-      </c>
-      <c r="S7" s="1">
-        <v>0</v>
-      </c>
+      <c r="Q7" s="2"/>
+      <c r="R7" s="2"/>
+      <c r="S7" s="2"/>
       <c r="T7" s="1">
         <v>0</v>
       </c>
@@ -1647,8 +1811,11 @@
       <c r="W7" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:23">
+      <c r="X7" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:31">
       <c r="C8" s="1">
         <v>10031</v>
       </c>
@@ -1659,13 +1826,13 @@
         <v>1003</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="I8" s="1">
         <v>0</v>
@@ -1691,15 +1858,9 @@
       <c r="P8" s="2">
         <v>20</v>
       </c>
-      <c r="Q8" s="1">
-        <v>0</v>
-      </c>
-      <c r="R8" s="1">
-        <v>0</v>
-      </c>
-      <c r="S8" s="1">
-        <v>0</v>
-      </c>
+      <c r="Q8" s="2"/>
+      <c r="R8" s="2"/>
+      <c r="S8" s="2"/>
       <c r="T8" s="1">
         <v>0</v>
       </c>
@@ -1712,8 +1873,11 @@
       <c r="W8" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:23">
+      <c r="X8" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:31">
       <c r="C9" s="1">
         <v>10041</v>
       </c>
@@ -1724,13 +1888,13 @@
         <v>1004</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="I9" s="1">
         <v>0</v>
@@ -1756,15 +1920,9 @@
       <c r="P9" s="2">
         <v>20</v>
       </c>
-      <c r="Q9" s="1">
-        <v>0</v>
-      </c>
-      <c r="R9" s="1">
-        <v>0</v>
-      </c>
-      <c r="S9" s="1">
-        <v>0</v>
-      </c>
+      <c r="Q9" s="2"/>
+      <c r="R9" s="2"/>
+      <c r="S9" s="2"/>
       <c r="T9" s="1">
         <v>0</v>
       </c>
@@ -1777,8 +1935,11 @@
       <c r="W9" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:23">
+      <c r="X9" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:31">
       <c r="C10" s="1">
         <v>10051</v>
       </c>
@@ -1789,13 +1950,13 @@
         <v>1005</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="I10" s="1">
         <v>0</v>
@@ -1821,15 +1982,9 @@
       <c r="P10" s="2">
         <v>5</v>
       </c>
-      <c r="Q10" s="1">
-        <v>0</v>
-      </c>
-      <c r="R10" s="1">
-        <v>0</v>
-      </c>
-      <c r="S10" s="1">
-        <v>0</v>
-      </c>
+      <c r="Q10" s="2"/>
+      <c r="R10" s="2"/>
+      <c r="S10" s="2"/>
       <c r="T10" s="1">
         <v>0</v>
       </c>
@@ -1842,8 +1997,11 @@
       <c r="W10" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:23">
+      <c r="X10" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:31">
       <c r="C11" s="1">
         <v>10061</v>
       </c>
@@ -1854,13 +2012,13 @@
         <v>1006</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>49</v>
+        <v>62</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="I11" s="1">
         <v>0</v>
@@ -1886,15 +2044,9 @@
       <c r="P11" s="2">
         <v>5</v>
       </c>
-      <c r="Q11" s="1">
-        <v>0</v>
-      </c>
-      <c r="R11" s="1">
-        <v>0</v>
-      </c>
-      <c r="S11" s="1">
-        <v>0</v>
-      </c>
+      <c r="Q11" s="2"/>
+      <c r="R11" s="2"/>
+      <c r="S11" s="2"/>
       <c r="T11" s="1">
         <v>0</v>
       </c>
@@ -1907,8 +2059,11 @@
       <c r="W11" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:23">
+      <c r="X11" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:31">
       <c r="C12" s="1">
         <v>10071</v>
       </c>
@@ -1919,13 +2074,13 @@
         <v>1007</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="I12" s="1">
         <v>0</v>
@@ -1951,15 +2106,9 @@
       <c r="P12" s="2">
         <v>20</v>
       </c>
-      <c r="Q12" s="1">
-        <v>0</v>
-      </c>
-      <c r="R12" s="1">
-        <v>0</v>
-      </c>
-      <c r="S12" s="1">
-        <v>0</v>
-      </c>
+      <c r="Q12" s="2"/>
+      <c r="R12" s="2"/>
+      <c r="S12" s="2"/>
       <c r="T12" s="1">
         <v>0</v>
       </c>
@@ -1972,8 +2121,11 @@
       <c r="W12" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:23">
+      <c r="X12" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:31">
       <c r="F13" s="2"/>
       <c r="G13" s="1"/>
       <c r="H13" s="1"/>
@@ -1981,9 +2133,9 @@
       <c r="J13" s="1"/>
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
-      <c r="S13" s="2"/>
-    </row>
-    <row r="14" s="1" customFormat="1" customHeight="1" spans="3:23">
+      <c r="W13" s="2"/>
+    </row>
+    <row r="14" s="1" customFormat="1" customHeight="1" spans="3:31">
       <c r="C14" s="1">
         <v>10022</v>
       </c>
@@ -1994,13 +2146,13 @@
         <v>1002</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="I14" s="1">
         <v>0</v>
@@ -2026,29 +2178,23 @@
       <c r="P14" s="1">
         <v>0</v>
       </c>
-      <c r="Q14" s="1">
-        <v>0</v>
-      </c>
-      <c r="R14" s="1">
-        <v>0</v>
-      </c>
-      <c r="S14" s="2">
+      <c r="T14" s="1">
+        <v>0</v>
+      </c>
+      <c r="U14" s="1">
+        <v>0</v>
+      </c>
+      <c r="V14" s="1">
+        <v>0</v>
+      </c>
+      <c r="W14" s="2">
         <v>20</v>
       </c>
-      <c r="T14" s="1">
-        <v>0</v>
-      </c>
-      <c r="U14" s="1">
-        <v>0</v>
-      </c>
-      <c r="V14" s="1">
-        <v>0</v>
-      </c>
-      <c r="W14" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" s="1" customFormat="1" customHeight="1" spans="3:23">
+      <c r="X14" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" s="1" customFormat="1" customHeight="1" spans="3:31">
       <c r="C15" s="1">
         <v>10032</v>
       </c>
@@ -2059,13 +2205,13 @@
         <v>1003</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="I15" s="1">
         <v>0</v>
@@ -2091,29 +2237,23 @@
       <c r="P15" s="1">
         <v>0</v>
       </c>
-      <c r="Q15" s="1">
-        <v>0</v>
-      </c>
-      <c r="R15" s="1">
-        <v>0</v>
-      </c>
-      <c r="S15" s="2">
+      <c r="T15" s="1">
+        <v>0</v>
+      </c>
+      <c r="U15" s="1">
+        <v>0</v>
+      </c>
+      <c r="V15" s="1">
+        <v>0</v>
+      </c>
+      <c r="W15" s="2">
         <v>20</v>
       </c>
-      <c r="T15" s="1">
-        <v>0</v>
-      </c>
-      <c r="U15" s="1">
-        <v>0</v>
-      </c>
-      <c r="V15" s="1">
-        <v>0</v>
-      </c>
-      <c r="W15" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" s="1" customFormat="1" customHeight="1" spans="3:23">
+      <c r="X15" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" s="1" customFormat="1" customHeight="1" spans="3:31">
       <c r="C16" s="1">
         <v>10042</v>
       </c>
@@ -2124,13 +2264,13 @@
         <v>1004</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="I16" s="1">
         <v>0</v>
@@ -2156,29 +2296,23 @@
       <c r="P16" s="1">
         <v>0</v>
       </c>
-      <c r="Q16" s="1">
-        <v>0</v>
-      </c>
-      <c r="R16" s="1">
-        <v>0</v>
-      </c>
-      <c r="S16" s="2">
+      <c r="T16" s="1">
+        <v>0</v>
+      </c>
+      <c r="U16" s="1">
+        <v>0</v>
+      </c>
+      <c r="V16" s="1">
+        <v>0</v>
+      </c>
+      <c r="W16" s="2">
         <v>20</v>
       </c>
-      <c r="T16" s="1">
-        <v>0</v>
-      </c>
-      <c r="U16" s="1">
-        <v>0</v>
-      </c>
-      <c r="V16" s="1">
-        <v>0</v>
-      </c>
-      <c r="W16" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" s="1" customFormat="1" customHeight="1" spans="3:23">
+      <c r="X16" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" s="1" customFormat="1" customHeight="1" spans="3:26">
       <c r="C17" s="1">
         <v>10072</v>
       </c>
@@ -2189,13 +2323,13 @@
         <v>1007</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="I17" s="1">
         <v>0</v>
@@ -2221,34 +2355,31 @@
       <c r="P17" s="1">
         <v>0</v>
       </c>
-      <c r="Q17" s="1">
-        <v>0</v>
-      </c>
-      <c r="R17" s="1">
-        <v>0</v>
-      </c>
-      <c r="S17" s="2">
+      <c r="T17" s="1">
+        <v>0</v>
+      </c>
+      <c r="U17" s="1">
+        <v>0</v>
+      </c>
+      <c r="V17" s="1">
+        <v>0</v>
+      </c>
+      <c r="W17" s="2">
         <v>20</v>
       </c>
-      <c r="T17" s="1">
-        <v>0</v>
-      </c>
-      <c r="U17" s="1">
-        <v>0</v>
-      </c>
-      <c r="V17" s="1">
-        <v>0</v>
-      </c>
-      <c r="W17" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" s="1" customFormat="1" customHeight="1" spans="3:23">
+      <c r="X17" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" s="1" customFormat="1" customHeight="1" spans="3:26">
       <c r="E18" s="2"/>
       <c r="F18" s="2"/>
       <c r="P18" s="2"/>
-    </row>
-    <row r="19" s="2" customFormat="1" customHeight="1" spans="3:23">
+      <c r="Q18" s="2"/>
+      <c r="R18" s="2"/>
+      <c r="S18" s="2"/>
+    </row>
+    <row r="19" s="2" customFormat="1" customHeight="1" spans="3:26">
       <c r="C19" s="1">
         <v>10023</v>
       </c>
@@ -2259,13 +2390,13 @@
         <v>1002</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="I19" s="1">
         <v>0</v>
@@ -2291,29 +2422,27 @@
       <c r="P19" s="1">
         <v>0</v>
       </c>
-      <c r="Q19" s="1">
-        <v>0</v>
-      </c>
-      <c r="R19" s="1">
-        <v>0</v>
-      </c>
-      <c r="S19" s="1">
-        <v>0</v>
-      </c>
-      <c r="T19" s="2">
+      <c r="Q19" s="1"/>
+      <c r="R19" s="1"/>
+      <c r="S19" s="1"/>
+      <c r="T19" s="1">
+        <v>0</v>
+      </c>
+      <c r="U19" s="1">
+        <v>0</v>
+      </c>
+      <c r="V19" s="1">
+        <v>0</v>
+      </c>
+      <c r="W19" s="1">
+        <v>0</v>
+      </c>
+      <c r="X19" s="2">
         <v>20</v>
       </c>
-      <c r="U19" s="1">
-        <v>0</v>
-      </c>
-      <c r="V19" s="1">
-        <v>0</v>
-      </c>
-      <c r="W19" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" s="2" customFormat="1" customHeight="1" spans="3:23">
+      <c r="Z19" s="1"/>
+    </row>
+    <row r="20" s="2" customFormat="1" customHeight="1" spans="3:26">
       <c r="C20" s="1">
         <v>10033</v>
       </c>
@@ -2324,13 +2453,13 @@
         <v>1003</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="I20" s="1">
         <v>0</v>
@@ -2356,29 +2485,27 @@
       <c r="P20" s="1">
         <v>0</v>
       </c>
-      <c r="Q20" s="1">
-        <v>0</v>
-      </c>
-      <c r="R20" s="1">
-        <v>0</v>
-      </c>
-      <c r="S20" s="1">
-        <v>0</v>
-      </c>
-      <c r="T20" s="2">
+      <c r="Q20" s="1"/>
+      <c r="R20" s="1"/>
+      <c r="S20" s="1"/>
+      <c r="T20" s="1">
+        <v>0</v>
+      </c>
+      <c r="U20" s="1">
+        <v>0</v>
+      </c>
+      <c r="V20" s="1">
+        <v>0</v>
+      </c>
+      <c r="W20" s="1">
+        <v>0</v>
+      </c>
+      <c r="X20" s="2">
         <v>20</v>
       </c>
-      <c r="U20" s="1">
-        <v>0</v>
-      </c>
-      <c r="V20" s="1">
-        <v>0</v>
-      </c>
-      <c r="W20" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" s="2" customFormat="1" customHeight="1" spans="3:23">
+      <c r="Z20" s="1"/>
+    </row>
+    <row r="21" s="2" customFormat="1" customHeight="1" spans="3:26">
       <c r="C21" s="1">
         <v>10043</v>
       </c>
@@ -2389,13 +2516,13 @@
         <v>1004</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="I21" s="1">
         <v>0</v>
@@ -2421,29 +2548,27 @@
       <c r="P21" s="1">
         <v>0</v>
       </c>
-      <c r="Q21" s="1">
-        <v>0</v>
-      </c>
-      <c r="R21" s="1">
-        <v>0</v>
-      </c>
-      <c r="S21" s="1">
-        <v>0</v>
-      </c>
-      <c r="T21" s="2">
+      <c r="Q21" s="1"/>
+      <c r="R21" s="1"/>
+      <c r="S21" s="1"/>
+      <c r="T21" s="1">
+        <v>0</v>
+      </c>
+      <c r="U21" s="1">
+        <v>0</v>
+      </c>
+      <c r="V21" s="1">
+        <v>0</v>
+      </c>
+      <c r="W21" s="1">
+        <v>0</v>
+      </c>
+      <c r="X21" s="2">
         <v>20</v>
       </c>
-      <c r="U21" s="1">
-        <v>0</v>
-      </c>
-      <c r="V21" s="1">
-        <v>0</v>
-      </c>
-      <c r="W21" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" s="2" customFormat="1" customHeight="1" spans="3:23">
+      <c r="Z21" s="1"/>
+    </row>
+    <row r="22" s="2" customFormat="1" customHeight="1" spans="3:26">
       <c r="C22" s="1">
         <v>10073</v>
       </c>
@@ -2454,13 +2579,13 @@
         <v>1007</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="I22" s="1">
         <v>0</v>
@@ -2486,29 +2611,27 @@
       <c r="P22" s="1">
         <v>0</v>
       </c>
-      <c r="Q22" s="1">
-        <v>0</v>
-      </c>
-      <c r="R22" s="1">
-        <v>0</v>
-      </c>
-      <c r="S22" s="1">
-        <v>0</v>
-      </c>
-      <c r="T22" s="2">
+      <c r="Q22" s="1"/>
+      <c r="R22" s="1"/>
+      <c r="S22" s="1"/>
+      <c r="T22" s="1">
+        <v>0</v>
+      </c>
+      <c r="U22" s="1">
+        <v>0</v>
+      </c>
+      <c r="V22" s="1">
+        <v>0</v>
+      </c>
+      <c r="W22" s="1">
+        <v>0</v>
+      </c>
+      <c r="X22" s="2">
         <v>20</v>
       </c>
-      <c r="U22" s="1">
-        <v>0</v>
-      </c>
-      <c r="V22" s="1">
-        <v>0</v>
-      </c>
-      <c r="W22" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" s="2" customFormat="1" customHeight="1" spans="3:23">
+      <c r="Z22" s="1"/>
+    </row>
+    <row r="23" s="2" customFormat="1" customHeight="1" spans="3:26">
       <c r="C23" s="1"/>
       <c r="D23" s="1"/>
       <c r="E23" s="2"/>
@@ -2530,8 +2653,10 @@
       <c r="U23" s="1"/>
       <c r="V23" s="1"/>
       <c r="W23" s="1"/>
-    </row>
-    <row r="24" s="2" customFormat="1" customHeight="1" spans="3:23">
+      <c r="X23" s="1"/>
+      <c r="Z23" s="1"/>
+    </row>
+    <row r="24" s="2" customFormat="1" customHeight="1" spans="3:26">
       <c r="C24" s="1">
         <v>10024</v>
       </c>
@@ -2542,13 +2667,13 @@
         <v>1002</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="I24" s="1">
         <v>0</v>
@@ -2574,29 +2699,27 @@
       <c r="P24" s="1">
         <v>0</v>
       </c>
-      <c r="Q24" s="1">
-        <v>0</v>
-      </c>
-      <c r="R24" s="1">
+      <c r="Q24" s="1"/>
+      <c r="R24" s="1"/>
+      <c r="S24" s="1"/>
+      <c r="T24" s="1">
+        <v>0</v>
+      </c>
+      <c r="U24" s="1">
         <v>100</v>
       </c>
-      <c r="S24" s="1">
-        <v>0</v>
-      </c>
-      <c r="T24" s="1">
-        <v>0</v>
-      </c>
-      <c r="U24" s="1">
-        <v>0</v>
-      </c>
       <c r="V24" s="1">
         <v>0</v>
       </c>
       <c r="W24" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" s="2" customFormat="1" customHeight="1" spans="3:23">
+      <c r="X24" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z24" s="1"/>
+    </row>
+    <row r="25" s="2" customFormat="1" customHeight="1" spans="3:26">
       <c r="C25" s="1">
         <v>10034</v>
       </c>
@@ -2607,13 +2730,13 @@
         <v>1003</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="I25" s="1">
         <v>0</v>
@@ -2639,29 +2762,27 @@
       <c r="P25" s="1">
         <v>0</v>
       </c>
-      <c r="Q25" s="1">
-        <v>0</v>
-      </c>
-      <c r="R25" s="1">
+      <c r="Q25" s="1"/>
+      <c r="R25" s="1"/>
+      <c r="S25" s="1"/>
+      <c r="T25" s="1">
+        <v>0</v>
+      </c>
+      <c r="U25" s="1">
         <v>100</v>
       </c>
-      <c r="S25" s="1">
-        <v>0</v>
-      </c>
-      <c r="T25" s="1">
-        <v>0</v>
-      </c>
-      <c r="U25" s="1">
-        <v>0</v>
-      </c>
       <c r="V25" s="1">
         <v>0</v>
       </c>
       <c r="W25" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" s="2" customFormat="1" customHeight="1" spans="3:23">
+      <c r="X25" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z25" s="1"/>
+    </row>
+    <row r="26" s="2" customFormat="1" customHeight="1" spans="3:26">
       <c r="C26" s="1">
         <v>10044</v>
       </c>
@@ -2672,13 +2793,13 @@
         <v>1004</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="I26" s="1">
         <v>0</v>
@@ -2704,29 +2825,27 @@
       <c r="P26" s="1">
         <v>0</v>
       </c>
-      <c r="Q26" s="1">
-        <v>0</v>
-      </c>
-      <c r="R26" s="1">
+      <c r="Q26" s="1"/>
+      <c r="R26" s="1"/>
+      <c r="S26" s="1"/>
+      <c r="T26" s="1">
+        <v>0</v>
+      </c>
+      <c r="U26" s="1">
         <v>100</v>
       </c>
-      <c r="S26" s="1">
-        <v>0</v>
-      </c>
-      <c r="T26" s="1">
-        <v>0</v>
-      </c>
-      <c r="U26" s="1">
-        <v>0</v>
-      </c>
       <c r="V26" s="1">
         <v>0</v>
       </c>
       <c r="W26" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" s="1" customFormat="1" customHeight="1" spans="3:23">
+      <c r="X26" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z26" s="1"/>
+    </row>
+    <row r="27" s="1" customFormat="1" customHeight="1" spans="3:26">
       <c r="C27" s="1">
         <v>10074</v>
       </c>
@@ -2737,13 +2856,13 @@
         <v>1007</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="I27" s="1">
         <v>0</v>
@@ -2769,30 +2888,24 @@
       <c r="P27" s="1">
         <v>0</v>
       </c>
-      <c r="Q27" s="1">
-        <v>0</v>
-      </c>
-      <c r="R27" s="1">
+      <c r="T27" s="1">
+        <v>0</v>
+      </c>
+      <c r="U27" s="1">
         <v>100</v>
       </c>
-      <c r="S27" s="1">
-        <v>0</v>
-      </c>
-      <c r="T27" s="1">
-        <v>0</v>
-      </c>
-      <c r="U27" s="1">
-        <v>0</v>
-      </c>
       <c r="V27" s="1">
         <v>0</v>
       </c>
       <c r="W27" s="1">
         <v>0</v>
       </c>
+      <c r="X27" s="1">
+        <v>0</v>
+      </c>
     </row>
     <row r="29" s="3" customFormat="1" customHeight="1"/>
-    <row r="31" s="1" customFormat="1" customHeight="1" spans="3:23">
+    <row r="31" s="1" customFormat="1" customHeight="1" spans="3:26">
       <c r="C31" s="1">
         <v>20011</v>
       </c>
@@ -2803,13 +2916,13 @@
         <v>2001</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="I31" s="1">
         <v>0</v>
@@ -2835,15 +2948,6 @@
       <c r="P31" s="1">
         <v>5</v>
       </c>
-      <c r="Q31" s="1">
-        <v>0</v>
-      </c>
-      <c r="R31" s="1">
-        <v>0</v>
-      </c>
-      <c r="S31" s="1">
-        <v>0</v>
-      </c>
       <c r="T31" s="1">
         <v>0</v>
       </c>
@@ -2856,8 +2960,11 @@
       <c r="W31" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" s="1" customFormat="1" customHeight="1" spans="3:23">
+      <c r="X31" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" s="1" customFormat="1" customHeight="1" spans="3:26">
       <c r="C32" s="1">
         <v>20021</v>
       </c>
@@ -2868,13 +2975,13 @@
         <v>2002</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="I32" s="1">
         <v>0</v>
@@ -2900,15 +3007,9 @@
       <c r="P32" s="2">
         <v>20</v>
       </c>
-      <c r="Q32" s="1">
-        <v>0</v>
-      </c>
-      <c r="R32" s="1">
-        <v>0</v>
-      </c>
-      <c r="S32" s="1">
-        <v>0</v>
-      </c>
+      <c r="Q32" s="2"/>
+      <c r="R32" s="2"/>
+      <c r="S32" s="2"/>
       <c r="T32" s="1">
         <v>0</v>
       </c>
@@ -2921,8 +3022,11 @@
       <c r="W32" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" s="1" customFormat="1" customHeight="1" spans="3:23">
+      <c r="X32" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" s="1" customFormat="1" customHeight="1" spans="3:26">
       <c r="C33" s="1">
         <v>20031</v>
       </c>
@@ -2933,13 +3037,13 @@
         <v>2003</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="I33" s="1">
         <v>0</v>
@@ -2965,15 +3069,9 @@
       <c r="P33" s="2">
         <v>20</v>
       </c>
-      <c r="Q33" s="1">
-        <v>0</v>
-      </c>
-      <c r="R33" s="1">
-        <v>0</v>
-      </c>
-      <c r="S33" s="1">
-        <v>0</v>
-      </c>
+      <c r="Q33" s="2"/>
+      <c r="R33" s="2"/>
+      <c r="S33" s="2"/>
       <c r="T33" s="1">
         <v>0</v>
       </c>
@@ -2986,8 +3084,11 @@
       <c r="W33" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" s="1" customFormat="1" customHeight="1" spans="3:23">
+      <c r="X33" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" s="1" customFormat="1" customHeight="1" spans="3:26">
       <c r="C34" s="1">
         <v>20041</v>
       </c>
@@ -2998,13 +3099,13 @@
         <v>2004</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="I34" s="1">
         <v>0</v>
@@ -3030,15 +3131,9 @@
       <c r="P34" s="2">
         <v>20</v>
       </c>
-      <c r="Q34" s="1">
-        <v>0</v>
-      </c>
-      <c r="R34" s="1">
-        <v>0</v>
-      </c>
-      <c r="S34" s="1">
-        <v>0</v>
-      </c>
+      <c r="Q34" s="2"/>
+      <c r="R34" s="2"/>
+      <c r="S34" s="2"/>
       <c r="T34" s="1">
         <v>0</v>
       </c>
@@ -3051,8 +3146,11 @@
       <c r="W34" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" s="1" customFormat="1" customHeight="1" spans="3:23">
+      <c r="X34" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" s="1" customFormat="1" customHeight="1" spans="3:26">
       <c r="C35" s="1">
         <v>20051</v>
       </c>
@@ -3063,13 +3161,13 @@
         <v>2005</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="I35" s="1">
         <v>0</v>
@@ -3095,15 +3193,9 @@
       <c r="P35" s="2">
         <v>5</v>
       </c>
-      <c r="Q35" s="1">
-        <v>0</v>
-      </c>
-      <c r="R35" s="1">
-        <v>0</v>
-      </c>
-      <c r="S35" s="1">
-        <v>0</v>
-      </c>
+      <c r="Q35" s="2"/>
+      <c r="R35" s="2"/>
+      <c r="S35" s="2"/>
       <c r="T35" s="1">
         <v>0</v>
       </c>
@@ -3116,8 +3208,11 @@
       <c r="W35" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="36" s="1" customFormat="1" customHeight="1" spans="3:23">
+      <c r="X35" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" s="1" customFormat="1" customHeight="1" spans="3:26">
       <c r="C36" s="1">
         <v>20061</v>
       </c>
@@ -3128,13 +3223,13 @@
         <v>2006</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="I36" s="1">
         <v>0</v>
@@ -3160,15 +3255,9 @@
       <c r="P36" s="2">
         <v>5</v>
       </c>
-      <c r="Q36" s="1">
-        <v>0</v>
-      </c>
-      <c r="R36" s="1">
-        <v>0</v>
-      </c>
-      <c r="S36" s="1">
-        <v>0</v>
-      </c>
+      <c r="Q36" s="2"/>
+      <c r="R36" s="2"/>
+      <c r="S36" s="2"/>
       <c r="T36" s="1">
         <v>0</v>
       </c>
@@ -3181,8 +3270,11 @@
       <c r="W36" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" s="1" customFormat="1" customHeight="1" spans="3:23">
+      <c r="X36" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" s="1" customFormat="1" customHeight="1" spans="3:26">
       <c r="C37" s="1">
         <v>20071</v>
       </c>
@@ -3193,13 +3285,13 @@
         <v>2007</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="I37" s="1">
         <v>0</v>
@@ -3225,15 +3317,9 @@
       <c r="P37" s="2">
         <v>20</v>
       </c>
-      <c r="Q37" s="1">
-        <v>0</v>
-      </c>
-      <c r="R37" s="1">
-        <v>0</v>
-      </c>
-      <c r="S37" s="1">
-        <v>0</v>
-      </c>
+      <c r="Q37" s="2"/>
+      <c r="R37" s="2"/>
+      <c r="S37" s="2"/>
       <c r="T37" s="1">
         <v>0</v>
       </c>
@@ -3246,12 +3332,15 @@
       <c r="W37" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="38" s="1" customFormat="1" customHeight="1" spans="3:23">
+      <c r="X37" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" s="1" customFormat="1" customHeight="1" spans="3:26">
       <c r="F38" s="2"/>
-      <c r="S38" s="2"/>
-    </row>
-    <row r="39" s="1" customFormat="1" customHeight="1" spans="3:23">
+      <c r="W38" s="2"/>
+    </row>
+    <row r="39" s="1" customFormat="1" customHeight="1" spans="3:26">
       <c r="C39" s="1">
         <v>20022</v>
       </c>
@@ -3262,13 +3351,13 @@
         <v>2002</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="I39" s="1">
         <v>0</v>
@@ -3294,29 +3383,23 @@
       <c r="P39" s="1">
         <v>0</v>
       </c>
-      <c r="Q39" s="1">
-        <v>0</v>
-      </c>
-      <c r="R39" s="1">
-        <v>0</v>
-      </c>
-      <c r="S39" s="2">
+      <c r="T39" s="1">
+        <v>0</v>
+      </c>
+      <c r="U39" s="1">
+        <v>0</v>
+      </c>
+      <c r="V39" s="1">
+        <v>0</v>
+      </c>
+      <c r="W39" s="2">
         <v>20</v>
       </c>
-      <c r="T39" s="1">
-        <v>0</v>
-      </c>
-      <c r="U39" s="1">
-        <v>0</v>
-      </c>
-      <c r="V39" s="1">
-        <v>0</v>
-      </c>
-      <c r="W39" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" s="1" customFormat="1" customHeight="1" spans="3:23">
+      <c r="X39" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" s="1" customFormat="1" customHeight="1" spans="3:26">
       <c r="C40" s="1">
         <v>20032</v>
       </c>
@@ -3327,13 +3410,13 @@
         <v>2003</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="I40" s="1">
         <v>0</v>
@@ -3359,29 +3442,23 @@
       <c r="P40" s="1">
         <v>0</v>
       </c>
-      <c r="Q40" s="1">
-        <v>0</v>
-      </c>
-      <c r="R40" s="1">
-        <v>0</v>
-      </c>
-      <c r="S40" s="2">
+      <c r="T40" s="1">
+        <v>0</v>
+      </c>
+      <c r="U40" s="1">
+        <v>0</v>
+      </c>
+      <c r="V40" s="1">
+        <v>0</v>
+      </c>
+      <c r="W40" s="2">
         <v>20</v>
       </c>
-      <c r="T40" s="1">
-        <v>0</v>
-      </c>
-      <c r="U40" s="1">
-        <v>0</v>
-      </c>
-      <c r="V40" s="1">
-        <v>0</v>
-      </c>
-      <c r="W40" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" s="1" customFormat="1" customHeight="1" spans="3:23">
+      <c r="X40" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" s="1" customFormat="1" customHeight="1" spans="3:26">
       <c r="C41" s="1">
         <v>20042</v>
       </c>
@@ -3392,13 +3469,13 @@
         <v>2004</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="I41" s="1">
         <v>0</v>
@@ -3424,29 +3501,23 @@
       <c r="P41" s="1">
         <v>0</v>
       </c>
-      <c r="Q41" s="1">
-        <v>0</v>
-      </c>
-      <c r="R41" s="1">
-        <v>0</v>
-      </c>
-      <c r="S41" s="2">
+      <c r="T41" s="1">
+        <v>0</v>
+      </c>
+      <c r="U41" s="1">
+        <v>0</v>
+      </c>
+      <c r="V41" s="1">
+        <v>0</v>
+      </c>
+      <c r="W41" s="2">
         <v>20</v>
       </c>
-      <c r="T41" s="1">
-        <v>0</v>
-      </c>
-      <c r="U41" s="1">
-        <v>0</v>
-      </c>
-      <c r="V41" s="1">
-        <v>0</v>
-      </c>
-      <c r="W41" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" s="1" customFormat="1" customHeight="1" spans="3:23">
+      <c r="X41" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" s="1" customFormat="1" customHeight="1" spans="3:26">
       <c r="C42" s="1">
         <v>20072</v>
       </c>
@@ -3457,13 +3528,13 @@
         <v>2007</v>
       </c>
       <c r="F42" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G42" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="G42" s="1" t="s">
-        <v>51</v>
-      </c>
       <c r="H42" s="1" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="I42" s="1">
         <v>0</v>
@@ -3489,34 +3560,31 @@
       <c r="P42" s="1">
         <v>0</v>
       </c>
-      <c r="Q42" s="1">
-        <v>0</v>
-      </c>
-      <c r="R42" s="1">
-        <v>0</v>
-      </c>
-      <c r="S42" s="2">
+      <c r="T42" s="1">
+        <v>0</v>
+      </c>
+      <c r="U42" s="1">
+        <v>0</v>
+      </c>
+      <c r="V42" s="1">
+        <v>0</v>
+      </c>
+      <c r="W42" s="2">
         <v>20</v>
       </c>
-      <c r="T42" s="1">
-        <v>0</v>
-      </c>
-      <c r="U42" s="1">
-        <v>0</v>
-      </c>
-      <c r="V42" s="1">
-        <v>0</v>
-      </c>
-      <c r="W42" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" s="1" customFormat="1" customHeight="1" spans="3:23">
+      <c r="X42" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" s="1" customFormat="1" customHeight="1" spans="3:26">
       <c r="E43" s="2"/>
       <c r="F43" s="2"/>
       <c r="P43" s="2"/>
-    </row>
-    <row r="44" s="2" customFormat="1" customHeight="1" spans="3:23">
+      <c r="Q43" s="2"/>
+      <c r="R43" s="2"/>
+      <c r="S43" s="2"/>
+    </row>
+    <row r="44" s="2" customFormat="1" customHeight="1" spans="3:26">
       <c r="C44" s="1">
         <v>20023</v>
       </c>
@@ -3527,13 +3595,13 @@
         <v>2002</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="I44" s="1">
         <v>0</v>
@@ -3559,29 +3627,27 @@
       <c r="P44" s="1">
         <v>0</v>
       </c>
-      <c r="Q44" s="1">
-        <v>0</v>
-      </c>
-      <c r="R44" s="1">
-        <v>0</v>
-      </c>
-      <c r="S44" s="1">
-        <v>0</v>
-      </c>
-      <c r="T44" s="2">
+      <c r="Q44" s="1"/>
+      <c r="R44" s="1"/>
+      <c r="S44" s="1"/>
+      <c r="T44" s="1">
+        <v>0</v>
+      </c>
+      <c r="U44" s="1">
+        <v>0</v>
+      </c>
+      <c r="V44" s="1">
+        <v>0</v>
+      </c>
+      <c r="W44" s="1">
+        <v>0</v>
+      </c>
+      <c r="X44" s="2">
         <v>20</v>
       </c>
-      <c r="U44" s="1">
-        <v>0</v>
-      </c>
-      <c r="V44" s="1">
-        <v>0</v>
-      </c>
-      <c r="W44" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" s="2" customFormat="1" customHeight="1" spans="3:23">
+      <c r="Z44" s="1"/>
+    </row>
+    <row r="45" s="2" customFormat="1" customHeight="1" spans="3:26">
       <c r="C45" s="1">
         <v>20033</v>
       </c>
@@ -3592,13 +3658,13 @@
         <v>2003</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="I45" s="1">
         <v>0</v>
@@ -3624,29 +3690,27 @@
       <c r="P45" s="1">
         <v>0</v>
       </c>
-      <c r="Q45" s="1">
-        <v>0</v>
-      </c>
-      <c r="R45" s="1">
-        <v>0</v>
-      </c>
-      <c r="S45" s="1">
-        <v>0</v>
-      </c>
-      <c r="T45" s="2">
+      <c r="Q45" s="1"/>
+      <c r="R45" s="1"/>
+      <c r="S45" s="1"/>
+      <c r="T45" s="1">
+        <v>0</v>
+      </c>
+      <c r="U45" s="1">
+        <v>0</v>
+      </c>
+      <c r="V45" s="1">
+        <v>0</v>
+      </c>
+      <c r="W45" s="1">
+        <v>0</v>
+      </c>
+      <c r="X45" s="2">
         <v>20</v>
       </c>
-      <c r="U45" s="1">
-        <v>0</v>
-      </c>
-      <c r="V45" s="1">
-        <v>0</v>
-      </c>
-      <c r="W45" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" s="2" customFormat="1" customHeight="1" spans="3:23">
+      <c r="Z45" s="1"/>
+    </row>
+    <row r="46" s="2" customFormat="1" customHeight="1" spans="3:26">
       <c r="C46" s="1">
         <v>20043</v>
       </c>
@@ -3657,13 +3721,13 @@
         <v>2004</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="I46" s="1">
         <v>0</v>
@@ -3689,29 +3753,27 @@
       <c r="P46" s="1">
         <v>0</v>
       </c>
-      <c r="Q46" s="1">
-        <v>0</v>
-      </c>
-      <c r="R46" s="1">
-        <v>0</v>
-      </c>
-      <c r="S46" s="1">
-        <v>0</v>
-      </c>
-      <c r="T46" s="2">
+      <c r="Q46" s="1"/>
+      <c r="R46" s="1"/>
+      <c r="S46" s="1"/>
+      <c r="T46" s="1">
+        <v>0</v>
+      </c>
+      <c r="U46" s="1">
+        <v>0</v>
+      </c>
+      <c r="V46" s="1">
+        <v>0</v>
+      </c>
+      <c r="W46" s="1">
+        <v>0</v>
+      </c>
+      <c r="X46" s="2">
         <v>20</v>
       </c>
-      <c r="U46" s="1">
-        <v>0</v>
-      </c>
-      <c r="V46" s="1">
-        <v>0</v>
-      </c>
-      <c r="W46" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" s="2" customFormat="1" customHeight="1" spans="3:23">
+      <c r="Z46" s="1"/>
+    </row>
+    <row r="47" s="2" customFormat="1" customHeight="1" spans="3:26">
       <c r="C47" s="1">
         <v>20073</v>
       </c>
@@ -3722,13 +3784,13 @@
         <v>2007</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="I47" s="1">
         <v>0</v>
@@ -3754,29 +3816,27 @@
       <c r="P47" s="1">
         <v>0</v>
       </c>
-      <c r="Q47" s="1">
-        <v>0</v>
-      </c>
-      <c r="R47" s="1">
-        <v>0</v>
-      </c>
-      <c r="S47" s="1">
-        <v>0</v>
-      </c>
-      <c r="T47" s="2">
+      <c r="Q47" s="1"/>
+      <c r="R47" s="1"/>
+      <c r="S47" s="1"/>
+      <c r="T47" s="1">
+        <v>0</v>
+      </c>
+      <c r="U47" s="1">
+        <v>0</v>
+      </c>
+      <c r="V47" s="1">
+        <v>0</v>
+      </c>
+      <c r="W47" s="1">
+        <v>0</v>
+      </c>
+      <c r="X47" s="2">
         <v>20</v>
       </c>
-      <c r="U47" s="1">
-        <v>0</v>
-      </c>
-      <c r="V47" s="1">
-        <v>0</v>
-      </c>
-      <c r="W47" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" s="2" customFormat="1" customHeight="1" spans="3:23">
+      <c r="Z47" s="1"/>
+    </row>
+    <row r="48" s="2" customFormat="1" customHeight="1" spans="3:26">
       <c r="C48" s="1"/>
       <c r="D48" s="1"/>
       <c r="G48" s="1"/>
@@ -3796,8 +3856,10 @@
       <c r="U48" s="1"/>
       <c r="V48" s="1"/>
       <c r="W48" s="1"/>
-    </row>
-    <row r="49" s="2" customFormat="1" customHeight="1" spans="3:23">
+      <c r="X48" s="1"/>
+      <c r="Z48" s="1"/>
+    </row>
+    <row r="49" s="2" customFormat="1" customHeight="1" spans="3:26">
       <c r="C49" s="1">
         <v>20024</v>
       </c>
@@ -3808,13 +3870,13 @@
         <v>2002</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="I49" s="1">
         <v>0</v>
@@ -3840,29 +3902,27 @@
       <c r="P49" s="1">
         <v>0</v>
       </c>
-      <c r="Q49" s="1">
-        <v>0</v>
-      </c>
-      <c r="R49" s="1">
+      <c r="Q49" s="1"/>
+      <c r="R49" s="1"/>
+      <c r="S49" s="1"/>
+      <c r="T49" s="1">
+        <v>0</v>
+      </c>
+      <c r="U49" s="1">
         <v>100</v>
       </c>
-      <c r="S49" s="1">
-        <v>0</v>
-      </c>
-      <c r="T49" s="1">
-        <v>0</v>
-      </c>
-      <c r="U49" s="1">
-        <v>0</v>
-      </c>
       <c r="V49" s="1">
         <v>0</v>
       </c>
       <c r="W49" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="50" s="2" customFormat="1" customHeight="1" spans="3:23">
+      <c r="X49" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z49" s="1"/>
+    </row>
+    <row r="50" s="2" customFormat="1" customHeight="1" spans="3:26">
       <c r="C50" s="1">
         <v>20034</v>
       </c>
@@ -3873,13 +3933,13 @@
         <v>2003</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="I50" s="1">
         <v>0</v>
@@ -3905,29 +3965,27 @@
       <c r="P50" s="1">
         <v>0</v>
       </c>
-      <c r="Q50" s="1">
-        <v>0</v>
-      </c>
-      <c r="R50" s="1">
+      <c r="Q50" s="1"/>
+      <c r="R50" s="1"/>
+      <c r="S50" s="1"/>
+      <c r="T50" s="1">
+        <v>0</v>
+      </c>
+      <c r="U50" s="1">
         <v>100</v>
       </c>
-      <c r="S50" s="1">
-        <v>0</v>
-      </c>
-      <c r="T50" s="1">
-        <v>0</v>
-      </c>
-      <c r="U50" s="1">
-        <v>0</v>
-      </c>
       <c r="V50" s="1">
         <v>0</v>
       </c>
       <c r="W50" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" s="2" customFormat="1" customHeight="1" spans="3:23">
+      <c r="X50" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z50" s="1"/>
+    </row>
+    <row r="51" s="2" customFormat="1" customHeight="1" spans="3:26">
       <c r="C51" s="1">
         <v>20044</v>
       </c>
@@ -3938,13 +3996,13 @@
         <v>2004</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="I51" s="1">
         <v>0</v>
@@ -3970,29 +4028,27 @@
       <c r="P51" s="1">
         <v>0</v>
       </c>
-      <c r="Q51" s="1">
-        <v>0</v>
-      </c>
-      <c r="R51" s="1">
+      <c r="Q51" s="1"/>
+      <c r="R51" s="1"/>
+      <c r="S51" s="1"/>
+      <c r="T51" s="1">
+        <v>0</v>
+      </c>
+      <c r="U51" s="1">
         <v>100</v>
       </c>
-      <c r="S51" s="1">
-        <v>0</v>
-      </c>
-      <c r="T51" s="1">
-        <v>0</v>
-      </c>
-      <c r="U51" s="1">
-        <v>0</v>
-      </c>
       <c r="V51" s="1">
         <v>0</v>
       </c>
       <c r="W51" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" s="1" customFormat="1" customHeight="1" spans="3:23">
+      <c r="X51" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z51" s="1"/>
+    </row>
+    <row r="52" s="1" customFormat="1" customHeight="1" spans="3:26">
       <c r="C52" s="1">
         <v>20074</v>
       </c>
@@ -4003,13 +4059,13 @@
         <v>2007</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="I52" s="1">
         <v>0</v>
@@ -4035,30 +4091,24 @@
       <c r="P52" s="1">
         <v>0</v>
       </c>
-      <c r="Q52" s="1">
-        <v>0</v>
-      </c>
-      <c r="R52" s="1">
+      <c r="T52" s="1">
+        <v>0</v>
+      </c>
+      <c r="U52" s="1">
         <v>100</v>
       </c>
-      <c r="S52" s="1">
-        <v>0</v>
-      </c>
-      <c r="T52" s="1">
-        <v>0</v>
-      </c>
-      <c r="U52" s="1">
-        <v>0</v>
-      </c>
       <c r="V52" s="1">
         <v>0</v>
       </c>
       <c r="W52" s="1">
         <v>0</v>
       </c>
+      <c r="X52" s="1">
+        <v>0</v>
+      </c>
     </row>
     <row r="54" s="3" customFormat="1" customHeight="1"/>
-    <row r="56" s="1" customFormat="1" customHeight="1" spans="3:23">
+    <row r="56" s="1" customFormat="1" customHeight="1" spans="3:26">
       <c r="C56" s="1">
         <v>30011</v>
       </c>
@@ -4069,13 +4119,13 @@
         <v>3001</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="I56" s="1">
         <v>0</v>
@@ -4101,15 +4151,6 @@
       <c r="P56" s="1">
         <v>5</v>
       </c>
-      <c r="Q56" s="1">
-        <v>0</v>
-      </c>
-      <c r="R56" s="1">
-        <v>0</v>
-      </c>
-      <c r="S56" s="1">
-        <v>0</v>
-      </c>
       <c r="T56" s="1">
         <v>0</v>
       </c>
@@ -4122,8 +4163,11 @@
       <c r="W56" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="57" s="1" customFormat="1" customHeight="1" spans="3:23">
+      <c r="X56" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" s="1" customFormat="1" customHeight="1" spans="3:26">
       <c r="C57" s="1">
         <v>30021</v>
       </c>
@@ -4134,13 +4178,13 @@
         <v>3002</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="I57" s="1">
         <v>0</v>
@@ -4166,15 +4210,9 @@
       <c r="P57" s="2">
         <v>20</v>
       </c>
-      <c r="Q57" s="1">
-        <v>0</v>
-      </c>
-      <c r="R57" s="1">
-        <v>0</v>
-      </c>
-      <c r="S57" s="1">
-        <v>0</v>
-      </c>
+      <c r="Q57" s="2"/>
+      <c r="R57" s="2"/>
+      <c r="S57" s="2"/>
       <c r="T57" s="1">
         <v>0</v>
       </c>
@@ -4187,8 +4225,11 @@
       <c r="W57" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" s="1" customFormat="1" customHeight="1" spans="3:23">
+      <c r="X57" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" s="1" customFormat="1" customHeight="1" spans="3:26">
       <c r="C58" s="1">
         <v>30031</v>
       </c>
@@ -4199,13 +4240,13 @@
         <v>3003</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="I58" s="1">
         <v>0</v>
@@ -4231,15 +4272,9 @@
       <c r="P58" s="2">
         <v>20</v>
       </c>
-      <c r="Q58" s="1">
-        <v>0</v>
-      </c>
-      <c r="R58" s="1">
-        <v>0</v>
-      </c>
-      <c r="S58" s="1">
-        <v>0</v>
-      </c>
+      <c r="Q58" s="2"/>
+      <c r="R58" s="2"/>
+      <c r="S58" s="2"/>
       <c r="T58" s="1">
         <v>0</v>
       </c>
@@ -4252,8 +4287,11 @@
       <c r="W58" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" s="1" customFormat="1" customHeight="1" spans="3:23">
+      <c r="X58" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" s="1" customFormat="1" customHeight="1" spans="3:26">
       <c r="C59" s="1">
         <v>30041</v>
       </c>
@@ -4264,13 +4302,13 @@
         <v>3004</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="I59" s="1">
         <v>0</v>
@@ -4296,15 +4334,9 @@
       <c r="P59" s="2">
         <v>20</v>
       </c>
-      <c r="Q59" s="1">
-        <v>0</v>
-      </c>
-      <c r="R59" s="1">
-        <v>0</v>
-      </c>
-      <c r="S59" s="1">
-        <v>0</v>
-      </c>
+      <c r="Q59" s="2"/>
+      <c r="R59" s="2"/>
+      <c r="S59" s="2"/>
       <c r="T59" s="1">
         <v>0</v>
       </c>
@@ -4317,8 +4349,11 @@
       <c r="W59" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" s="1" customFormat="1" customHeight="1" spans="3:23">
+      <c r="X59" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" s="1" customFormat="1" customHeight="1" spans="3:26">
       <c r="C60" s="1">
         <v>30051</v>
       </c>
@@ -4329,13 +4364,13 @@
         <v>3005</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="I60" s="1">
         <v>0</v>
@@ -4361,15 +4396,9 @@
       <c r="P60" s="2">
         <v>5</v>
       </c>
-      <c r="Q60" s="1">
-        <v>0</v>
-      </c>
-      <c r="R60" s="1">
-        <v>0</v>
-      </c>
-      <c r="S60" s="1">
-        <v>0</v>
-      </c>
+      <c r="Q60" s="2"/>
+      <c r="R60" s="2"/>
+      <c r="S60" s="2"/>
       <c r="T60" s="1">
         <v>0</v>
       </c>
@@ -4382,8 +4411,11 @@
       <c r="W60" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" s="1" customFormat="1" customHeight="1" spans="3:23">
+      <c r="X60" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" s="1" customFormat="1" customHeight="1" spans="3:26">
       <c r="C61" s="1">
         <v>30061</v>
       </c>
@@ -4394,13 +4426,13 @@
         <v>3006</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="I61" s="1">
         <v>0</v>
@@ -4426,15 +4458,9 @@
       <c r="P61" s="2">
         <v>5</v>
       </c>
-      <c r="Q61" s="1">
-        <v>0</v>
-      </c>
-      <c r="R61" s="1">
-        <v>0</v>
-      </c>
-      <c r="S61" s="1">
-        <v>0</v>
-      </c>
+      <c r="Q61" s="2"/>
+      <c r="R61" s="2"/>
+      <c r="S61" s="2"/>
       <c r="T61" s="1">
         <v>0</v>
       </c>
@@ -4447,8 +4473,11 @@
       <c r="W61" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" s="1" customFormat="1" customHeight="1" spans="3:23">
+      <c r="X61" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" s="1" customFormat="1" customHeight="1" spans="3:26">
       <c r="C62" s="1">
         <v>30071</v>
       </c>
@@ -4459,13 +4488,13 @@
         <v>3007</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="I62" s="1">
         <v>0</v>
@@ -4491,15 +4520,9 @@
       <c r="P62" s="2">
         <v>20</v>
       </c>
-      <c r="Q62" s="1">
-        <v>0</v>
-      </c>
-      <c r="R62" s="1">
-        <v>0</v>
-      </c>
-      <c r="S62" s="1">
-        <v>0</v>
-      </c>
+      <c r="Q62" s="2"/>
+      <c r="R62" s="2"/>
+      <c r="S62" s="2"/>
       <c r="T62" s="1">
         <v>0</v>
       </c>
@@ -4512,12 +4535,15 @@
       <c r="W62" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" s="1" customFormat="1" customHeight="1" spans="3:23">
+      <c r="X62" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" s="1" customFormat="1" customHeight="1" spans="3:26">
       <c r="F63" s="2"/>
-      <c r="S63" s="2"/>
-    </row>
-    <row r="64" s="1" customFormat="1" customHeight="1" spans="3:23">
+      <c r="W63" s="2"/>
+    </row>
+    <row r="64" s="1" customFormat="1" customHeight="1" spans="3:26">
       <c r="C64" s="1">
         <v>30022</v>
       </c>
@@ -4528,13 +4554,13 @@
         <v>3002</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="I64" s="1">
         <v>0</v>
@@ -4560,29 +4586,23 @@
       <c r="P64" s="1">
         <v>0</v>
       </c>
-      <c r="Q64" s="1">
-        <v>0</v>
-      </c>
-      <c r="R64" s="1">
-        <v>0</v>
-      </c>
-      <c r="S64" s="2">
+      <c r="T64" s="1">
+        <v>0</v>
+      </c>
+      <c r="U64" s="1">
+        <v>0</v>
+      </c>
+      <c r="V64" s="1">
+        <v>0</v>
+      </c>
+      <c r="W64" s="2">
         <v>20</v>
       </c>
-      <c r="T64" s="1">
-        <v>0</v>
-      </c>
-      <c r="U64" s="1">
-        <v>0</v>
-      </c>
-      <c r="V64" s="1">
-        <v>0</v>
-      </c>
-      <c r="W64" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" s="1" customFormat="1" customHeight="1" spans="3:23">
+      <c r="X64" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" s="1" customFormat="1" customHeight="1" spans="3:26">
       <c r="C65" s="1">
         <v>30032</v>
       </c>
@@ -4593,13 +4613,13 @@
         <v>3003</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="I65" s="1">
         <v>0</v>
@@ -4625,29 +4645,23 @@
       <c r="P65" s="1">
         <v>0</v>
       </c>
-      <c r="Q65" s="1">
-        <v>0</v>
-      </c>
-      <c r="R65" s="1">
-        <v>0</v>
-      </c>
-      <c r="S65" s="2">
+      <c r="T65" s="1">
+        <v>0</v>
+      </c>
+      <c r="U65" s="1">
+        <v>0</v>
+      </c>
+      <c r="V65" s="1">
+        <v>0</v>
+      </c>
+      <c r="W65" s="2">
         <v>20</v>
       </c>
-      <c r="T65" s="1">
-        <v>0</v>
-      </c>
-      <c r="U65" s="1">
-        <v>0</v>
-      </c>
-      <c r="V65" s="1">
-        <v>0</v>
-      </c>
-      <c r="W65" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" s="1" customFormat="1" customHeight="1" spans="3:23">
+      <c r="X65" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" s="1" customFormat="1" customHeight="1" spans="3:26">
       <c r="C66" s="1">
         <v>30042</v>
       </c>
@@ -4658,13 +4672,13 @@
         <v>3004</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="I66" s="1">
         <v>0</v>
@@ -4690,29 +4704,23 @@
       <c r="P66" s="1">
         <v>0</v>
       </c>
-      <c r="Q66" s="1">
-        <v>0</v>
-      </c>
-      <c r="R66" s="1">
-        <v>0</v>
-      </c>
-      <c r="S66" s="2">
+      <c r="T66" s="1">
+        <v>0</v>
+      </c>
+      <c r="U66" s="1">
+        <v>0</v>
+      </c>
+      <c r="V66" s="1">
+        <v>0</v>
+      </c>
+      <c r="W66" s="2">
         <v>20</v>
       </c>
-      <c r="T66" s="1">
-        <v>0</v>
-      </c>
-      <c r="U66" s="1">
-        <v>0</v>
-      </c>
-      <c r="V66" s="1">
-        <v>0</v>
-      </c>
-      <c r="W66" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" s="1" customFormat="1" customHeight="1" spans="3:23">
+      <c r="X66" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" s="1" customFormat="1" customHeight="1" spans="3:26">
       <c r="C67" s="1">
         <v>30072</v>
       </c>
@@ -4723,13 +4731,13 @@
         <v>3007</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="I67" s="1">
         <v>0</v>
@@ -4755,34 +4763,31 @@
       <c r="P67" s="1">
         <v>0</v>
       </c>
-      <c r="Q67" s="1">
-        <v>0</v>
-      </c>
-      <c r="R67" s="1">
-        <v>0</v>
-      </c>
-      <c r="S67" s="2">
+      <c r="T67" s="1">
+        <v>0</v>
+      </c>
+      <c r="U67" s="1">
+        <v>0</v>
+      </c>
+      <c r="V67" s="1">
+        <v>0</v>
+      </c>
+      <c r="W67" s="2">
         <v>20</v>
       </c>
-      <c r="T67" s="1">
-        <v>0</v>
-      </c>
-      <c r="U67" s="1">
-        <v>0</v>
-      </c>
-      <c r="V67" s="1">
-        <v>0</v>
-      </c>
-      <c r="W67" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" s="1" customFormat="1" customHeight="1" spans="3:23">
+      <c r="X67" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" s="1" customFormat="1" customHeight="1" spans="3:26">
       <c r="E68" s="2"/>
       <c r="F68" s="2"/>
       <c r="P68" s="2"/>
-    </row>
-    <row r="69" s="2" customFormat="1" customHeight="1" spans="3:23">
+      <c r="Q68" s="2"/>
+      <c r="R68" s="2"/>
+      <c r="S68" s="2"/>
+    </row>
+    <row r="69" s="2" customFormat="1" customHeight="1" spans="3:26">
       <c r="C69" s="1">
         <v>30023</v>
       </c>
@@ -4793,14 +4798,14 @@
         <v>3002</v>
       </c>
       <c r="F69" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="G69" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="H69" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="G69" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="H69" s="1" t="s">
-        <v>54</v>
-      </c>
       <c r="I69" s="1">
         <v>0</v>
       </c>
@@ -4825,29 +4830,27 @@
       <c r="P69" s="1">
         <v>0</v>
       </c>
-      <c r="Q69" s="1">
-        <v>0</v>
-      </c>
-      <c r="R69" s="1">
-        <v>0</v>
-      </c>
-      <c r="S69" s="1">
-        <v>0</v>
-      </c>
-      <c r="T69" s="2">
+      <c r="Q69" s="1"/>
+      <c r="R69" s="1"/>
+      <c r="S69" s="1"/>
+      <c r="T69" s="1">
+        <v>0</v>
+      </c>
+      <c r="U69" s="1">
+        <v>0</v>
+      </c>
+      <c r="V69" s="1">
+        <v>0</v>
+      </c>
+      <c r="W69" s="1">
+        <v>0</v>
+      </c>
+      <c r="X69" s="2">
         <v>20</v>
       </c>
-      <c r="U69" s="1">
-        <v>0</v>
-      </c>
-      <c r="V69" s="1">
-        <v>0</v>
-      </c>
-      <c r="W69" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" s="2" customFormat="1" customHeight="1" spans="3:23">
+      <c r="Z69" s="1"/>
+    </row>
+    <row r="70" s="2" customFormat="1" customHeight="1" spans="3:26">
       <c r="C70" s="1">
         <v>30033</v>
       </c>
@@ -4858,13 +4861,13 @@
         <v>3003</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="I70" s="1">
         <v>0</v>
@@ -4890,29 +4893,27 @@
       <c r="P70" s="1">
         <v>0</v>
       </c>
-      <c r="Q70" s="1">
-        <v>0</v>
-      </c>
-      <c r="R70" s="1">
-        <v>0</v>
-      </c>
-      <c r="S70" s="1">
-        <v>0</v>
-      </c>
-      <c r="T70" s="2">
+      <c r="Q70" s="1"/>
+      <c r="R70" s="1"/>
+      <c r="S70" s="1"/>
+      <c r="T70" s="1">
+        <v>0</v>
+      </c>
+      <c r="U70" s="1">
+        <v>0</v>
+      </c>
+      <c r="V70" s="1">
+        <v>0</v>
+      </c>
+      <c r="W70" s="1">
+        <v>0</v>
+      </c>
+      <c r="X70" s="2">
         <v>20</v>
       </c>
-      <c r="U70" s="1">
-        <v>0</v>
-      </c>
-      <c r="V70" s="1">
-        <v>0</v>
-      </c>
-      <c r="W70" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" s="2" customFormat="1" customHeight="1" spans="3:23">
+      <c r="Z70" s="1"/>
+    </row>
+    <row r="71" s="2" customFormat="1" customHeight="1" spans="3:26">
       <c r="C71" s="1">
         <v>30043</v>
       </c>
@@ -4923,13 +4924,13 @@
         <v>3004</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>54</v>
+        <v>67</v>
       </c>
       <c r="I71" s="1">
         <v>0</v>
@@ -4955,29 +4956,27 @@
       <c r="P71" s="1">
         <v>0</v>
       </c>
-      <c r="Q71" s="1">
-        <v>0</v>
-      </c>
-      <c r="R71" s="1">
-        <v>0</v>
-      </c>
-      <c r="S71" s="1">
-        <v>0</v>
-      </c>
-      <c r="T71" s="2">
+      <c r="Q71" s="1"/>
+      <c r="R71" s="1"/>
+      <c r="S71" s="1"/>
+      <c r="T71" s="1">
+        <v>0</v>
+      </c>
+      <c r="U71" s="1">
+        <v>0</v>
+      </c>
+      <c r="V71" s="1">
+        <v>0</v>
+      </c>
+      <c r="W71" s="1">
+        <v>0</v>
+      </c>
+      <c r="X71" s="2">
         <v>20</v>
       </c>
-      <c r="U71" s="1">
-        <v>0</v>
-      </c>
-      <c r="V71" s="1">
-        <v>0</v>
-      </c>
-      <c r="W71" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" s="2" customFormat="1" customHeight="1" spans="3:23">
+      <c r="Z71" s="1"/>
+    </row>
+    <row r="72" s="2" customFormat="1" customHeight="1" spans="3:26">
       <c r="C72" s="1">
         <v>30073</v>
       </c>
@@ -4988,13 +4987,13 @@
         <v>3007</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="H72" s="1" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="I72" s="1">
         <v>0</v>
@@ -5020,29 +5019,27 @@
       <c r="P72" s="1">
         <v>0</v>
       </c>
-      <c r="Q72" s="1">
-        <v>0</v>
-      </c>
-      <c r="R72" s="1">
-        <v>0</v>
-      </c>
-      <c r="S72" s="1">
-        <v>0</v>
-      </c>
-      <c r="T72" s="2">
+      <c r="Q72" s="1"/>
+      <c r="R72" s="1"/>
+      <c r="S72" s="1"/>
+      <c r="T72" s="1">
+        <v>0</v>
+      </c>
+      <c r="U72" s="1">
+        <v>0</v>
+      </c>
+      <c r="V72" s="1">
+        <v>0</v>
+      </c>
+      <c r="W72" s="1">
+        <v>0</v>
+      </c>
+      <c r="X72" s="2">
         <v>20</v>
       </c>
-      <c r="U72" s="1">
-        <v>0</v>
-      </c>
-      <c r="V72" s="1">
-        <v>0</v>
-      </c>
-      <c r="W72" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" s="2" customFormat="1" customHeight="1" spans="3:23">
+      <c r="Z72" s="1"/>
+    </row>
+    <row r="73" s="2" customFormat="1" customHeight="1" spans="3:26">
       <c r="C73" s="1"/>
       <c r="D73" s="1"/>
       <c r="G73" s="1"/>
@@ -5062,8 +5059,10 @@
       <c r="U73" s="1"/>
       <c r="V73" s="1"/>
       <c r="W73" s="1"/>
-    </row>
-    <row r="74" s="2" customFormat="1" customHeight="1" spans="3:23">
+      <c r="X73" s="1"/>
+      <c r="Z73" s="1"/>
+    </row>
+    <row r="74" s="2" customFormat="1" customHeight="1" spans="3:26">
       <c r="C74" s="1">
         <v>30024</v>
       </c>
@@ -5074,13 +5073,13 @@
         <v>3002</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="H74" s="1" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="I74" s="1">
         <v>0</v>
@@ -5106,29 +5105,27 @@
       <c r="P74" s="1">
         <v>0</v>
       </c>
-      <c r="Q74" s="1">
-        <v>0</v>
-      </c>
-      <c r="R74" s="1">
+      <c r="Q74" s="1"/>
+      <c r="R74" s="1"/>
+      <c r="S74" s="1"/>
+      <c r="T74" s="1">
+        <v>0</v>
+      </c>
+      <c r="U74" s="1">
         <v>100</v>
       </c>
-      <c r="S74" s="1">
-        <v>0</v>
-      </c>
-      <c r="T74" s="1">
-        <v>0</v>
-      </c>
-      <c r="U74" s="1">
-        <v>0</v>
-      </c>
       <c r="V74" s="1">
         <v>0</v>
       </c>
       <c r="W74" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" s="2" customFormat="1" customHeight="1" spans="3:23">
+      <c r="X74" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z74" s="1"/>
+    </row>
+    <row r="75" s="2" customFormat="1" customHeight="1" spans="3:26">
       <c r="C75" s="1">
         <v>30034</v>
       </c>
@@ -5139,13 +5136,13 @@
         <v>3003</v>
       </c>
       <c r="F75" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="G75" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="G75" s="1" t="s">
-        <v>55</v>
-      </c>
       <c r="H75" s="1" t="s">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="I75" s="1">
         <v>0</v>
@@ -5171,29 +5168,27 @@
       <c r="P75" s="1">
         <v>0</v>
       </c>
-      <c r="Q75" s="1">
-        <v>0</v>
-      </c>
-      <c r="R75" s="1">
+      <c r="Q75" s="1"/>
+      <c r="R75" s="1"/>
+      <c r="S75" s="1"/>
+      <c r="T75" s="1">
+        <v>0</v>
+      </c>
+      <c r="U75" s="1">
         <v>100</v>
       </c>
-      <c r="S75" s="1">
-        <v>0</v>
-      </c>
-      <c r="T75" s="1">
-        <v>0</v>
-      </c>
-      <c r="U75" s="1">
-        <v>0</v>
-      </c>
       <c r="V75" s="1">
         <v>0</v>
       </c>
       <c r="W75" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" s="2" customFormat="1" customHeight="1" spans="3:23">
+      <c r="X75" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z75" s="1"/>
+    </row>
+    <row r="76" s="2" customFormat="1" customHeight="1" spans="3:26">
       <c r="C76" s="1">
         <v>30044</v>
       </c>
@@ -5204,14 +5199,14 @@
         <v>3004</v>
       </c>
       <c r="F76" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G76" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="H76" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="G76" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="H76" s="1" t="s">
-        <v>56</v>
-      </c>
       <c r="I76" s="1">
         <v>0</v>
       </c>
@@ -5236,29 +5231,27 @@
       <c r="P76" s="1">
         <v>0</v>
       </c>
-      <c r="Q76" s="1">
-        <v>0</v>
-      </c>
-      <c r="R76" s="1">
+      <c r="Q76" s="1"/>
+      <c r="R76" s="1"/>
+      <c r="S76" s="1"/>
+      <c r="T76" s="1">
+        <v>0</v>
+      </c>
+      <c r="U76" s="1">
         <v>100</v>
       </c>
-      <c r="S76" s="1">
-        <v>0</v>
-      </c>
-      <c r="T76" s="1">
-        <v>0</v>
-      </c>
-      <c r="U76" s="1">
-        <v>0</v>
-      </c>
       <c r="V76" s="1">
         <v>0</v>
       </c>
       <c r="W76" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="77" s="1" customFormat="1" customHeight="1" spans="3:23">
+      <c r="X76" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z76" s="1"/>
+    </row>
+    <row r="77" s="1" customFormat="1" customHeight="1" spans="3:26">
       <c r="C77" s="1">
         <v>30074</v>
       </c>
@@ -5269,13 +5262,13 @@
         <v>3007</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="I77" s="1">
         <v>0</v>
@@ -5301,25 +5294,19 @@
       <c r="P77" s="1">
         <v>0</v>
       </c>
-      <c r="Q77" s="1">
-        <v>0</v>
-      </c>
-      <c r="R77" s="1">
+      <c r="T77" s="1">
+        <v>0</v>
+      </c>
+      <c r="U77" s="1">
         <v>100</v>
       </c>
-      <c r="S77" s="1">
-        <v>0</v>
-      </c>
-      <c r="T77" s="1">
-        <v>0</v>
-      </c>
-      <c r="U77" s="1">
-        <v>0</v>
-      </c>
       <c r="V77" s="1">
         <v>0</v>
       </c>
       <c r="W77" s="1">
+        <v>0</v>
+      </c>
+      <c r="X77" s="1">
         <v>0</v>
       </c>
     </row>

--- a/Excel/SkillSuitConfig.xlsx
+++ b/Excel/SkillSuitConfig.xlsx
@@ -56,7 +56,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K3" authorId="0">
+    <comment ref="N3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -79,7 +79,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P3" authorId="0">
+    <comment ref="S3" authorId="0">
       <text>
         <r>
           <rPr>
@@ -101,7 +101,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AC4" authorId="1">
+    <comment ref="AF4" authorId="1">
       <text>
         <r>
           <rPr>
@@ -123,7 +123,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AD4" authorId="1">
+    <comment ref="AG4" authorId="1">
       <text>
         <r>
           <rPr>
@@ -145,7 +145,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AE4" authorId="1">
+    <comment ref="AH4" authorId="1">
       <text>
         <r>
           <rPr>
@@ -174,7 +174,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="91">
   <si>
     <t>_ID</t>
   </si>
@@ -189,6 +189,15 @@
   </si>
   <si>
     <t>技能描述</t>
+  </si>
+  <si>
+    <t>EquipRate</t>
+  </si>
+  <si>
+    <t>StartQuality</t>
+  </si>
+  <si>
+    <t>EndQuality</t>
   </si>
   <si>
     <t>减少冷却时间</t>
@@ -1087,7 +1096,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1095,6 +1104,8 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1414,30 +1425,32 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:AE77"/>
+  <dimension ref="C3:AH77"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="6" width="9" style="1"/>
     <col min="7" max="7" width="13.75" style="1" customWidth="1"/>
     <col min="8" max="8" width="25.5833333333333" style="1" customWidth="1"/>
-    <col min="9" max="9" width="9.16666666666667" style="1" customWidth="1"/>
-    <col min="10" max="10" width="9" style="1"/>
-    <col min="11" max="11" width="7.91666666666667" style="1" customWidth="1"/>
-    <col min="12" max="14" width="10.375" style="1" customWidth="1"/>
-    <col min="15" max="15" width="10.875" style="1" customWidth="1"/>
-    <col min="16" max="19" width="8.83333333333333" style="1" customWidth="1"/>
-    <col min="20" max="20" width="13" style="1" customWidth="1"/>
-    <col min="21" max="21" width="9.08333333333333" style="1" customWidth="1"/>
-    <col min="22" max="22" width="10.625" style="1" customWidth="1"/>
-    <col min="23" max="23" width="12.625" style="1" customWidth="1"/>
-    <col min="24" max="24" width="9" style="1" customWidth="1"/>
-    <col min="26" max="26" width="9.75" style="1" customWidth="1"/>
-    <col min="27" max="32" width="9" style="1"/>
-    <col min="33" max="33" width="19.25" style="1" customWidth="1"/>
-    <col min="34" max="16384" width="9" style="1"/>
+    <col min="9" max="9" width="15.75" style="1" customWidth="1"/>
+    <col min="10" max="11" width="14.75" style="1" customWidth="1"/>
+    <col min="12" max="12" width="9.16666666666667" style="1" customWidth="1"/>
+    <col min="13" max="13" width="9" style="1"/>
+    <col min="14" max="14" width="7.91666666666667" style="1" customWidth="1"/>
+    <col min="15" max="17" width="10.375" style="1" customWidth="1"/>
+    <col min="18" max="18" width="10.875" style="1" customWidth="1"/>
+    <col min="19" max="22" width="8.83333333333333" style="1" customWidth="1"/>
+    <col min="23" max="23" width="13" style="1" customWidth="1"/>
+    <col min="24" max="24" width="9.08333333333333" style="1" customWidth="1"/>
+    <col min="25" max="25" width="10.625" style="1" customWidth="1"/>
+    <col min="26" max="26" width="12.625" style="1" customWidth="1"/>
+    <col min="27" max="27" width="9" style="1" customWidth="1"/>
+    <col min="29" max="29" width="9.75" style="1" customWidth="1"/>
+    <col min="30" max="35" width="9" style="1"/>
+    <col min="36" max="36" width="19.25" style="1" customWidth="1"/>
+    <col min="37" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:31">
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:34">
       <c r="C3" s="4" t="s">
         <v>0</v>
       </c>
@@ -1517,34 +1530,43 @@
       <c r="AC3" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="AD3" s="4"/>
-      <c r="AE3" s="4"/>
-    </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:31">
+      <c r="AD3" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="AE3" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="AF3" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="AG3" s="4"/>
+      <c r="AH3" s="4"/>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:34">
       <c r="C4" s="4" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>1</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="F4" s="4"/>
       <c r="G4" s="4" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>31</v>
+        <v>6</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="L4" s="4" t="s">
         <v>33</v>
@@ -1586,19 +1608,19 @@
         <v>45</v>
       </c>
       <c r="Y4" s="4" t="s">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="Z4" s="4" t="s">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="AA4" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AB4" s="4" t="s">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="AC4" s="4" t="s">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="AD4" s="4" t="s">
         <v>49</v>
@@ -1606,95 +1628,113 @@
       <c r="AE4" s="4" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:31">
+      <c r="AF4" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="AG4" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="AH4" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:34">
       <c r="C5" s="4" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="F5" s="4"/>
       <c r="G5" s="4" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="L5" s="4" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="M5" s="4" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="N5" s="4" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="O5" s="4" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="P5" s="4" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="R5" s="4" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="S5" s="4" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="U5" s="4" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="V5" s="4" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="W5" s="4" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="X5" s="4" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="Y5" s="4" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="Z5" s="4" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="AA5" s="4" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="AB5" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="AC5" s="4" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="AD5" s="4" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="AE5" s="4" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:31">
+        <v>56</v>
+      </c>
+      <c r="AF5" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="AG5" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="AH5" s="4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:34">
       <c r="C6" s="1">
         <v>10011</v>
       </c>
@@ -1705,22 +1745,22 @@
         <v>1001</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="I6" s="1">
-        <v>0</v>
-      </c>
-      <c r="J6" s="1">
-        <v>0</v>
-      </c>
-      <c r="K6" s="1">
-        <v>0</v>
+        <v>59</v>
+      </c>
+      <c r="I6" s="5">
+        <v>100</v>
+      </c>
+      <c r="J6" s="5">
+        <v>1</v>
+      </c>
+      <c r="K6" s="5">
+        <v>5</v>
       </c>
       <c r="L6" s="1">
         <v>0</v>
@@ -1735,16 +1775,16 @@
         <v>0</v>
       </c>
       <c r="P6" s="1">
-        <v>5</v>
-      </c>
-      <c r="T6" s="1">
-        <v>0</v>
-      </c>
-      <c r="U6" s="1">
-        <v>0</v>
-      </c>
-      <c r="V6" s="1">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="Q6" s="1">
+        <v>0</v>
+      </c>
+      <c r="R6" s="1">
+        <v>0</v>
+      </c>
+      <c r="S6" s="1">
+        <v>5</v>
       </c>
       <c r="W6" s="1">
         <v>0</v>
@@ -1752,8 +1792,17 @@
       <c r="X6" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:31">
+      <c r="Y6" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:34">
       <c r="C7" s="1">
         <v>10021</v>
       </c>
@@ -1764,22 +1813,22 @@
         <v>1002</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="I7" s="1">
-        <v>0</v>
-      </c>
-      <c r="J7" s="1">
-        <v>0</v>
-      </c>
-      <c r="K7" s="1">
-        <v>0</v>
+        <v>61</v>
+      </c>
+      <c r="I7" s="5">
+        <v>100</v>
+      </c>
+      <c r="J7" s="5">
+        <v>1</v>
+      </c>
+      <c r="K7" s="5">
+        <v>5</v>
       </c>
       <c r="L7" s="1">
         <v>0</v>
@@ -1793,29 +1842,38 @@
       <c r="O7" s="1">
         <v>0</v>
       </c>
-      <c r="P7" s="2">
+      <c r="P7" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="1">
+        <v>0</v>
+      </c>
+      <c r="R7" s="1">
+        <v>0</v>
+      </c>
+      <c r="S7" s="2">
         <v>20</v>
       </c>
-      <c r="Q7" s="2"/>
-      <c r="R7" s="2"/>
-      <c r="S7" s="2"/>
-      <c r="T7" s="1">
-        <v>0</v>
-      </c>
-      <c r="U7" s="1">
-        <v>0</v>
-      </c>
-      <c r="V7" s="1">
-        <v>0</v>
-      </c>
+      <c r="T7" s="2"/>
+      <c r="U7" s="2"/>
+      <c r="V7" s="2"/>
       <c r="W7" s="1">
         <v>0</v>
       </c>
       <c r="X7" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:31">
+      <c r="Y7" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z7" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA7" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:34">
       <c r="C8" s="1">
         <v>10031</v>
       </c>
@@ -1826,22 +1884,22 @@
         <v>1003</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="I8" s="1">
-        <v>0</v>
-      </c>
-      <c r="J8" s="1">
-        <v>0</v>
-      </c>
-      <c r="K8" s="1">
-        <v>0</v>
+        <v>61</v>
+      </c>
+      <c r="I8" s="5">
+        <v>100</v>
+      </c>
+      <c r="J8" s="5">
+        <v>1</v>
+      </c>
+      <c r="K8" s="5">
+        <v>5</v>
       </c>
       <c r="L8" s="1">
         <v>0</v>
@@ -1855,29 +1913,38 @@
       <c r="O8" s="1">
         <v>0</v>
       </c>
-      <c r="P8" s="2">
+      <c r="P8" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="1">
+        <v>0</v>
+      </c>
+      <c r="R8" s="1">
+        <v>0</v>
+      </c>
+      <c r="S8" s="2">
         <v>20</v>
       </c>
-      <c r="Q8" s="2"/>
-      <c r="R8" s="2"/>
-      <c r="S8" s="2"/>
-      <c r="T8" s="1">
-        <v>0</v>
-      </c>
-      <c r="U8" s="1">
-        <v>0</v>
-      </c>
-      <c r="V8" s="1">
-        <v>0</v>
-      </c>
+      <c r="T8" s="2"/>
+      <c r="U8" s="2"/>
+      <c r="V8" s="2"/>
       <c r="W8" s="1">
         <v>0</v>
       </c>
       <c r="X8" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:31">
+      <c r="Y8" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA8" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:34">
       <c r="C9" s="1">
         <v>10041</v>
       </c>
@@ -1888,22 +1955,22 @@
         <v>1004</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="I9" s="1">
-        <v>0</v>
-      </c>
-      <c r="J9" s="1">
-        <v>0</v>
-      </c>
-      <c r="K9" s="1">
-        <v>0</v>
+        <v>61</v>
+      </c>
+      <c r="I9" s="5">
+        <v>100</v>
+      </c>
+      <c r="J9" s="5">
+        <v>1</v>
+      </c>
+      <c r="K9" s="5">
+        <v>5</v>
       </c>
       <c r="L9" s="1">
         <v>0</v>
@@ -1917,29 +1984,38 @@
       <c r="O9" s="1">
         <v>0</v>
       </c>
-      <c r="P9" s="2">
+      <c r="P9" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="1">
+        <v>0</v>
+      </c>
+      <c r="R9" s="1">
+        <v>0</v>
+      </c>
+      <c r="S9" s="2">
         <v>20</v>
       </c>
-      <c r="Q9" s="2"/>
-      <c r="R9" s="2"/>
-      <c r="S9" s="2"/>
-      <c r="T9" s="1">
-        <v>0</v>
-      </c>
-      <c r="U9" s="1">
-        <v>0</v>
-      </c>
-      <c r="V9" s="1">
-        <v>0</v>
-      </c>
+      <c r="T9" s="2"/>
+      <c r="U9" s="2"/>
+      <c r="V9" s="2"/>
       <c r="W9" s="1">
         <v>0</v>
       </c>
       <c r="X9" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:31">
+      <c r="Y9" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z9" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA9" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:34">
       <c r="C10" s="1">
         <v>10051</v>
       </c>
@@ -1950,22 +2026,22 @@
         <v>1005</v>
       </c>
       <c r="F10" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="H10" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="G10" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="I10" s="1">
-        <v>0</v>
-      </c>
-      <c r="J10" s="1">
-        <v>0</v>
-      </c>
-      <c r="K10" s="1">
-        <v>0</v>
+      <c r="I10" s="5">
+        <v>100</v>
+      </c>
+      <c r="J10" s="5">
+        <v>1</v>
+      </c>
+      <c r="K10" s="5">
+        <v>5</v>
       </c>
       <c r="L10" s="1">
         <v>0</v>
@@ -1979,29 +2055,38 @@
       <c r="O10" s="1">
         <v>0</v>
       </c>
-      <c r="P10" s="2">
-        <v>5</v>
-      </c>
-      <c r="Q10" s="2"/>
-      <c r="R10" s="2"/>
-      <c r="S10" s="2"/>
-      <c r="T10" s="1">
-        <v>0</v>
-      </c>
-      <c r="U10" s="1">
-        <v>0</v>
-      </c>
-      <c r="V10" s="1">
-        <v>0</v>
-      </c>
+      <c r="P10" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="1">
+        <v>0</v>
+      </c>
+      <c r="R10" s="1">
+        <v>0</v>
+      </c>
+      <c r="S10" s="2">
+        <v>5</v>
+      </c>
+      <c r="T10" s="2"/>
+      <c r="U10" s="2"/>
+      <c r="V10" s="2"/>
       <c r="W10" s="1">
         <v>0</v>
       </c>
       <c r="X10" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:31">
+      <c r="Y10" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z10" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA10" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:34">
       <c r="C11" s="1">
         <v>10061</v>
       </c>
@@ -2012,22 +2097,22 @@
         <v>1006</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="I11" s="1">
-        <v>0</v>
-      </c>
-      <c r="J11" s="1">
-        <v>0</v>
-      </c>
-      <c r="K11" s="1">
-        <v>0</v>
+        <v>61</v>
+      </c>
+      <c r="I11" s="5">
+        <v>100</v>
+      </c>
+      <c r="J11" s="5">
+        <v>1</v>
+      </c>
+      <c r="K11" s="5">
+        <v>5</v>
       </c>
       <c r="L11" s="1">
         <v>0</v>
@@ -2041,29 +2126,38 @@
       <c r="O11" s="1">
         <v>0</v>
       </c>
-      <c r="P11" s="2">
-        <v>5</v>
-      </c>
-      <c r="Q11" s="2"/>
-      <c r="R11" s="2"/>
-      <c r="S11" s="2"/>
-      <c r="T11" s="1">
-        <v>0</v>
-      </c>
-      <c r="U11" s="1">
-        <v>0</v>
-      </c>
-      <c r="V11" s="1">
-        <v>0</v>
-      </c>
+      <c r="P11" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="1">
+        <v>0</v>
+      </c>
+      <c r="R11" s="1">
+        <v>0</v>
+      </c>
+      <c r="S11" s="2">
+        <v>5</v>
+      </c>
+      <c r="T11" s="2"/>
+      <c r="U11" s="2"/>
+      <c r="V11" s="2"/>
       <c r="W11" s="1">
         <v>0</v>
       </c>
       <c r="X11" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:31">
+      <c r="Y11" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z11" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA11" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:34">
       <c r="C12" s="1">
         <v>10071</v>
       </c>
@@ -2074,22 +2168,22 @@
         <v>1007</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="I12" s="1">
-        <v>0</v>
-      </c>
-      <c r="J12" s="1">
-        <v>0</v>
-      </c>
-      <c r="K12" s="1">
-        <v>0</v>
+        <v>61</v>
+      </c>
+      <c r="I12" s="5">
+        <v>100</v>
+      </c>
+      <c r="J12" s="5">
+        <v>1</v>
+      </c>
+      <c r="K12" s="5">
+        <v>5</v>
       </c>
       <c r="L12" s="1">
         <v>0</v>
@@ -2103,39 +2197,51 @@
       <c r="O12" s="1">
         <v>0</v>
       </c>
-      <c r="P12" s="2">
+      <c r="P12" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="1">
+        <v>0</v>
+      </c>
+      <c r="R12" s="1">
+        <v>0</v>
+      </c>
+      <c r="S12" s="2">
         <v>20</v>
       </c>
-      <c r="Q12" s="2"/>
-      <c r="R12" s="2"/>
-      <c r="S12" s="2"/>
-      <c r="T12" s="1">
-        <v>0</v>
-      </c>
-      <c r="U12" s="1">
-        <v>0</v>
-      </c>
-      <c r="V12" s="1">
-        <v>0</v>
-      </c>
+      <c r="T12" s="2"/>
+      <c r="U12" s="2"/>
+      <c r="V12" s="2"/>
       <c r="W12" s="1">
         <v>0</v>
       </c>
       <c r="X12" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:31">
+      <c r="Y12" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z12" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA12" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:34">
       <c r="F13" s="2"/>
       <c r="G13" s="1"/>
       <c r="H13" s="1"/>
-      <c r="I13" s="1"/>
-      <c r="J13" s="1"/>
-      <c r="K13" s="1"/>
+      <c r="I13" s="5"/>
+      <c r="J13" s="5"/>
+      <c r="K13" s="5"/>
       <c r="L13" s="1"/>
-      <c r="W13" s="2"/>
-    </row>
-    <row r="14" s="1" customFormat="1" customHeight="1" spans="3:31">
+      <c r="M13" s="1"/>
+      <c r="N13" s="1"/>
+      <c r="O13" s="1"/>
+      <c r="Z13" s="2"/>
+    </row>
+    <row r="14" s="1" customFormat="1" customHeight="1" spans="3:34">
       <c r="C14" s="1">
         <v>10022</v>
       </c>
@@ -2146,22 +2252,22 @@
         <v>1002</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="I14" s="1">
-        <v>0</v>
-      </c>
-      <c r="J14" s="1">
-        <v>0</v>
-      </c>
-      <c r="K14" s="1">
-        <v>0</v>
+        <v>68</v>
+      </c>
+      <c r="I14" s="5">
+        <v>40</v>
+      </c>
+      <c r="J14" s="5">
+        <v>4</v>
+      </c>
+      <c r="K14" s="5">
+        <v>5</v>
       </c>
       <c r="L14" s="1">
         <v>0</v>
@@ -2178,23 +2284,32 @@
       <c r="P14" s="1">
         <v>0</v>
       </c>
-      <c r="T14" s="1">
-        <v>0</v>
-      </c>
-      <c r="U14" s="1">
-        <v>0</v>
-      </c>
-      <c r="V14" s="1">
-        <v>0</v>
-      </c>
-      <c r="W14" s="2">
+      <c r="Q14" s="1">
+        <v>0</v>
+      </c>
+      <c r="R14" s="1">
+        <v>0</v>
+      </c>
+      <c r="S14" s="1">
+        <v>0</v>
+      </c>
+      <c r="W14" s="1">
+        <v>0</v>
+      </c>
+      <c r="X14" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="2">
         <v>20</v>
       </c>
-      <c r="X14" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" s="1" customFormat="1" customHeight="1" spans="3:31">
+      <c r="AA14" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" s="1" customFormat="1" customHeight="1" spans="3:34">
       <c r="C15" s="1">
         <v>10032</v>
       </c>
@@ -2205,22 +2320,22 @@
         <v>1003</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="I15" s="1">
-        <v>0</v>
-      </c>
-      <c r="J15" s="1">
-        <v>0</v>
-      </c>
-      <c r="K15" s="1">
-        <v>0</v>
+        <v>68</v>
+      </c>
+      <c r="I15" s="5">
+        <v>40</v>
+      </c>
+      <c r="J15" s="5">
+        <v>4</v>
+      </c>
+      <c r="K15" s="5">
+        <v>5</v>
       </c>
       <c r="L15" s="1">
         <v>0</v>
@@ -2237,23 +2352,32 @@
       <c r="P15" s="1">
         <v>0</v>
       </c>
-      <c r="T15" s="1">
-        <v>0</v>
-      </c>
-      <c r="U15" s="1">
-        <v>0</v>
-      </c>
-      <c r="V15" s="1">
-        <v>0</v>
-      </c>
-      <c r="W15" s="2">
+      <c r="Q15" s="1">
+        <v>0</v>
+      </c>
+      <c r="R15" s="1">
+        <v>0</v>
+      </c>
+      <c r="S15" s="1">
+        <v>0</v>
+      </c>
+      <c r="W15" s="1">
+        <v>0</v>
+      </c>
+      <c r="X15" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z15" s="2">
         <v>20</v>
       </c>
-      <c r="X15" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" s="1" customFormat="1" customHeight="1" spans="3:31">
+      <c r="AA15" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" s="1" customFormat="1" customHeight="1" spans="3:34">
       <c r="C16" s="1">
         <v>10042</v>
       </c>
@@ -2264,22 +2388,22 @@
         <v>1004</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="I16" s="1">
-        <v>0</v>
-      </c>
-      <c r="J16" s="1">
-        <v>0</v>
-      </c>
-      <c r="K16" s="1">
-        <v>0</v>
+        <v>68</v>
+      </c>
+      <c r="I16" s="5">
+        <v>40</v>
+      </c>
+      <c r="J16" s="5">
+        <v>4</v>
+      </c>
+      <c r="K16" s="5">
+        <v>5</v>
       </c>
       <c r="L16" s="1">
         <v>0</v>
@@ -2296,23 +2420,32 @@
       <c r="P16" s="1">
         <v>0</v>
       </c>
-      <c r="T16" s="1">
-        <v>0</v>
-      </c>
-      <c r="U16" s="1">
-        <v>0</v>
-      </c>
-      <c r="V16" s="1">
-        <v>0</v>
-      </c>
-      <c r="W16" s="2">
+      <c r="Q16" s="1">
+        <v>0</v>
+      </c>
+      <c r="R16" s="1">
+        <v>0</v>
+      </c>
+      <c r="S16" s="1">
+        <v>0</v>
+      </c>
+      <c r="W16" s="1">
+        <v>0</v>
+      </c>
+      <c r="X16" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y16" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z16" s="2">
         <v>20</v>
       </c>
-      <c r="X16" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" s="1" customFormat="1" customHeight="1" spans="3:26">
+      <c r="AA16" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" s="1" customFormat="1" customHeight="1" spans="3:29">
       <c r="C17" s="1">
         <v>10072</v>
       </c>
@@ -2323,22 +2456,22 @@
         <v>1007</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="I17" s="1">
-        <v>0</v>
-      </c>
-      <c r="J17" s="1">
-        <v>0</v>
-      </c>
-      <c r="K17" s="1">
-        <v>0</v>
+        <v>68</v>
+      </c>
+      <c r="I17" s="5">
+        <v>40</v>
+      </c>
+      <c r="J17" s="5">
+        <v>4</v>
+      </c>
+      <c r="K17" s="5">
+        <v>5</v>
       </c>
       <c r="L17" s="1">
         <v>0</v>
@@ -2355,31 +2488,43 @@
       <c r="P17" s="1">
         <v>0</v>
       </c>
-      <c r="T17" s="1">
-        <v>0</v>
-      </c>
-      <c r="U17" s="1">
-        <v>0</v>
-      </c>
-      <c r="V17" s="1">
-        <v>0</v>
-      </c>
-      <c r="W17" s="2">
+      <c r="Q17" s="1">
+        <v>0</v>
+      </c>
+      <c r="R17" s="1">
+        <v>0</v>
+      </c>
+      <c r="S17" s="1">
+        <v>0</v>
+      </c>
+      <c r="W17" s="1">
+        <v>0</v>
+      </c>
+      <c r="X17" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y17" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z17" s="2">
         <v>20</v>
       </c>
-      <c r="X17" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" s="1" customFormat="1" customHeight="1" spans="3:26">
+      <c r="AA17" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" s="1" customFormat="1" customHeight="1" spans="3:29">
       <c r="E18" s="2"/>
       <c r="F18" s="2"/>
-      <c r="P18" s="2"/>
-      <c r="Q18" s="2"/>
-      <c r="R18" s="2"/>
+      <c r="I18" s="5"/>
+      <c r="J18" s="5"/>
+      <c r="K18" s="5"/>
       <c r="S18" s="2"/>
-    </row>
-    <row r="19" s="2" customFormat="1" customHeight="1" spans="3:26">
+      <c r="T18" s="2"/>
+      <c r="U18" s="2"/>
+      <c r="V18" s="2"/>
+    </row>
+    <row r="19" s="2" customFormat="1" customHeight="1" spans="3:29">
       <c r="C19" s="1">
         <v>10023</v>
       </c>
@@ -2390,22 +2535,22 @@
         <v>1002</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="I19" s="1">
-        <v>0</v>
-      </c>
-      <c r="J19" s="1">
-        <v>0</v>
-      </c>
-      <c r="K19" s="1">
-        <v>0</v>
+        <v>70</v>
+      </c>
+      <c r="I19" s="5">
+        <v>60</v>
+      </c>
+      <c r="J19" s="5">
+        <v>4</v>
+      </c>
+      <c r="K19" s="5">
+        <v>5</v>
       </c>
       <c r="L19" s="1">
         <v>0</v>
@@ -2422,27 +2567,36 @@
       <c r="P19" s="1">
         <v>0</v>
       </c>
-      <c r="Q19" s="1"/>
-      <c r="R19" s="1"/>
-      <c r="S19" s="1"/>
-      <c r="T19" s="1">
-        <v>0</v>
-      </c>
-      <c r="U19" s="1">
-        <v>0</v>
-      </c>
-      <c r="V19" s="1">
-        <v>0</v>
-      </c>
+      <c r="Q19" s="1">
+        <v>0</v>
+      </c>
+      <c r="R19" s="1">
+        <v>0</v>
+      </c>
+      <c r="S19" s="1">
+        <v>0</v>
+      </c>
+      <c r="T19" s="1"/>
+      <c r="U19" s="1"/>
+      <c r="V19" s="1"/>
       <c r="W19" s="1">
         <v>0</v>
       </c>
-      <c r="X19" s="2">
+      <c r="X19" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y19" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z19" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA19" s="2">
         <v>20</v>
       </c>
-      <c r="Z19" s="1"/>
-    </row>
-    <row r="20" s="2" customFormat="1" customHeight="1" spans="3:26">
+      <c r="AC19" s="1"/>
+    </row>
+    <row r="20" s="2" customFormat="1" customHeight="1" spans="3:29">
       <c r="C20" s="1">
         <v>10033</v>
       </c>
@@ -2453,22 +2607,22 @@
         <v>1003</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="I20" s="1">
-        <v>0</v>
-      </c>
-      <c r="J20" s="1">
-        <v>0</v>
-      </c>
-      <c r="K20" s="1">
-        <v>0</v>
+        <v>70</v>
+      </c>
+      <c r="I20" s="5">
+        <v>60</v>
+      </c>
+      <c r="J20" s="5">
+        <v>4</v>
+      </c>
+      <c r="K20" s="5">
+        <v>5</v>
       </c>
       <c r="L20" s="1">
         <v>0</v>
@@ -2485,27 +2639,36 @@
       <c r="P20" s="1">
         <v>0</v>
       </c>
-      <c r="Q20" s="1"/>
-      <c r="R20" s="1"/>
-      <c r="S20" s="1"/>
-      <c r="T20" s="1">
-        <v>0</v>
-      </c>
-      <c r="U20" s="1">
-        <v>0</v>
-      </c>
-      <c r="V20" s="1">
-        <v>0</v>
-      </c>
+      <c r="Q20" s="1">
+        <v>0</v>
+      </c>
+      <c r="R20" s="1">
+        <v>0</v>
+      </c>
+      <c r="S20" s="1">
+        <v>0</v>
+      </c>
+      <c r="T20" s="1"/>
+      <c r="U20" s="1"/>
+      <c r="V20" s="1"/>
       <c r="W20" s="1">
         <v>0</v>
       </c>
-      <c r="X20" s="2">
+      <c r="X20" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="2">
         <v>20</v>
       </c>
-      <c r="Z20" s="1"/>
-    </row>
-    <row r="21" s="2" customFormat="1" customHeight="1" spans="3:26">
+      <c r="AC20" s="1"/>
+    </row>
+    <row r="21" s="2" customFormat="1" customHeight="1" spans="3:29">
       <c r="C21" s="1">
         <v>10043</v>
       </c>
@@ -2516,22 +2679,22 @@
         <v>1004</v>
       </c>
       <c r="F21" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="G21" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="H21" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="I21" s="5">
         <v>60</v>
       </c>
-      <c r="G21" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="H21" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="I21" s="1">
-        <v>0</v>
-      </c>
-      <c r="J21" s="1">
-        <v>0</v>
-      </c>
-      <c r="K21" s="1">
-        <v>0</v>
+      <c r="J21" s="5">
+        <v>4</v>
+      </c>
+      <c r="K21" s="5">
+        <v>5</v>
       </c>
       <c r="L21" s="1">
         <v>0</v>
@@ -2548,27 +2711,36 @@
       <c r="P21" s="1">
         <v>0</v>
       </c>
-      <c r="Q21" s="1"/>
-      <c r="R21" s="1"/>
-      <c r="S21" s="1"/>
-      <c r="T21" s="1">
-        <v>0</v>
-      </c>
-      <c r="U21" s="1">
-        <v>0</v>
-      </c>
-      <c r="V21" s="1">
-        <v>0</v>
-      </c>
+      <c r="Q21" s="1">
+        <v>0</v>
+      </c>
+      <c r="R21" s="1">
+        <v>0</v>
+      </c>
+      <c r="S21" s="1">
+        <v>0</v>
+      </c>
+      <c r="T21" s="1"/>
+      <c r="U21" s="1"/>
+      <c r="V21" s="1"/>
       <c r="W21" s="1">
         <v>0</v>
       </c>
-      <c r="X21" s="2">
+      <c r="X21" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y21" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z21" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA21" s="2">
         <v>20</v>
       </c>
-      <c r="Z21" s="1"/>
-    </row>
-    <row r="22" s="2" customFormat="1" customHeight="1" spans="3:26">
+      <c r="AC21" s="1"/>
+    </row>
+    <row r="22" s="2" customFormat="1" customHeight="1" spans="3:29">
       <c r="C22" s="1">
         <v>10073</v>
       </c>
@@ -2579,22 +2751,22 @@
         <v>1007</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="I22" s="1">
-        <v>0</v>
-      </c>
-      <c r="J22" s="1">
-        <v>0</v>
-      </c>
-      <c r="K22" s="1">
-        <v>0</v>
+        <v>70</v>
+      </c>
+      <c r="I22" s="5">
+        <v>60</v>
+      </c>
+      <c r="J22" s="5">
+        <v>4</v>
+      </c>
+      <c r="K22" s="5">
+        <v>5</v>
       </c>
       <c r="L22" s="1">
         <v>0</v>
@@ -2611,36 +2783,45 @@
       <c r="P22" s="1">
         <v>0</v>
       </c>
-      <c r="Q22" s="1"/>
-      <c r="R22" s="1"/>
-      <c r="S22" s="1"/>
-      <c r="T22" s="1">
-        <v>0</v>
-      </c>
-      <c r="U22" s="1">
-        <v>0</v>
-      </c>
-      <c r="V22" s="1">
-        <v>0</v>
-      </c>
+      <c r="Q22" s="1">
+        <v>0</v>
+      </c>
+      <c r="R22" s="1">
+        <v>0</v>
+      </c>
+      <c r="S22" s="1">
+        <v>0</v>
+      </c>
+      <c r="T22" s="1"/>
+      <c r="U22" s="1"/>
+      <c r="V22" s="1"/>
       <c r="W22" s="1">
         <v>0</v>
       </c>
-      <c r="X22" s="2">
+      <c r="X22" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y22" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z22" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA22" s="2">
         <v>20</v>
       </c>
-      <c r="Z22" s="1"/>
-    </row>
-    <row r="23" s="2" customFormat="1" customHeight="1" spans="3:26">
+      <c r="AC22" s="1"/>
+    </row>
+    <row r="23" s="2" customFormat="1" customHeight="1" spans="3:29">
       <c r="C23" s="1"/>
       <c r="D23" s="1"/>
       <c r="E23" s="2"/>
       <c r="F23" s="2"/>
       <c r="G23" s="1"/>
       <c r="H23" s="1"/>
-      <c r="I23" s="1"/>
-      <c r="J23" s="1"/>
-      <c r="K23" s="1"/>
+      <c r="I23" s="5"/>
+      <c r="J23" s="5"/>
+      <c r="K23" s="5"/>
       <c r="L23" s="1"/>
       <c r="M23" s="1"/>
       <c r="N23" s="1"/>
@@ -2654,9 +2835,12 @@
       <c r="V23" s="1"/>
       <c r="W23" s="1"/>
       <c r="X23" s="1"/>
+      <c r="Y23" s="1"/>
       <c r="Z23" s="1"/>
-    </row>
-    <row r="24" s="2" customFormat="1" customHeight="1" spans="3:26">
+      <c r="AA23" s="1"/>
+      <c r="AC23" s="1"/>
+    </row>
+    <row r="24" s="2" customFormat="1" customHeight="1" spans="3:29">
       <c r="C24" s="1">
         <v>10024</v>
       </c>
@@ -2667,22 +2851,22 @@
         <v>1002</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="I24" s="1">
-        <v>0</v>
-      </c>
-      <c r="J24" s="1">
-        <v>0</v>
-      </c>
-      <c r="K24" s="1">
-        <v>0</v>
+        <v>72</v>
+      </c>
+      <c r="I24" s="6">
+        <v>20</v>
+      </c>
+      <c r="J24" s="6">
+        <v>5</v>
+      </c>
+      <c r="K24" s="6">
+        <v>5</v>
       </c>
       <c r="L24" s="1">
         <v>0</v>
@@ -2699,27 +2883,36 @@
       <c r="P24" s="1">
         <v>0</v>
       </c>
-      <c r="Q24" s="1"/>
-      <c r="R24" s="1"/>
-      <c r="S24" s="1"/>
-      <c r="T24" s="1">
-        <v>0</v>
-      </c>
-      <c r="U24" s="1">
+      <c r="Q24" s="1">
+        <v>0</v>
+      </c>
+      <c r="R24" s="1">
+        <v>0</v>
+      </c>
+      <c r="S24" s="1">
+        <v>0</v>
+      </c>
+      <c r="T24" s="1"/>
+      <c r="U24" s="1"/>
+      <c r="V24" s="1"/>
+      <c r="W24" s="1">
+        <v>0</v>
+      </c>
+      <c r="X24" s="1">
         <v>100</v>
       </c>
-      <c r="V24" s="1">
-        <v>0</v>
-      </c>
-      <c r="W24" s="1">
-        <v>0</v>
-      </c>
-      <c r="X24" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z24" s="1"/>
-    </row>
-    <row r="25" s="2" customFormat="1" customHeight="1" spans="3:26">
+      <c r="Y24" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z24" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA24" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC24" s="1"/>
+    </row>
+    <row r="25" s="2" customFormat="1" customHeight="1" spans="3:29">
       <c r="C25" s="1">
         <v>10034</v>
       </c>
@@ -2730,22 +2923,22 @@
         <v>1003</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="I25" s="1">
-        <v>0</v>
-      </c>
-      <c r="J25" s="1">
-        <v>0</v>
-      </c>
-      <c r="K25" s="1">
-        <v>0</v>
+        <v>72</v>
+      </c>
+      <c r="I25" s="6">
+        <v>20</v>
+      </c>
+      <c r="J25" s="6">
+        <v>5</v>
+      </c>
+      <c r="K25" s="6">
+        <v>5</v>
       </c>
       <c r="L25" s="1">
         <v>0</v>
@@ -2762,27 +2955,36 @@
       <c r="P25" s="1">
         <v>0</v>
       </c>
-      <c r="Q25" s="1"/>
-      <c r="R25" s="1"/>
-      <c r="S25" s="1"/>
-      <c r="T25" s="1">
-        <v>0</v>
-      </c>
-      <c r="U25" s="1">
+      <c r="Q25" s="1">
+        <v>0</v>
+      </c>
+      <c r="R25" s="1">
+        <v>0</v>
+      </c>
+      <c r="S25" s="1">
+        <v>0</v>
+      </c>
+      <c r="T25" s="1"/>
+      <c r="U25" s="1"/>
+      <c r="V25" s="1"/>
+      <c r="W25" s="1">
+        <v>0</v>
+      </c>
+      <c r="X25" s="1">
         <v>100</v>
       </c>
-      <c r="V25" s="1">
-        <v>0</v>
-      </c>
-      <c r="W25" s="1">
-        <v>0</v>
-      </c>
-      <c r="X25" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z25" s="1"/>
-    </row>
-    <row r="26" s="2" customFormat="1" customHeight="1" spans="3:26">
+      <c r="Y25" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z25" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA25" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC25" s="1"/>
+    </row>
+    <row r="26" s="2" customFormat="1" customHeight="1" spans="3:29">
       <c r="C26" s="1">
         <v>10044</v>
       </c>
@@ -2793,22 +2995,22 @@
         <v>1004</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="I26" s="1">
-        <v>0</v>
-      </c>
-      <c r="J26" s="1">
-        <v>0</v>
-      </c>
-      <c r="K26" s="1">
-        <v>0</v>
+        <v>72</v>
+      </c>
+      <c r="I26" s="6">
+        <v>20</v>
+      </c>
+      <c r="J26" s="6">
+        <v>5</v>
+      </c>
+      <c r="K26" s="6">
+        <v>5</v>
       </c>
       <c r="L26" s="1">
         <v>0</v>
@@ -2825,27 +3027,36 @@
       <c r="P26" s="1">
         <v>0</v>
       </c>
-      <c r="Q26" s="1"/>
-      <c r="R26" s="1"/>
-      <c r="S26" s="1"/>
-      <c r="T26" s="1">
-        <v>0</v>
-      </c>
-      <c r="U26" s="1">
+      <c r="Q26" s="1">
+        <v>0</v>
+      </c>
+      <c r="R26" s="1">
+        <v>0</v>
+      </c>
+      <c r="S26" s="1">
+        <v>0</v>
+      </c>
+      <c r="T26" s="1"/>
+      <c r="U26" s="1"/>
+      <c r="V26" s="1"/>
+      <c r="W26" s="1">
+        <v>0</v>
+      </c>
+      <c r="X26" s="1">
         <v>100</v>
       </c>
-      <c r="V26" s="1">
-        <v>0</v>
-      </c>
-      <c r="W26" s="1">
-        <v>0</v>
-      </c>
-      <c r="X26" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z26" s="1"/>
-    </row>
-    <row r="27" s="1" customFormat="1" customHeight="1" spans="3:26">
+      <c r="Y26" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z26" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA26" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC26" s="1"/>
+    </row>
+    <row r="27" s="1" customFormat="1" customHeight="1" spans="3:29">
       <c r="C27" s="1">
         <v>10074</v>
       </c>
@@ -2856,22 +3067,22 @@
         <v>1007</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="I27" s="1">
-        <v>0</v>
-      </c>
-      <c r="J27" s="1">
-        <v>0</v>
-      </c>
-      <c r="K27" s="1">
-        <v>0</v>
+        <v>72</v>
+      </c>
+      <c r="I27" s="6">
+        <v>20</v>
+      </c>
+      <c r="J27" s="6">
+        <v>5</v>
+      </c>
+      <c r="K27" s="6">
+        <v>5</v>
       </c>
       <c r="L27" s="1">
         <v>0</v>
@@ -2888,24 +3099,43 @@
       <c r="P27" s="1">
         <v>0</v>
       </c>
-      <c r="T27" s="1">
-        <v>0</v>
-      </c>
-      <c r="U27" s="1">
+      <c r="Q27" s="1">
+        <v>0</v>
+      </c>
+      <c r="R27" s="1">
+        <v>0</v>
+      </c>
+      <c r="S27" s="1">
+        <v>0</v>
+      </c>
+      <c r="W27" s="1">
+        <v>0</v>
+      </c>
+      <c r="X27" s="1">
         <v>100</v>
       </c>
-      <c r="V27" s="1">
-        <v>0</v>
-      </c>
-      <c r="W27" s="1">
-        <v>0</v>
-      </c>
-      <c r="X27" s="1">
-        <v>0</v>
-      </c>
+      <c r="Y27" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z27" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA27" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" customHeight="1" spans="3:29">
+      <c r="I28" s="5"/>
+      <c r="J28" s="5"/>
+      <c r="K28" s="5"/>
     </row>
     <row r="29" s="3" customFormat="1" customHeight="1"/>
-    <row r="31" s="1" customFormat="1" customHeight="1" spans="3:26">
+    <row r="30" customHeight="1" spans="3:29">
+      <c r="I30" s="5"/>
+      <c r="J30" s="5"/>
+      <c r="K30" s="5"/>
+    </row>
+    <row r="31" s="1" customFormat="1" customHeight="1" spans="3:29">
       <c r="C31" s="1">
         <v>20011</v>
       </c>
@@ -2916,22 +3146,22 @@
         <v>2001</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="I31" s="1">
-        <v>0</v>
-      </c>
-      <c r="J31" s="1">
-        <v>0</v>
-      </c>
-      <c r="K31" s="1">
-        <v>0</v>
+        <v>74</v>
+      </c>
+      <c r="I31" s="5">
+        <v>100</v>
+      </c>
+      <c r="J31" s="5">
+        <v>1</v>
+      </c>
+      <c r="K31" s="5">
+        <v>5</v>
       </c>
       <c r="L31" s="1">
         <v>0</v>
@@ -2946,16 +3176,16 @@
         <v>0</v>
       </c>
       <c r="P31" s="1">
-        <v>5</v>
-      </c>
-      <c r="T31" s="1">
-        <v>0</v>
-      </c>
-      <c r="U31" s="1">
-        <v>0</v>
-      </c>
-      <c r="V31" s="1">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="Q31" s="1">
+        <v>0</v>
+      </c>
+      <c r="R31" s="1">
+        <v>0</v>
+      </c>
+      <c r="S31" s="1">
+        <v>5</v>
       </c>
       <c r="W31" s="1">
         <v>0</v>
@@ -2963,8 +3193,17 @@
       <c r="X31" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" s="1" customFormat="1" customHeight="1" spans="3:26">
+      <c r="Y31" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z31" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA31" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" s="1" customFormat="1" customHeight="1" spans="3:29">
       <c r="C32" s="1">
         <v>20021</v>
       </c>
@@ -2975,22 +3214,22 @@
         <v>2002</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="I32" s="1">
-        <v>0</v>
-      </c>
-      <c r="J32" s="1">
-        <v>0</v>
-      </c>
-      <c r="K32" s="1">
-        <v>0</v>
+        <v>61</v>
+      </c>
+      <c r="I32" s="5">
+        <v>100</v>
+      </c>
+      <c r="J32" s="5">
+        <v>1</v>
+      </c>
+      <c r="K32" s="5">
+        <v>5</v>
       </c>
       <c r="L32" s="1">
         <v>0</v>
@@ -3004,29 +3243,38 @@
       <c r="O32" s="1">
         <v>0</v>
       </c>
-      <c r="P32" s="2">
+      <c r="P32" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="1">
+        <v>0</v>
+      </c>
+      <c r="R32" s="1">
+        <v>0</v>
+      </c>
+      <c r="S32" s="2">
         <v>20</v>
       </c>
-      <c r="Q32" s="2"/>
-      <c r="R32" s="2"/>
-      <c r="S32" s="2"/>
-      <c r="T32" s="1">
-        <v>0</v>
-      </c>
-      <c r="U32" s="1">
-        <v>0</v>
-      </c>
-      <c r="V32" s="1">
-        <v>0</v>
-      </c>
+      <c r="T32" s="2"/>
+      <c r="U32" s="2"/>
+      <c r="V32" s="2"/>
       <c r="W32" s="1">
         <v>0</v>
       </c>
       <c r="X32" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" s="1" customFormat="1" customHeight="1" spans="3:26">
+      <c r="Y32" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z32" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA32" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" s="1" customFormat="1" customHeight="1" spans="3:29">
       <c r="C33" s="1">
         <v>20031</v>
       </c>
@@ -3037,22 +3285,22 @@
         <v>2003</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="I33" s="1">
-        <v>0</v>
-      </c>
-      <c r="J33" s="1">
-        <v>0</v>
-      </c>
-      <c r="K33" s="1">
-        <v>0</v>
+        <v>61</v>
+      </c>
+      <c r="I33" s="5">
+        <v>100</v>
+      </c>
+      <c r="J33" s="5">
+        <v>1</v>
+      </c>
+      <c r="K33" s="5">
+        <v>5</v>
       </c>
       <c r="L33" s="1">
         <v>0</v>
@@ -3066,29 +3314,38 @@
       <c r="O33" s="1">
         <v>0</v>
       </c>
-      <c r="P33" s="2">
+      <c r="P33" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q33" s="1">
+        <v>0</v>
+      </c>
+      <c r="R33" s="1">
+        <v>0</v>
+      </c>
+      <c r="S33" s="2">
         <v>20</v>
       </c>
-      <c r="Q33" s="2"/>
-      <c r="R33" s="2"/>
-      <c r="S33" s="2"/>
-      <c r="T33" s="1">
-        <v>0</v>
-      </c>
-      <c r="U33" s="1">
-        <v>0</v>
-      </c>
-      <c r="V33" s="1">
-        <v>0</v>
-      </c>
+      <c r="T33" s="2"/>
+      <c r="U33" s="2"/>
+      <c r="V33" s="2"/>
       <c r="W33" s="1">
         <v>0</v>
       </c>
       <c r="X33" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="34" s="1" customFormat="1" customHeight="1" spans="3:26">
+      <c r="Y33" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z33" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA33" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" s="1" customFormat="1" customHeight="1" spans="3:29">
       <c r="C34" s="1">
         <v>20041</v>
       </c>
@@ -3099,22 +3356,22 @@
         <v>2004</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="I34" s="1">
-        <v>0</v>
-      </c>
-      <c r="J34" s="1">
-        <v>0</v>
-      </c>
-      <c r="K34" s="1">
-        <v>0</v>
+        <v>61</v>
+      </c>
+      <c r="I34" s="5">
+        <v>100</v>
+      </c>
+      <c r="J34" s="5">
+        <v>1</v>
+      </c>
+      <c r="K34" s="5">
+        <v>5</v>
       </c>
       <c r="L34" s="1">
         <v>0</v>
@@ -3128,29 +3385,38 @@
       <c r="O34" s="1">
         <v>0</v>
       </c>
-      <c r="P34" s="2">
+      <c r="P34" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="1">
+        <v>0</v>
+      </c>
+      <c r="R34" s="1">
+        <v>0</v>
+      </c>
+      <c r="S34" s="2">
         <v>20</v>
       </c>
-      <c r="Q34" s="2"/>
-      <c r="R34" s="2"/>
-      <c r="S34" s="2"/>
-      <c r="T34" s="1">
-        <v>0</v>
-      </c>
-      <c r="U34" s="1">
-        <v>0</v>
-      </c>
-      <c r="V34" s="1">
-        <v>0</v>
-      </c>
+      <c r="T34" s="2"/>
+      <c r="U34" s="2"/>
+      <c r="V34" s="2"/>
       <c r="W34" s="1">
         <v>0</v>
       </c>
       <c r="X34" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" s="1" customFormat="1" customHeight="1" spans="3:26">
+      <c r="Y34" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z34" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA34" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" s="1" customFormat="1" customHeight="1" spans="3:29">
       <c r="C35" s="1">
         <v>20051</v>
       </c>
@@ -3161,22 +3427,22 @@
         <v>2005</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="I35" s="1">
-        <v>0</v>
-      </c>
-      <c r="J35" s="1">
-        <v>0</v>
-      </c>
-      <c r="K35" s="1">
-        <v>0</v>
+        <v>61</v>
+      </c>
+      <c r="I35" s="5">
+        <v>100</v>
+      </c>
+      <c r="J35" s="5">
+        <v>1</v>
+      </c>
+      <c r="K35" s="5">
+        <v>5</v>
       </c>
       <c r="L35" s="1">
         <v>0</v>
@@ -3190,29 +3456,38 @@
       <c r="O35" s="1">
         <v>0</v>
       </c>
-      <c r="P35" s="2">
-        <v>5</v>
-      </c>
-      <c r="Q35" s="2"/>
-      <c r="R35" s="2"/>
-      <c r="S35" s="2"/>
-      <c r="T35" s="1">
-        <v>0</v>
-      </c>
-      <c r="U35" s="1">
-        <v>0</v>
-      </c>
-      <c r="V35" s="1">
-        <v>0</v>
-      </c>
+      <c r="P35" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q35" s="1">
+        <v>0</v>
+      </c>
+      <c r="R35" s="1">
+        <v>0</v>
+      </c>
+      <c r="S35" s="2">
+        <v>5</v>
+      </c>
+      <c r="T35" s="2"/>
+      <c r="U35" s="2"/>
+      <c r="V35" s="2"/>
       <c r="W35" s="1">
         <v>0</v>
       </c>
       <c r="X35" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="36" s="1" customFormat="1" customHeight="1" spans="3:26">
+      <c r="Y35" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z35" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA35" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" s="1" customFormat="1" customHeight="1" spans="3:29">
       <c r="C36" s="1">
         <v>20061</v>
       </c>
@@ -3223,22 +3498,22 @@
         <v>2006</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="I36" s="1">
-        <v>0</v>
-      </c>
-      <c r="J36" s="1">
-        <v>0</v>
-      </c>
-      <c r="K36" s="1">
-        <v>0</v>
+        <v>61</v>
+      </c>
+      <c r="I36" s="5">
+        <v>100</v>
+      </c>
+      <c r="J36" s="5">
+        <v>1</v>
+      </c>
+      <c r="K36" s="5">
+        <v>5</v>
       </c>
       <c r="L36" s="1">
         <v>0</v>
@@ -3252,29 +3527,38 @@
       <c r="O36" s="1">
         <v>0</v>
       </c>
-      <c r="P36" s="2">
-        <v>5</v>
-      </c>
-      <c r="Q36" s="2"/>
-      <c r="R36" s="2"/>
-      <c r="S36" s="2"/>
-      <c r="T36" s="1">
-        <v>0</v>
-      </c>
-      <c r="U36" s="1">
-        <v>0</v>
-      </c>
-      <c r="V36" s="1">
-        <v>0</v>
-      </c>
+      <c r="P36" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q36" s="1">
+        <v>0</v>
+      </c>
+      <c r="R36" s="1">
+        <v>0</v>
+      </c>
+      <c r="S36" s="2">
+        <v>5</v>
+      </c>
+      <c r="T36" s="2"/>
+      <c r="U36" s="2"/>
+      <c r="V36" s="2"/>
       <c r="W36" s="1">
         <v>0</v>
       </c>
       <c r="X36" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="37" s="1" customFormat="1" customHeight="1" spans="3:26">
+      <c r="Y36" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z36" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA36" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" s="1" customFormat="1" customHeight="1" spans="3:29">
       <c r="C37" s="1">
         <v>20071</v>
       </c>
@@ -3285,22 +3569,22 @@
         <v>2007</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="I37" s="1">
-        <v>0</v>
-      </c>
-      <c r="J37" s="1">
-        <v>0</v>
-      </c>
-      <c r="K37" s="1">
-        <v>0</v>
+        <v>61</v>
+      </c>
+      <c r="I37" s="5">
+        <v>100</v>
+      </c>
+      <c r="J37" s="5">
+        <v>1</v>
+      </c>
+      <c r="K37" s="5">
+        <v>5</v>
       </c>
       <c r="L37" s="1">
         <v>0</v>
@@ -3314,33 +3598,45 @@
       <c r="O37" s="1">
         <v>0</v>
       </c>
-      <c r="P37" s="2">
+      <c r="P37" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q37" s="1">
+        <v>0</v>
+      </c>
+      <c r="R37" s="1">
+        <v>0</v>
+      </c>
+      <c r="S37" s="2">
         <v>20</v>
       </c>
-      <c r="Q37" s="2"/>
-      <c r="R37" s="2"/>
-      <c r="S37" s="2"/>
-      <c r="T37" s="1">
-        <v>0</v>
-      </c>
-      <c r="U37" s="1">
-        <v>0</v>
-      </c>
-      <c r="V37" s="1">
-        <v>0</v>
-      </c>
+      <c r="T37" s="2"/>
+      <c r="U37" s="2"/>
+      <c r="V37" s="2"/>
       <c r="W37" s="1">
         <v>0</v>
       </c>
       <c r="X37" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="38" s="1" customFormat="1" customHeight="1" spans="3:26">
+      <c r="Y37" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z37" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA37" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" s="1" customFormat="1" customHeight="1" spans="3:29">
       <c r="F38" s="2"/>
-      <c r="W38" s="2"/>
-    </row>
-    <row r="39" s="1" customFormat="1" customHeight="1" spans="3:26">
+      <c r="I38" s="5"/>
+      <c r="J38" s="5"/>
+      <c r="K38" s="5"/>
+      <c r="Z38" s="2"/>
+    </row>
+    <row r="39" s="1" customFormat="1" customHeight="1" spans="3:29">
       <c r="C39" s="1">
         <v>20022</v>
       </c>
@@ -3351,22 +3647,22 @@
         <v>2002</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="I39" s="1">
-        <v>0</v>
-      </c>
-      <c r="J39" s="1">
-        <v>0</v>
-      </c>
-      <c r="K39" s="1">
-        <v>0</v>
+        <v>68</v>
+      </c>
+      <c r="I39" s="5">
+        <v>40</v>
+      </c>
+      <c r="J39" s="5">
+        <v>4</v>
+      </c>
+      <c r="K39" s="5">
+        <v>5</v>
       </c>
       <c r="L39" s="1">
         <v>0</v>
@@ -3383,23 +3679,32 @@
       <c r="P39" s="1">
         <v>0</v>
       </c>
-      <c r="T39" s="1">
-        <v>0</v>
-      </c>
-      <c r="U39" s="1">
-        <v>0</v>
-      </c>
-      <c r="V39" s="1">
-        <v>0</v>
-      </c>
-      <c r="W39" s="2">
+      <c r="Q39" s="1">
+        <v>0</v>
+      </c>
+      <c r="R39" s="1">
+        <v>0</v>
+      </c>
+      <c r="S39" s="1">
+        <v>0</v>
+      </c>
+      <c r="W39" s="1">
+        <v>0</v>
+      </c>
+      <c r="X39" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y39" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z39" s="2">
         <v>20</v>
       </c>
-      <c r="X39" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" s="1" customFormat="1" customHeight="1" spans="3:26">
+      <c r="AA39" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" s="1" customFormat="1" customHeight="1" spans="3:29">
       <c r="C40" s="1">
         <v>20032</v>
       </c>
@@ -3410,22 +3715,22 @@
         <v>2003</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="I40" s="1">
-        <v>0</v>
-      </c>
-      <c r="J40" s="1">
-        <v>0</v>
-      </c>
-      <c r="K40" s="1">
-        <v>0</v>
+        <v>68</v>
+      </c>
+      <c r="I40" s="5">
+        <v>40</v>
+      </c>
+      <c r="J40" s="5">
+        <v>4</v>
+      </c>
+      <c r="K40" s="5">
+        <v>5</v>
       </c>
       <c r="L40" s="1">
         <v>0</v>
@@ -3442,23 +3747,32 @@
       <c r="P40" s="1">
         <v>0</v>
       </c>
-      <c r="T40" s="1">
-        <v>0</v>
-      </c>
-      <c r="U40" s="1">
-        <v>0</v>
-      </c>
-      <c r="V40" s="1">
-        <v>0</v>
-      </c>
-      <c r="W40" s="2">
+      <c r="Q40" s="1">
+        <v>0</v>
+      </c>
+      <c r="R40" s="1">
+        <v>0</v>
+      </c>
+      <c r="S40" s="1">
+        <v>0</v>
+      </c>
+      <c r="W40" s="1">
+        <v>0</v>
+      </c>
+      <c r="X40" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y40" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z40" s="2">
         <v>20</v>
       </c>
-      <c r="X40" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" s="1" customFormat="1" customHeight="1" spans="3:26">
+      <c r="AA40" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" s="1" customFormat="1" customHeight="1" spans="3:29">
       <c r="C41" s="1">
         <v>20042</v>
       </c>
@@ -3469,22 +3783,22 @@
         <v>2004</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="I41" s="1">
-        <v>0</v>
-      </c>
-      <c r="J41" s="1">
-        <v>0</v>
-      </c>
-      <c r="K41" s="1">
-        <v>0</v>
+        <v>68</v>
+      </c>
+      <c r="I41" s="5">
+        <v>40</v>
+      </c>
+      <c r="J41" s="5">
+        <v>4</v>
+      </c>
+      <c r="K41" s="5">
+        <v>5</v>
       </c>
       <c r="L41" s="1">
         <v>0</v>
@@ -3501,23 +3815,32 @@
       <c r="P41" s="1">
         <v>0</v>
       </c>
-      <c r="T41" s="1">
-        <v>0</v>
-      </c>
-      <c r="U41" s="1">
-        <v>0</v>
-      </c>
-      <c r="V41" s="1">
-        <v>0</v>
-      </c>
-      <c r="W41" s="2">
+      <c r="Q41" s="1">
+        <v>0</v>
+      </c>
+      <c r="R41" s="1">
+        <v>0</v>
+      </c>
+      <c r="S41" s="1">
+        <v>0</v>
+      </c>
+      <c r="W41" s="1">
+        <v>0</v>
+      </c>
+      <c r="X41" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y41" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z41" s="2">
         <v>20</v>
       </c>
-      <c r="X41" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" s="1" customFormat="1" customHeight="1" spans="3:26">
+      <c r="AA41" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" s="1" customFormat="1" customHeight="1" spans="3:29">
       <c r="C42" s="1">
         <v>20072</v>
       </c>
@@ -3528,22 +3851,22 @@
         <v>2007</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="I42" s="1">
-        <v>0</v>
-      </c>
-      <c r="J42" s="1">
-        <v>0</v>
-      </c>
-      <c r="K42" s="1">
-        <v>0</v>
+        <v>68</v>
+      </c>
+      <c r="I42" s="5">
+        <v>40</v>
+      </c>
+      <c r="J42" s="5">
+        <v>4</v>
+      </c>
+      <c r="K42" s="5">
+        <v>5</v>
       </c>
       <c r="L42" s="1">
         <v>0</v>
@@ -3560,31 +3883,43 @@
       <c r="P42" s="1">
         <v>0</v>
       </c>
-      <c r="T42" s="1">
-        <v>0</v>
-      </c>
-      <c r="U42" s="1">
-        <v>0</v>
-      </c>
-      <c r="V42" s="1">
-        <v>0</v>
-      </c>
-      <c r="W42" s="2">
+      <c r="Q42" s="1">
+        <v>0</v>
+      </c>
+      <c r="R42" s="1">
+        <v>0</v>
+      </c>
+      <c r="S42" s="1">
+        <v>0</v>
+      </c>
+      <c r="W42" s="1">
+        <v>0</v>
+      </c>
+      <c r="X42" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y42" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z42" s="2">
         <v>20</v>
       </c>
-      <c r="X42" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" s="1" customFormat="1" customHeight="1" spans="3:26">
+      <c r="AA42" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" s="1" customFormat="1" customHeight="1" spans="3:29">
       <c r="E43" s="2"/>
       <c r="F43" s="2"/>
-      <c r="P43" s="2"/>
-      <c r="Q43" s="2"/>
-      <c r="R43" s="2"/>
+      <c r="I43" s="5"/>
+      <c r="J43" s="5"/>
+      <c r="K43" s="5"/>
       <c r="S43" s="2"/>
-    </row>
-    <row r="44" s="2" customFormat="1" customHeight="1" spans="3:26">
+      <c r="T43" s="2"/>
+      <c r="U43" s="2"/>
+      <c r="V43" s="2"/>
+    </row>
+    <row r="44" s="2" customFormat="1" customHeight="1" spans="3:29">
       <c r="C44" s="1">
         <v>20023</v>
       </c>
@@ -3595,22 +3930,22 @@
         <v>2002</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="I44" s="1">
-        <v>0</v>
-      </c>
-      <c r="J44" s="1">
-        <v>0</v>
-      </c>
-      <c r="K44" s="1">
-        <v>0</v>
+        <v>70</v>
+      </c>
+      <c r="I44" s="5">
+        <v>60</v>
+      </c>
+      <c r="J44" s="5">
+        <v>4</v>
+      </c>
+      <c r="K44" s="5">
+        <v>5</v>
       </c>
       <c r="L44" s="1">
         <v>0</v>
@@ -3627,27 +3962,36 @@
       <c r="P44" s="1">
         <v>0</v>
       </c>
-      <c r="Q44" s="1"/>
-      <c r="R44" s="1"/>
-      <c r="S44" s="1"/>
-      <c r="T44" s="1">
-        <v>0</v>
-      </c>
-      <c r="U44" s="1">
-        <v>0</v>
-      </c>
-      <c r="V44" s="1">
-        <v>0</v>
-      </c>
+      <c r="Q44" s="1">
+        <v>0</v>
+      </c>
+      <c r="R44" s="1">
+        <v>0</v>
+      </c>
+      <c r="S44" s="1">
+        <v>0</v>
+      </c>
+      <c r="T44" s="1"/>
+      <c r="U44" s="1"/>
+      <c r="V44" s="1"/>
       <c r="W44" s="1">
         <v>0</v>
       </c>
-      <c r="X44" s="2">
+      <c r="X44" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y44" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z44" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA44" s="2">
         <v>20</v>
       </c>
-      <c r="Z44" s="1"/>
-    </row>
-    <row r="45" s="2" customFormat="1" customHeight="1" spans="3:26">
+      <c r="AC44" s="1"/>
+    </row>
+    <row r="45" s="2" customFormat="1" customHeight="1" spans="3:29">
       <c r="C45" s="1">
         <v>20033</v>
       </c>
@@ -3658,22 +4002,22 @@
         <v>2003</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="I45" s="1">
-        <v>0</v>
-      </c>
-      <c r="J45" s="1">
-        <v>0</v>
-      </c>
-      <c r="K45" s="1">
-        <v>0</v>
+        <v>70</v>
+      </c>
+      <c r="I45" s="5">
+        <v>60</v>
+      </c>
+      <c r="J45" s="5">
+        <v>4</v>
+      </c>
+      <c r="K45" s="5">
+        <v>5</v>
       </c>
       <c r="L45" s="1">
         <v>0</v>
@@ -3690,27 +4034,36 @@
       <c r="P45" s="1">
         <v>0</v>
       </c>
-      <c r="Q45" s="1"/>
-      <c r="R45" s="1"/>
-      <c r="S45" s="1"/>
-      <c r="T45" s="1">
-        <v>0</v>
-      </c>
-      <c r="U45" s="1">
-        <v>0</v>
-      </c>
-      <c r="V45" s="1">
-        <v>0</v>
-      </c>
+      <c r="Q45" s="1">
+        <v>0</v>
+      </c>
+      <c r="R45" s="1">
+        <v>0</v>
+      </c>
+      <c r="S45" s="1">
+        <v>0</v>
+      </c>
+      <c r="T45" s="1"/>
+      <c r="U45" s="1"/>
+      <c r="V45" s="1"/>
       <c r="W45" s="1">
         <v>0</v>
       </c>
-      <c r="X45" s="2">
+      <c r="X45" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y45" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z45" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA45" s="2">
         <v>20</v>
       </c>
-      <c r="Z45" s="1"/>
-    </row>
-    <row r="46" s="2" customFormat="1" customHeight="1" spans="3:26">
+      <c r="AC45" s="1"/>
+    </row>
+    <row r="46" s="2" customFormat="1" customHeight="1" spans="3:29">
       <c r="C46" s="1">
         <v>20043</v>
       </c>
@@ -3721,22 +4074,22 @@
         <v>2004</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="I46" s="1">
-        <v>0</v>
-      </c>
-      <c r="J46" s="1">
-        <v>0</v>
-      </c>
-      <c r="K46" s="1">
-        <v>0</v>
+        <v>70</v>
+      </c>
+      <c r="I46" s="5">
+        <v>60</v>
+      </c>
+      <c r="J46" s="5">
+        <v>4</v>
+      </c>
+      <c r="K46" s="5">
+        <v>5</v>
       </c>
       <c r="L46" s="1">
         <v>0</v>
@@ -3753,27 +4106,36 @@
       <c r="P46" s="1">
         <v>0</v>
       </c>
-      <c r="Q46" s="1"/>
-      <c r="R46" s="1"/>
-      <c r="S46" s="1"/>
-      <c r="T46" s="1">
-        <v>0</v>
-      </c>
-      <c r="U46" s="1">
-        <v>0</v>
-      </c>
-      <c r="V46" s="1">
-        <v>0</v>
-      </c>
+      <c r="Q46" s="1">
+        <v>0</v>
+      </c>
+      <c r="R46" s="1">
+        <v>0</v>
+      </c>
+      <c r="S46" s="1">
+        <v>0</v>
+      </c>
+      <c r="T46" s="1"/>
+      <c r="U46" s="1"/>
+      <c r="V46" s="1"/>
       <c r="W46" s="1">
         <v>0</v>
       </c>
-      <c r="X46" s="2">
+      <c r="X46" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y46" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z46" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA46" s="2">
         <v>20</v>
       </c>
-      <c r="Z46" s="1"/>
-    </row>
-    <row r="47" s="2" customFormat="1" customHeight="1" spans="3:26">
+      <c r="AC46" s="1"/>
+    </row>
+    <row r="47" s="2" customFormat="1" customHeight="1" spans="3:29">
       <c r="C47" s="1">
         <v>20073</v>
       </c>
@@ -3784,22 +4146,22 @@
         <v>2007</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="I47" s="1">
-        <v>0</v>
-      </c>
-      <c r="J47" s="1">
-        <v>0</v>
-      </c>
-      <c r="K47" s="1">
-        <v>0</v>
+        <v>70</v>
+      </c>
+      <c r="I47" s="5">
+        <v>60</v>
+      </c>
+      <c r="J47" s="5">
+        <v>4</v>
+      </c>
+      <c r="K47" s="5">
+        <v>5</v>
       </c>
       <c r="L47" s="1">
         <v>0</v>
@@ -3816,34 +4178,43 @@
       <c r="P47" s="1">
         <v>0</v>
       </c>
-      <c r="Q47" s="1"/>
-      <c r="R47" s="1"/>
-      <c r="S47" s="1"/>
-      <c r="T47" s="1">
-        <v>0</v>
-      </c>
-      <c r="U47" s="1">
-        <v>0</v>
-      </c>
-      <c r="V47" s="1">
-        <v>0</v>
-      </c>
+      <c r="Q47" s="1">
+        <v>0</v>
+      </c>
+      <c r="R47" s="1">
+        <v>0</v>
+      </c>
+      <c r="S47" s="1">
+        <v>0</v>
+      </c>
+      <c r="T47" s="1"/>
+      <c r="U47" s="1"/>
+      <c r="V47" s="1"/>
       <c r="W47" s="1">
         <v>0</v>
       </c>
-      <c r="X47" s="2">
+      <c r="X47" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y47" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z47" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA47" s="2">
         <v>20</v>
       </c>
-      <c r="Z47" s="1"/>
-    </row>
-    <row r="48" s="2" customFormat="1" customHeight="1" spans="3:26">
+      <c r="AC47" s="1"/>
+    </row>
+    <row r="48" s="2" customFormat="1" customHeight="1" spans="3:29">
       <c r="C48" s="1"/>
       <c r="D48" s="1"/>
       <c r="G48" s="1"/>
       <c r="H48" s="1"/>
-      <c r="I48" s="1"/>
-      <c r="J48" s="1"/>
-      <c r="K48" s="1"/>
+      <c r="I48" s="5"/>
+      <c r="J48" s="5"/>
+      <c r="K48" s="5"/>
       <c r="L48" s="1"/>
       <c r="M48" s="1"/>
       <c r="N48" s="1"/>
@@ -3857,9 +4228,12 @@
       <c r="V48" s="1"/>
       <c r="W48" s="1"/>
       <c r="X48" s="1"/>
+      <c r="Y48" s="1"/>
       <c r="Z48" s="1"/>
-    </row>
-    <row r="49" s="2" customFormat="1" customHeight="1" spans="3:26">
+      <c r="AA48" s="1"/>
+      <c r="AC48" s="1"/>
+    </row>
+    <row r="49" s="2" customFormat="1" customHeight="1" spans="3:29">
       <c r="C49" s="1">
         <v>20024</v>
       </c>
@@ -3870,22 +4244,22 @@
         <v>2002</v>
       </c>
       <c r="F49" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="G49" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="H49" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="G49" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="H49" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="I49" s="1">
-        <v>0</v>
-      </c>
-      <c r="J49" s="1">
-        <v>0</v>
-      </c>
-      <c r="K49" s="1">
-        <v>0</v>
+      <c r="I49" s="6">
+        <v>20</v>
+      </c>
+      <c r="J49" s="6">
+        <v>5</v>
+      </c>
+      <c r="K49" s="6">
+        <v>5</v>
       </c>
       <c r="L49" s="1">
         <v>0</v>
@@ -3902,27 +4276,36 @@
       <c r="P49" s="1">
         <v>0</v>
       </c>
-      <c r="Q49" s="1"/>
-      <c r="R49" s="1"/>
-      <c r="S49" s="1"/>
-      <c r="T49" s="1">
-        <v>0</v>
-      </c>
-      <c r="U49" s="1">
+      <c r="Q49" s="1">
+        <v>0</v>
+      </c>
+      <c r="R49" s="1">
+        <v>0</v>
+      </c>
+      <c r="S49" s="1">
+        <v>0</v>
+      </c>
+      <c r="T49" s="1"/>
+      <c r="U49" s="1"/>
+      <c r="V49" s="1"/>
+      <c r="W49" s="1">
+        <v>0</v>
+      </c>
+      <c r="X49" s="1">
         <v>100</v>
       </c>
-      <c r="V49" s="1">
-        <v>0</v>
-      </c>
-      <c r="W49" s="1">
-        <v>0</v>
-      </c>
-      <c r="X49" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z49" s="1"/>
-    </row>
-    <row r="50" s="2" customFormat="1" customHeight="1" spans="3:26">
+      <c r="Y49" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z49" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA49" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC49" s="1"/>
+    </row>
+    <row r="50" s="2" customFormat="1" customHeight="1" spans="3:29">
       <c r="C50" s="1">
         <v>20034</v>
       </c>
@@ -3933,22 +4316,22 @@
         <v>2003</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="I50" s="1">
-        <v>0</v>
-      </c>
-      <c r="J50" s="1">
-        <v>0</v>
-      </c>
-      <c r="K50" s="1">
-        <v>0</v>
+        <v>72</v>
+      </c>
+      <c r="I50" s="6">
+        <v>20</v>
+      </c>
+      <c r="J50" s="6">
+        <v>5</v>
+      </c>
+      <c r="K50" s="6">
+        <v>5</v>
       </c>
       <c r="L50" s="1">
         <v>0</v>
@@ -3965,27 +4348,36 @@
       <c r="P50" s="1">
         <v>0</v>
       </c>
-      <c r="Q50" s="1"/>
-      <c r="R50" s="1"/>
-      <c r="S50" s="1"/>
-      <c r="T50" s="1">
-        <v>0</v>
-      </c>
-      <c r="U50" s="1">
+      <c r="Q50" s="1">
+        <v>0</v>
+      </c>
+      <c r="R50" s="1">
+        <v>0</v>
+      </c>
+      <c r="S50" s="1">
+        <v>0</v>
+      </c>
+      <c r="T50" s="1"/>
+      <c r="U50" s="1"/>
+      <c r="V50" s="1"/>
+      <c r="W50" s="1">
+        <v>0</v>
+      </c>
+      <c r="X50" s="1">
         <v>100</v>
       </c>
-      <c r="V50" s="1">
-        <v>0</v>
-      </c>
-      <c r="W50" s="1">
-        <v>0</v>
-      </c>
-      <c r="X50" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z50" s="1"/>
-    </row>
-    <row r="51" s="2" customFormat="1" customHeight="1" spans="3:26">
+      <c r="Y50" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z50" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA50" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC50" s="1"/>
+    </row>
+    <row r="51" s="2" customFormat="1" customHeight="1" spans="3:29">
       <c r="C51" s="1">
         <v>20044</v>
       </c>
@@ -3996,22 +4388,22 @@
         <v>2004</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="I51" s="1">
-        <v>0</v>
-      </c>
-      <c r="J51" s="1">
-        <v>0</v>
-      </c>
-      <c r="K51" s="1">
-        <v>0</v>
+        <v>72</v>
+      </c>
+      <c r="I51" s="6">
+        <v>20</v>
+      </c>
+      <c r="J51" s="6">
+        <v>5</v>
+      </c>
+      <c r="K51" s="6">
+        <v>5</v>
       </c>
       <c r="L51" s="1">
         <v>0</v>
@@ -4028,27 +4420,36 @@
       <c r="P51" s="1">
         <v>0</v>
       </c>
-      <c r="Q51" s="1"/>
-      <c r="R51" s="1"/>
-      <c r="S51" s="1"/>
-      <c r="T51" s="1">
-        <v>0</v>
-      </c>
-      <c r="U51" s="1">
+      <c r="Q51" s="1">
+        <v>0</v>
+      </c>
+      <c r="R51" s="1">
+        <v>0</v>
+      </c>
+      <c r="S51" s="1">
+        <v>0</v>
+      </c>
+      <c r="T51" s="1"/>
+      <c r="U51" s="1"/>
+      <c r="V51" s="1"/>
+      <c r="W51" s="1">
+        <v>0</v>
+      </c>
+      <c r="X51" s="1">
         <v>100</v>
       </c>
-      <c r="V51" s="1">
-        <v>0</v>
-      </c>
-      <c r="W51" s="1">
-        <v>0</v>
-      </c>
-      <c r="X51" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z51" s="1"/>
-    </row>
-    <row r="52" s="1" customFormat="1" customHeight="1" spans="3:26">
+      <c r="Y51" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z51" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA51" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC51" s="1"/>
+    </row>
+    <row r="52" s="1" customFormat="1" customHeight="1" spans="3:29">
       <c r="C52" s="1">
         <v>20074</v>
       </c>
@@ -4059,22 +4460,22 @@
         <v>2007</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="I52" s="1">
-        <v>0</v>
-      </c>
-      <c r="J52" s="1">
-        <v>0</v>
-      </c>
-      <c r="K52" s="1">
-        <v>0</v>
+        <v>72</v>
+      </c>
+      <c r="I52" s="6">
+        <v>20</v>
+      </c>
+      <c r="J52" s="6">
+        <v>5</v>
+      </c>
+      <c r="K52" s="6">
+        <v>5</v>
       </c>
       <c r="L52" s="1">
         <v>0</v>
@@ -4091,24 +4492,43 @@
       <c r="P52" s="1">
         <v>0</v>
       </c>
-      <c r="T52" s="1">
-        <v>0</v>
-      </c>
-      <c r="U52" s="1">
+      <c r="Q52" s="1">
+        <v>0</v>
+      </c>
+      <c r="R52" s="1">
+        <v>0</v>
+      </c>
+      <c r="S52" s="1">
+        <v>0</v>
+      </c>
+      <c r="W52" s="1">
+        <v>0</v>
+      </c>
+      <c r="X52" s="1">
         <v>100</v>
       </c>
-      <c r="V52" s="1">
-        <v>0</v>
-      </c>
-      <c r="W52" s="1">
-        <v>0</v>
-      </c>
-      <c r="X52" s="1">
-        <v>0</v>
-      </c>
+      <c r="Y52" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z52" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA52" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" customHeight="1" spans="3:29">
+      <c r="I53" s="5"/>
+      <c r="J53" s="5"/>
+      <c r="K53" s="5"/>
     </row>
     <row r="54" s="3" customFormat="1" customHeight="1"/>
-    <row r="56" s="1" customFormat="1" customHeight="1" spans="3:26">
+    <row r="55" customHeight="1" spans="3:29">
+      <c r="I55" s="5"/>
+      <c r="J55" s="5"/>
+      <c r="K55" s="5"/>
+    </row>
+    <row r="56" s="1" customFormat="1" customHeight="1" spans="3:29">
       <c r="C56" s="1">
         <v>30011</v>
       </c>
@@ -4119,22 +4539,22 @@
         <v>3001</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="I56" s="1">
-        <v>0</v>
-      </c>
-      <c r="J56" s="1">
-        <v>0</v>
-      </c>
-      <c r="K56" s="1">
-        <v>0</v>
+        <v>82</v>
+      </c>
+      <c r="I56" s="5">
+        <v>100</v>
+      </c>
+      <c r="J56" s="5">
+        <v>1</v>
+      </c>
+      <c r="K56" s="5">
+        <v>5</v>
       </c>
       <c r="L56" s="1">
         <v>0</v>
@@ -4149,16 +4569,16 @@
         <v>0</v>
       </c>
       <c r="P56" s="1">
-        <v>5</v>
-      </c>
-      <c r="T56" s="1">
-        <v>0</v>
-      </c>
-      <c r="U56" s="1">
-        <v>0</v>
-      </c>
-      <c r="V56" s="1">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="Q56" s="1">
+        <v>0</v>
+      </c>
+      <c r="R56" s="1">
+        <v>0</v>
+      </c>
+      <c r="S56" s="1">
+        <v>5</v>
       </c>
       <c r="W56" s="1">
         <v>0</v>
@@ -4166,8 +4586,17 @@
       <c r="X56" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="57" s="1" customFormat="1" customHeight="1" spans="3:26">
+      <c r="Y56" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z56" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA56" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" s="1" customFormat="1" customHeight="1" spans="3:29">
       <c r="C57" s="1">
         <v>30021</v>
       </c>
@@ -4178,22 +4607,22 @@
         <v>3002</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="I57" s="1">
-        <v>0</v>
-      </c>
-      <c r="J57" s="1">
-        <v>0</v>
-      </c>
-      <c r="K57" s="1">
-        <v>0</v>
+        <v>61</v>
+      </c>
+      <c r="I57" s="5">
+        <v>100</v>
+      </c>
+      <c r="J57" s="5">
+        <v>1</v>
+      </c>
+      <c r="K57" s="5">
+        <v>5</v>
       </c>
       <c r="L57" s="1">
         <v>0</v>
@@ -4207,29 +4636,38 @@
       <c r="O57" s="1">
         <v>0</v>
       </c>
-      <c r="P57" s="2">
+      <c r="P57" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q57" s="1">
+        <v>0</v>
+      </c>
+      <c r="R57" s="1">
+        <v>0</v>
+      </c>
+      <c r="S57" s="2">
         <v>20</v>
       </c>
-      <c r="Q57" s="2"/>
-      <c r="R57" s="2"/>
-      <c r="S57" s="2"/>
-      <c r="T57" s="1">
-        <v>0</v>
-      </c>
-      <c r="U57" s="1">
-        <v>0</v>
-      </c>
-      <c r="V57" s="1">
-        <v>0</v>
-      </c>
+      <c r="T57" s="2"/>
+      <c r="U57" s="2"/>
+      <c r="V57" s="2"/>
       <c r="W57" s="1">
         <v>0</v>
       </c>
       <c r="X57" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" s="1" customFormat="1" customHeight="1" spans="3:26">
+      <c r="Y57" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z57" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA57" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" s="1" customFormat="1" customHeight="1" spans="3:29">
       <c r="C58" s="1">
         <v>30031</v>
       </c>
@@ -4240,22 +4678,22 @@
         <v>3003</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="I58" s="1">
-        <v>0</v>
-      </c>
-      <c r="J58" s="1">
-        <v>0</v>
-      </c>
-      <c r="K58" s="1">
-        <v>0</v>
+        <v>61</v>
+      </c>
+      <c r="I58" s="5">
+        <v>100</v>
+      </c>
+      <c r="J58" s="5">
+        <v>1</v>
+      </c>
+      <c r="K58" s="5">
+        <v>5</v>
       </c>
       <c r="L58" s="1">
         <v>0</v>
@@ -4269,29 +4707,38 @@
       <c r="O58" s="1">
         <v>0</v>
       </c>
-      <c r="P58" s="2">
+      <c r="P58" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q58" s="1">
+        <v>0</v>
+      </c>
+      <c r="R58" s="1">
+        <v>0</v>
+      </c>
+      <c r="S58" s="2">
         <v>20</v>
       </c>
-      <c r="Q58" s="2"/>
-      <c r="R58" s="2"/>
-      <c r="S58" s="2"/>
-      <c r="T58" s="1">
-        <v>0</v>
-      </c>
-      <c r="U58" s="1">
-        <v>0</v>
-      </c>
-      <c r="V58" s="1">
-        <v>0</v>
-      </c>
+      <c r="T58" s="2"/>
+      <c r="U58" s="2"/>
+      <c r="V58" s="2"/>
       <c r="W58" s="1">
         <v>0</v>
       </c>
       <c r="X58" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" s="1" customFormat="1" customHeight="1" spans="3:26">
+      <c r="Y58" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z58" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA58" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" s="1" customFormat="1" customHeight="1" spans="3:29">
       <c r="C59" s="1">
         <v>30041</v>
       </c>
@@ -4302,22 +4749,22 @@
         <v>3004</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="I59" s="1">
-        <v>0</v>
-      </c>
-      <c r="J59" s="1">
-        <v>0</v>
-      </c>
-      <c r="K59" s="1">
-        <v>0</v>
+        <v>61</v>
+      </c>
+      <c r="I59" s="5">
+        <v>100</v>
+      </c>
+      <c r="J59" s="5">
+        <v>1</v>
+      </c>
+      <c r="K59" s="5">
+        <v>5</v>
       </c>
       <c r="L59" s="1">
         <v>0</v>
@@ -4331,29 +4778,38 @@
       <c r="O59" s="1">
         <v>0</v>
       </c>
-      <c r="P59" s="2">
+      <c r="P59" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q59" s="1">
+        <v>0</v>
+      </c>
+      <c r="R59" s="1">
+        <v>0</v>
+      </c>
+      <c r="S59" s="2">
         <v>20</v>
       </c>
-      <c r="Q59" s="2"/>
-      <c r="R59" s="2"/>
-      <c r="S59" s="2"/>
-      <c r="T59" s="1">
-        <v>0</v>
-      </c>
-      <c r="U59" s="1">
-        <v>0</v>
-      </c>
-      <c r="V59" s="1">
-        <v>0</v>
-      </c>
+      <c r="T59" s="2"/>
+      <c r="U59" s="2"/>
+      <c r="V59" s="2"/>
       <c r="W59" s="1">
         <v>0</v>
       </c>
       <c r="X59" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="60" s="1" customFormat="1" customHeight="1" spans="3:26">
+      <c r="Y59" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z59" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA59" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" s="1" customFormat="1" customHeight="1" spans="3:29">
       <c r="C60" s="1">
         <v>30051</v>
       </c>
@@ -4364,22 +4820,22 @@
         <v>3005</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="I60" s="1">
-        <v>0</v>
-      </c>
-      <c r="J60" s="1">
-        <v>0</v>
-      </c>
-      <c r="K60" s="1">
-        <v>0</v>
+        <v>61</v>
+      </c>
+      <c r="I60" s="5">
+        <v>100</v>
+      </c>
+      <c r="J60" s="5">
+        <v>1</v>
+      </c>
+      <c r="K60" s="5">
+        <v>5</v>
       </c>
       <c r="L60" s="1">
         <v>0</v>
@@ -4393,29 +4849,38 @@
       <c r="O60" s="1">
         <v>0</v>
       </c>
-      <c r="P60" s="2">
-        <v>5</v>
-      </c>
-      <c r="Q60" s="2"/>
-      <c r="R60" s="2"/>
-      <c r="S60" s="2"/>
-      <c r="T60" s="1">
-        <v>0</v>
-      </c>
-      <c r="U60" s="1">
-        <v>0</v>
-      </c>
-      <c r="V60" s="1">
-        <v>0</v>
-      </c>
+      <c r="P60" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q60" s="1">
+        <v>0</v>
+      </c>
+      <c r="R60" s="1">
+        <v>0</v>
+      </c>
+      <c r="S60" s="2">
+        <v>5</v>
+      </c>
+      <c r="T60" s="2"/>
+      <c r="U60" s="2"/>
+      <c r="V60" s="2"/>
       <c r="W60" s="1">
         <v>0</v>
       </c>
       <c r="X60" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" s="1" customFormat="1" customHeight="1" spans="3:26">
+      <c r="Y60" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z60" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA60" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" s="1" customFormat="1" customHeight="1" spans="3:29">
       <c r="C61" s="1">
         <v>30061</v>
       </c>
@@ -4426,22 +4891,22 @@
         <v>3006</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="I61" s="1">
-        <v>0</v>
-      </c>
-      <c r="J61" s="1">
-        <v>0</v>
-      </c>
-      <c r="K61" s="1">
-        <v>0</v>
+        <v>61</v>
+      </c>
+      <c r="I61" s="5">
+        <v>100</v>
+      </c>
+      <c r="J61" s="5">
+        <v>1</v>
+      </c>
+      <c r="K61" s="5">
+        <v>5</v>
       </c>
       <c r="L61" s="1">
         <v>0</v>
@@ -4455,29 +4920,38 @@
       <c r="O61" s="1">
         <v>0</v>
       </c>
-      <c r="P61" s="2">
-        <v>5</v>
-      </c>
-      <c r="Q61" s="2"/>
-      <c r="R61" s="2"/>
-      <c r="S61" s="2"/>
-      <c r="T61" s="1">
-        <v>0</v>
-      </c>
-      <c r="U61" s="1">
-        <v>0</v>
-      </c>
-      <c r="V61" s="1">
-        <v>0</v>
-      </c>
+      <c r="P61" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="1">
+        <v>0</v>
+      </c>
+      <c r="R61" s="1">
+        <v>0</v>
+      </c>
+      <c r="S61" s="2">
+        <v>5</v>
+      </c>
+      <c r="T61" s="2"/>
+      <c r="U61" s="2"/>
+      <c r="V61" s="2"/>
       <c r="W61" s="1">
         <v>0</v>
       </c>
       <c r="X61" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" s="1" customFormat="1" customHeight="1" spans="3:26">
+      <c r="Y61" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z61" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA61" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" s="1" customFormat="1" customHeight="1" spans="3:29">
       <c r="C62" s="1">
         <v>30071</v>
       </c>
@@ -4488,22 +4962,22 @@
         <v>3007</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="I62" s="1">
-        <v>0</v>
-      </c>
-      <c r="J62" s="1">
-        <v>0</v>
-      </c>
-      <c r="K62" s="1">
-        <v>0</v>
+        <v>61</v>
+      </c>
+      <c r="I62" s="5">
+        <v>100</v>
+      </c>
+      <c r="J62" s="5">
+        <v>1</v>
+      </c>
+      <c r="K62" s="5">
+        <v>5</v>
       </c>
       <c r="L62" s="1">
         <v>0</v>
@@ -4517,33 +4991,45 @@
       <c r="O62" s="1">
         <v>0</v>
       </c>
-      <c r="P62" s="2">
+      <c r="P62" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q62" s="1">
+        <v>0</v>
+      </c>
+      <c r="R62" s="1">
+        <v>0</v>
+      </c>
+      <c r="S62" s="2">
         <v>20</v>
       </c>
-      <c r="Q62" s="2"/>
-      <c r="R62" s="2"/>
-      <c r="S62" s="2"/>
-      <c r="T62" s="1">
-        <v>0</v>
-      </c>
-      <c r="U62" s="1">
-        <v>0</v>
-      </c>
-      <c r="V62" s="1">
-        <v>0</v>
-      </c>
+      <c r="T62" s="2"/>
+      <c r="U62" s="2"/>
+      <c r="V62" s="2"/>
       <c r="W62" s="1">
         <v>0</v>
       </c>
       <c r="X62" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" s="1" customFormat="1" customHeight="1" spans="3:26">
+      <c r="Y62" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z62" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA62" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" s="1" customFormat="1" customHeight="1" spans="3:29">
       <c r="F63" s="2"/>
-      <c r="W63" s="2"/>
-    </row>
-    <row r="64" s="1" customFormat="1" customHeight="1" spans="3:26">
+      <c r="I63" s="5"/>
+      <c r="J63" s="5"/>
+      <c r="K63" s="5"/>
+      <c r="Z63" s="2"/>
+    </row>
+    <row r="64" s="1" customFormat="1" customHeight="1" spans="3:29">
       <c r="C64" s="1">
         <v>30022</v>
       </c>
@@ -4554,22 +5040,22 @@
         <v>3002</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="I64" s="1">
-        <v>0</v>
-      </c>
-      <c r="J64" s="1">
-        <v>0</v>
-      </c>
-      <c r="K64" s="1">
-        <v>0</v>
+        <v>68</v>
+      </c>
+      <c r="I64" s="5">
+        <v>40</v>
+      </c>
+      <c r="J64" s="5">
+        <v>4</v>
+      </c>
+      <c r="K64" s="5">
+        <v>5</v>
       </c>
       <c r="L64" s="1">
         <v>0</v>
@@ -4586,23 +5072,32 @@
       <c r="P64" s="1">
         <v>0</v>
       </c>
-      <c r="T64" s="1">
-        <v>0</v>
-      </c>
-      <c r="U64" s="1">
-        <v>0</v>
-      </c>
-      <c r="V64" s="1">
-        <v>0</v>
-      </c>
-      <c r="W64" s="2">
+      <c r="Q64" s="1">
+        <v>0</v>
+      </c>
+      <c r="R64" s="1">
+        <v>0</v>
+      </c>
+      <c r="S64" s="1">
+        <v>0</v>
+      </c>
+      <c r="W64" s="1">
+        <v>0</v>
+      </c>
+      <c r="X64" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y64" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z64" s="2">
         <v>20</v>
       </c>
-      <c r="X64" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" s="1" customFormat="1" customHeight="1" spans="3:26">
+      <c r="AA64" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" s="1" customFormat="1" customHeight="1" spans="3:29">
       <c r="C65" s="1">
         <v>30032</v>
       </c>
@@ -4613,22 +5108,22 @@
         <v>3003</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="I65" s="1">
-        <v>0</v>
-      </c>
-      <c r="J65" s="1">
-        <v>0</v>
-      </c>
-      <c r="K65" s="1">
-        <v>0</v>
+        <v>68</v>
+      </c>
+      <c r="I65" s="5">
+        <v>40</v>
+      </c>
+      <c r="J65" s="5">
+        <v>4</v>
+      </c>
+      <c r="K65" s="5">
+        <v>5</v>
       </c>
       <c r="L65" s="1">
         <v>0</v>
@@ -4645,23 +5140,32 @@
       <c r="P65" s="1">
         <v>0</v>
       </c>
-      <c r="T65" s="1">
-        <v>0</v>
-      </c>
-      <c r="U65" s="1">
-        <v>0</v>
-      </c>
-      <c r="V65" s="1">
-        <v>0</v>
-      </c>
-      <c r="W65" s="2">
+      <c r="Q65" s="1">
+        <v>0</v>
+      </c>
+      <c r="R65" s="1">
+        <v>0</v>
+      </c>
+      <c r="S65" s="1">
+        <v>0</v>
+      </c>
+      <c r="W65" s="1">
+        <v>0</v>
+      </c>
+      <c r="X65" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y65" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z65" s="2">
         <v>20</v>
       </c>
-      <c r="X65" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" s="1" customFormat="1" customHeight="1" spans="3:26">
+      <c r="AA65" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" s="1" customFormat="1" customHeight="1" spans="3:29">
       <c r="C66" s="1">
         <v>30042</v>
       </c>
@@ -4672,22 +5176,22 @@
         <v>3004</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="I66" s="1">
-        <v>0</v>
-      </c>
-      <c r="J66" s="1">
-        <v>0</v>
-      </c>
-      <c r="K66" s="1">
-        <v>0</v>
+        <v>68</v>
+      </c>
+      <c r="I66" s="5">
+        <v>40</v>
+      </c>
+      <c r="J66" s="5">
+        <v>4</v>
+      </c>
+      <c r="K66" s="5">
+        <v>5</v>
       </c>
       <c r="L66" s="1">
         <v>0</v>
@@ -4704,23 +5208,32 @@
       <c r="P66" s="1">
         <v>0</v>
       </c>
-      <c r="T66" s="1">
-        <v>0</v>
-      </c>
-      <c r="U66" s="1">
-        <v>0</v>
-      </c>
-      <c r="V66" s="1">
-        <v>0</v>
-      </c>
-      <c r="W66" s="2">
+      <c r="Q66" s="1">
+        <v>0</v>
+      </c>
+      <c r="R66" s="1">
+        <v>0</v>
+      </c>
+      <c r="S66" s="1">
+        <v>0</v>
+      </c>
+      <c r="W66" s="1">
+        <v>0</v>
+      </c>
+      <c r="X66" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y66" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z66" s="2">
         <v>20</v>
       </c>
-      <c r="X66" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" s="1" customFormat="1" customHeight="1" spans="3:26">
+      <c r="AA66" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" s="1" customFormat="1" customHeight="1" spans="3:29">
       <c r="C67" s="1">
         <v>30072</v>
       </c>
@@ -4731,22 +5244,22 @@
         <v>3007</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="I67" s="1">
-        <v>0</v>
-      </c>
-      <c r="J67" s="1">
-        <v>0</v>
-      </c>
-      <c r="K67" s="1">
-        <v>0</v>
+        <v>68</v>
+      </c>
+      <c r="I67" s="5">
+        <v>40</v>
+      </c>
+      <c r="J67" s="5">
+        <v>4</v>
+      </c>
+      <c r="K67" s="5">
+        <v>5</v>
       </c>
       <c r="L67" s="1">
         <v>0</v>
@@ -4763,31 +5276,43 @@
       <c r="P67" s="1">
         <v>0</v>
       </c>
-      <c r="T67" s="1">
-        <v>0</v>
-      </c>
-      <c r="U67" s="1">
-        <v>0</v>
-      </c>
-      <c r="V67" s="1">
-        <v>0</v>
-      </c>
-      <c r="W67" s="2">
+      <c r="Q67" s="1">
+        <v>0</v>
+      </c>
+      <c r="R67" s="1">
+        <v>0</v>
+      </c>
+      <c r="S67" s="1">
+        <v>0</v>
+      </c>
+      <c r="W67" s="1">
+        <v>0</v>
+      </c>
+      <c r="X67" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y67" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z67" s="2">
         <v>20</v>
       </c>
-      <c r="X67" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" s="1" customFormat="1" customHeight="1" spans="3:26">
+      <c r="AA67" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" s="1" customFormat="1" customHeight="1" spans="3:29">
       <c r="E68" s="2"/>
       <c r="F68" s="2"/>
-      <c r="P68" s="2"/>
-      <c r="Q68" s="2"/>
-      <c r="R68" s="2"/>
+      <c r="I68" s="5"/>
+      <c r="J68" s="5"/>
+      <c r="K68" s="5"/>
       <c r="S68" s="2"/>
-    </row>
-    <row r="69" s="2" customFormat="1" customHeight="1" spans="3:26">
+      <c r="T68" s="2"/>
+      <c r="U68" s="2"/>
+      <c r="V68" s="2"/>
+    </row>
+    <row r="69" s="2" customFormat="1" customHeight="1" spans="3:29">
       <c r="C69" s="1">
         <v>30023</v>
       </c>
@@ -4798,22 +5323,22 @@
         <v>3002</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="I69" s="1">
-        <v>0</v>
-      </c>
-      <c r="J69" s="1">
-        <v>0</v>
-      </c>
-      <c r="K69" s="1">
-        <v>0</v>
+        <v>70</v>
+      </c>
+      <c r="I69" s="5">
+        <v>60</v>
+      </c>
+      <c r="J69" s="5">
+        <v>4</v>
+      </c>
+      <c r="K69" s="5">
+        <v>5</v>
       </c>
       <c r="L69" s="1">
         <v>0</v>
@@ -4830,27 +5355,36 @@
       <c r="P69" s="1">
         <v>0</v>
       </c>
-      <c r="Q69" s="1"/>
-      <c r="R69" s="1"/>
-      <c r="S69" s="1"/>
-      <c r="T69" s="1">
-        <v>0</v>
-      </c>
-      <c r="U69" s="1">
-        <v>0</v>
-      </c>
-      <c r="V69" s="1">
-        <v>0</v>
-      </c>
+      <c r="Q69" s="1">
+        <v>0</v>
+      </c>
+      <c r="R69" s="1">
+        <v>0</v>
+      </c>
+      <c r="S69" s="1">
+        <v>0</v>
+      </c>
+      <c r="T69" s="1"/>
+      <c r="U69" s="1"/>
+      <c r="V69" s="1"/>
       <c r="W69" s="1">
         <v>0</v>
       </c>
-      <c r="X69" s="2">
+      <c r="X69" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y69" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z69" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA69" s="2">
         <v>20</v>
       </c>
-      <c r="Z69" s="1"/>
-    </row>
-    <row r="70" s="2" customFormat="1" customHeight="1" spans="3:26">
+      <c r="AC69" s="1"/>
+    </row>
+    <row r="70" s="2" customFormat="1" customHeight="1" spans="3:29">
       <c r="C70" s="1">
         <v>30033</v>
       </c>
@@ -4861,22 +5395,22 @@
         <v>3003</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="I70" s="1">
-        <v>0</v>
-      </c>
-      <c r="J70" s="1">
-        <v>0</v>
-      </c>
-      <c r="K70" s="1">
-        <v>0</v>
+        <v>70</v>
+      </c>
+      <c r="I70" s="5">
+        <v>60</v>
+      </c>
+      <c r="J70" s="5">
+        <v>4</v>
+      </c>
+      <c r="K70" s="5">
+        <v>5</v>
       </c>
       <c r="L70" s="1">
         <v>0</v>
@@ -4893,27 +5427,36 @@
       <c r="P70" s="1">
         <v>0</v>
       </c>
-      <c r="Q70" s="1"/>
-      <c r="R70" s="1"/>
-      <c r="S70" s="1"/>
-      <c r="T70" s="1">
-        <v>0</v>
-      </c>
-      <c r="U70" s="1">
-        <v>0</v>
-      </c>
-      <c r="V70" s="1">
-        <v>0</v>
-      </c>
+      <c r="Q70" s="1">
+        <v>0</v>
+      </c>
+      <c r="R70" s="1">
+        <v>0</v>
+      </c>
+      <c r="S70" s="1">
+        <v>0</v>
+      </c>
+      <c r="T70" s="1"/>
+      <c r="U70" s="1"/>
+      <c r="V70" s="1"/>
       <c r="W70" s="1">
         <v>0</v>
       </c>
-      <c r="X70" s="2">
+      <c r="X70" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y70" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z70" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA70" s="2">
         <v>20</v>
       </c>
-      <c r="Z70" s="1"/>
-    </row>
-    <row r="71" s="2" customFormat="1" customHeight="1" spans="3:26">
+      <c r="AC70" s="1"/>
+    </row>
+    <row r="71" s="2" customFormat="1" customHeight="1" spans="3:29">
       <c r="C71" s="1">
         <v>30043</v>
       </c>
@@ -4924,22 +5467,22 @@
         <v>3004</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="I71" s="1">
-        <v>0</v>
-      </c>
-      <c r="J71" s="1">
-        <v>0</v>
-      </c>
-      <c r="K71" s="1">
-        <v>0</v>
+        <v>70</v>
+      </c>
+      <c r="I71" s="5">
+        <v>60</v>
+      </c>
+      <c r="J71" s="5">
+        <v>4</v>
+      </c>
+      <c r="K71" s="5">
+        <v>5</v>
       </c>
       <c r="L71" s="1">
         <v>0</v>
@@ -4956,27 +5499,36 @@
       <c r="P71" s="1">
         <v>0</v>
       </c>
-      <c r="Q71" s="1"/>
-      <c r="R71" s="1"/>
-      <c r="S71" s="1"/>
-      <c r="T71" s="1">
-        <v>0</v>
-      </c>
-      <c r="U71" s="1">
-        <v>0</v>
-      </c>
-      <c r="V71" s="1">
-        <v>0</v>
-      </c>
+      <c r="Q71" s="1">
+        <v>0</v>
+      </c>
+      <c r="R71" s="1">
+        <v>0</v>
+      </c>
+      <c r="S71" s="1">
+        <v>0</v>
+      </c>
+      <c r="T71" s="1"/>
+      <c r="U71" s="1"/>
+      <c r="V71" s="1"/>
       <c r="W71" s="1">
         <v>0</v>
       </c>
-      <c r="X71" s="2">
+      <c r="X71" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y71" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z71" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA71" s="2">
         <v>20</v>
       </c>
-      <c r="Z71" s="1"/>
-    </row>
-    <row r="72" s="2" customFormat="1" customHeight="1" spans="3:26">
+      <c r="AC71" s="1"/>
+    </row>
+    <row r="72" s="2" customFormat="1" customHeight="1" spans="3:29">
       <c r="C72" s="1">
         <v>30073</v>
       </c>
@@ -4987,22 +5539,22 @@
         <v>3007</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="H72" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="I72" s="1">
-        <v>0</v>
-      </c>
-      <c r="J72" s="1">
-        <v>0</v>
-      </c>
-      <c r="K72" s="1">
-        <v>0</v>
+        <v>89</v>
+      </c>
+      <c r="I72" s="5">
+        <v>60</v>
+      </c>
+      <c r="J72" s="5">
+        <v>4</v>
+      </c>
+      <c r="K72" s="5">
+        <v>5</v>
       </c>
       <c r="L72" s="1">
         <v>0</v>
@@ -5019,34 +5571,43 @@
       <c r="P72" s="1">
         <v>0</v>
       </c>
-      <c r="Q72" s="1"/>
-      <c r="R72" s="1"/>
-      <c r="S72" s="1"/>
-      <c r="T72" s="1">
-        <v>0</v>
-      </c>
-      <c r="U72" s="1">
-        <v>0</v>
-      </c>
-      <c r="V72" s="1">
-        <v>0</v>
-      </c>
+      <c r="Q72" s="1">
+        <v>0</v>
+      </c>
+      <c r="R72" s="1">
+        <v>0</v>
+      </c>
+      <c r="S72" s="1">
+        <v>0</v>
+      </c>
+      <c r="T72" s="1"/>
+      <c r="U72" s="1"/>
+      <c r="V72" s="1"/>
       <c r="W72" s="1">
         <v>0</v>
       </c>
-      <c r="X72" s="2">
+      <c r="X72" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y72" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z72" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA72" s="2">
         <v>20</v>
       </c>
-      <c r="Z72" s="1"/>
-    </row>
-    <row r="73" s="2" customFormat="1" customHeight="1" spans="3:26">
+      <c r="AC72" s="1"/>
+    </row>
+    <row r="73" s="2" customFormat="1" customHeight="1" spans="3:29">
       <c r="C73" s="1"/>
       <c r="D73" s="1"/>
       <c r="G73" s="1"/>
       <c r="H73" s="1"/>
-      <c r="I73" s="1"/>
-      <c r="J73" s="1"/>
-      <c r="K73" s="1"/>
+      <c r="I73" s="5"/>
+      <c r="J73" s="5"/>
+      <c r="K73" s="5"/>
       <c r="L73" s="1"/>
       <c r="M73" s="1"/>
       <c r="N73" s="1"/>
@@ -5060,9 +5621,12 @@
       <c r="V73" s="1"/>
       <c r="W73" s="1"/>
       <c r="X73" s="1"/>
+      <c r="Y73" s="1"/>
       <c r="Z73" s="1"/>
-    </row>
-    <row r="74" s="2" customFormat="1" customHeight="1" spans="3:26">
+      <c r="AA73" s="1"/>
+      <c r="AC73" s="1"/>
+    </row>
+    <row r="74" s="2" customFormat="1" customHeight="1" spans="3:29">
       <c r="C74" s="1">
         <v>30024</v>
       </c>
@@ -5073,22 +5637,22 @@
         <v>3002</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="H74" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="I74" s="1">
-        <v>0</v>
-      </c>
-      <c r="J74" s="1">
-        <v>0</v>
-      </c>
-      <c r="K74" s="1">
-        <v>0</v>
+        <v>72</v>
+      </c>
+      <c r="I74" s="6">
+        <v>20</v>
+      </c>
+      <c r="J74" s="6">
+        <v>5</v>
+      </c>
+      <c r="K74" s="6">
+        <v>5</v>
       </c>
       <c r="L74" s="1">
         <v>0</v>
@@ -5105,27 +5669,36 @@
       <c r="P74" s="1">
         <v>0</v>
       </c>
-      <c r="Q74" s="1"/>
-      <c r="R74" s="1"/>
-      <c r="S74" s="1"/>
-      <c r="T74" s="1">
-        <v>0</v>
-      </c>
-      <c r="U74" s="1">
+      <c r="Q74" s="1">
+        <v>0</v>
+      </c>
+      <c r="R74" s="1">
+        <v>0</v>
+      </c>
+      <c r="S74" s="1">
+        <v>0</v>
+      </c>
+      <c r="T74" s="1"/>
+      <c r="U74" s="1"/>
+      <c r="V74" s="1"/>
+      <c r="W74" s="1">
+        <v>0</v>
+      </c>
+      <c r="X74" s="1">
         <v>100</v>
       </c>
-      <c r="V74" s="1">
-        <v>0</v>
-      </c>
-      <c r="W74" s="1">
-        <v>0</v>
-      </c>
-      <c r="X74" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z74" s="1"/>
-    </row>
-    <row r="75" s="2" customFormat="1" customHeight="1" spans="3:26">
+      <c r="Y74" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z74" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA74" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC74" s="1"/>
+    </row>
+    <row r="75" s="2" customFormat="1" customHeight="1" spans="3:29">
       <c r="C75" s="1">
         <v>30034</v>
       </c>
@@ -5136,22 +5709,22 @@
         <v>3003</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="H75" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="I75" s="1">
-        <v>0</v>
-      </c>
-      <c r="J75" s="1">
-        <v>0</v>
-      </c>
-      <c r="K75" s="1">
-        <v>0</v>
+        <v>72</v>
+      </c>
+      <c r="I75" s="6">
+        <v>20</v>
+      </c>
+      <c r="J75" s="6">
+        <v>5</v>
+      </c>
+      <c r="K75" s="6">
+        <v>5</v>
       </c>
       <c r="L75" s="1">
         <v>0</v>
@@ -5168,27 +5741,36 @@
       <c r="P75" s="1">
         <v>0</v>
       </c>
-      <c r="Q75" s="1"/>
-      <c r="R75" s="1"/>
-      <c r="S75" s="1"/>
-      <c r="T75" s="1">
-        <v>0</v>
-      </c>
-      <c r="U75" s="1">
+      <c r="Q75" s="1">
+        <v>0</v>
+      </c>
+      <c r="R75" s="1">
+        <v>0</v>
+      </c>
+      <c r="S75" s="1">
+        <v>0</v>
+      </c>
+      <c r="T75" s="1"/>
+      <c r="U75" s="1"/>
+      <c r="V75" s="1"/>
+      <c r="W75" s="1">
+        <v>0</v>
+      </c>
+      <c r="X75" s="1">
         <v>100</v>
       </c>
-      <c r="V75" s="1">
-        <v>0</v>
-      </c>
-      <c r="W75" s="1">
-        <v>0</v>
-      </c>
-      <c r="X75" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z75" s="1"/>
-    </row>
-    <row r="76" s="2" customFormat="1" customHeight="1" spans="3:26">
+      <c r="Y75" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z75" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA75" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC75" s="1"/>
+    </row>
+    <row r="76" s="2" customFormat="1" customHeight="1" spans="3:29">
       <c r="C76" s="1">
         <v>30044</v>
       </c>
@@ -5199,22 +5781,22 @@
         <v>3004</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="I76" s="1">
-        <v>0</v>
-      </c>
-      <c r="J76" s="1">
-        <v>0</v>
-      </c>
-      <c r="K76" s="1">
-        <v>0</v>
+        <v>72</v>
+      </c>
+      <c r="I76" s="6">
+        <v>20</v>
+      </c>
+      <c r="J76" s="6">
+        <v>5</v>
+      </c>
+      <c r="K76" s="6">
+        <v>5</v>
       </c>
       <c r="L76" s="1">
         <v>0</v>
@@ -5231,27 +5813,36 @@
       <c r="P76" s="1">
         <v>0</v>
       </c>
-      <c r="Q76" s="1"/>
-      <c r="R76" s="1"/>
-      <c r="S76" s="1"/>
-      <c r="T76" s="1">
-        <v>0</v>
-      </c>
-      <c r="U76" s="1">
+      <c r="Q76" s="1">
+        <v>0</v>
+      </c>
+      <c r="R76" s="1">
+        <v>0</v>
+      </c>
+      <c r="S76" s="1">
+        <v>0</v>
+      </c>
+      <c r="T76" s="1"/>
+      <c r="U76" s="1"/>
+      <c r="V76" s="1"/>
+      <c r="W76" s="1">
+        <v>0</v>
+      </c>
+      <c r="X76" s="1">
         <v>100</v>
       </c>
-      <c r="V76" s="1">
-        <v>0</v>
-      </c>
-      <c r="W76" s="1">
-        <v>0</v>
-      </c>
-      <c r="X76" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z76" s="1"/>
-    </row>
-    <row r="77" s="1" customFormat="1" customHeight="1" spans="3:26">
+      <c r="Y76" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z76" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA76" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC76" s="1"/>
+    </row>
+    <row r="77" s="1" customFormat="1" customHeight="1" spans="3:29">
       <c r="C77" s="1">
         <v>30074</v>
       </c>
@@ -5262,22 +5853,22 @@
         <v>3007</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="I77" s="1">
-        <v>0</v>
-      </c>
-      <c r="J77" s="1">
-        <v>0</v>
-      </c>
-      <c r="K77" s="1">
-        <v>0</v>
+        <v>90</v>
+      </c>
+      <c r="I77" s="6">
+        <v>20</v>
+      </c>
+      <c r="J77" s="6">
+        <v>5</v>
+      </c>
+      <c r="K77" s="6">
+        <v>5</v>
       </c>
       <c r="L77" s="1">
         <v>0</v>
@@ -5294,25 +5885,34 @@
       <c r="P77" s="1">
         <v>0</v>
       </c>
-      <c r="T77" s="1">
-        <v>0</v>
-      </c>
-      <c r="U77" s="1">
+      <c r="Q77" s="1">
+        <v>0</v>
+      </c>
+      <c r="R77" s="1">
+        <v>0</v>
+      </c>
+      <c r="S77" s="1">
+        <v>0</v>
+      </c>
+      <c r="W77" s="1">
+        <v>0</v>
+      </c>
+      <c r="X77" s="1">
         <v>100</v>
       </c>
-      <c r="V77" s="1">
-        <v>0</v>
-      </c>
-      <c r="W77" s="1">
-        <v>0</v>
-      </c>
-      <c r="X77" s="1">
+      <c r="Y77" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z77" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA77" s="1">
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:I5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="L3:L5 C3:H5 I3:K5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/SkillSuitConfig.xlsx
+++ b/Excel/SkillSuitConfig.xlsx
@@ -1096,7 +1096,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1104,8 +1104,6 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1753,13 +1751,13 @@
       <c r="H6" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="I6" s="5">
+      <c r="I6" s="2">
         <v>100</v>
       </c>
-      <c r="J6" s="5">
+      <c r="J6" s="2">
         <v>1</v>
       </c>
-      <c r="K6" s="5">
+      <c r="K6" s="2">
         <v>5</v>
       </c>
       <c r="L6" s="1">
@@ -1821,13 +1819,13 @@
       <c r="H7" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="I7" s="5">
+      <c r="I7" s="2">
         <v>100</v>
       </c>
-      <c r="J7" s="5">
+      <c r="J7" s="2">
         <v>1</v>
       </c>
-      <c r="K7" s="5">
+      <c r="K7" s="2">
         <v>5</v>
       </c>
       <c r="L7" s="1">
@@ -1892,13 +1890,13 @@
       <c r="H8" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="I8" s="5">
+      <c r="I8" s="2">
         <v>100</v>
       </c>
-      <c r="J8" s="5">
+      <c r="J8" s="2">
         <v>1</v>
       </c>
-      <c r="K8" s="5">
+      <c r="K8" s="2">
         <v>5</v>
       </c>
       <c r="L8" s="1">
@@ -1963,13 +1961,13 @@
       <c r="H9" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="I9" s="5">
+      <c r="I9" s="2">
         <v>100</v>
       </c>
-      <c r="J9" s="5">
+      <c r="J9" s="2">
         <v>1</v>
       </c>
-      <c r="K9" s="5">
+      <c r="K9" s="2">
         <v>5</v>
       </c>
       <c r="L9" s="1">
@@ -2034,13 +2032,13 @@
       <c r="H10" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="I10" s="5">
+      <c r="I10" s="2">
         <v>100</v>
       </c>
-      <c r="J10" s="5">
+      <c r="J10" s="2">
         <v>1</v>
       </c>
-      <c r="K10" s="5">
+      <c r="K10" s="2">
         <v>5</v>
       </c>
       <c r="L10" s="1">
@@ -2105,13 +2103,13 @@
       <c r="H11" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="I11" s="5">
+      <c r="I11" s="2">
         <v>100</v>
       </c>
-      <c r="J11" s="5">
+      <c r="J11" s="2">
         <v>1</v>
       </c>
-      <c r="K11" s="5">
+      <c r="K11" s="2">
         <v>5</v>
       </c>
       <c r="L11" s="1">
@@ -2176,13 +2174,13 @@
       <c r="H12" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="I12" s="5">
+      <c r="I12" s="2">
         <v>100</v>
       </c>
-      <c r="J12" s="5">
+      <c r="J12" s="2">
         <v>1</v>
       </c>
-      <c r="K12" s="5">
+      <c r="K12" s="2">
         <v>5</v>
       </c>
       <c r="L12" s="1">
@@ -2232,9 +2230,9 @@
       <c r="F13" s="2"/>
       <c r="G13" s="1"/>
       <c r="H13" s="1"/>
-      <c r="I13" s="5"/>
-      <c r="J13" s="5"/>
-      <c r="K13" s="5"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
+      <c r="K13" s="2"/>
       <c r="L13" s="1"/>
       <c r="M13" s="1"/>
       <c r="N13" s="1"/>
@@ -2260,13 +2258,13 @@
       <c r="H14" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="I14" s="5">
+      <c r="I14" s="2">
         <v>40</v>
       </c>
-      <c r="J14" s="5">
+      <c r="J14" s="2">
         <v>4</v>
       </c>
-      <c r="K14" s="5">
+      <c r="K14" s="2">
         <v>5</v>
       </c>
       <c r="L14" s="1">
@@ -2328,13 +2326,13 @@
       <c r="H15" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="I15" s="5">
+      <c r="I15" s="2">
         <v>40</v>
       </c>
-      <c r="J15" s="5">
+      <c r="J15" s="2">
         <v>4</v>
       </c>
-      <c r="K15" s="5">
+      <c r="K15" s="2">
         <v>5</v>
       </c>
       <c r="L15" s="1">
@@ -2396,13 +2394,13 @@
       <c r="H16" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="I16" s="5">
+      <c r="I16" s="2">
         <v>40</v>
       </c>
-      <c r="J16" s="5">
+      <c r="J16" s="2">
         <v>4</v>
       </c>
-      <c r="K16" s="5">
+      <c r="K16" s="2">
         <v>5</v>
       </c>
       <c r="L16" s="1">
@@ -2464,13 +2462,13 @@
       <c r="H17" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="I17" s="5">
+      <c r="I17" s="2">
         <v>40</v>
       </c>
-      <c r="J17" s="5">
+      <c r="J17" s="2">
         <v>4</v>
       </c>
-      <c r="K17" s="5">
+      <c r="K17" s="2">
         <v>5</v>
       </c>
       <c r="L17" s="1">
@@ -2516,9 +2514,9 @@
     <row r="18" s="1" customFormat="1" customHeight="1" spans="3:29">
       <c r="E18" s="2"/>
       <c r="F18" s="2"/>
-      <c r="I18" s="5"/>
-      <c r="J18" s="5"/>
-      <c r="K18" s="5"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="2"/>
+      <c r="K18" s="2"/>
       <c r="S18" s="2"/>
       <c r="T18" s="2"/>
       <c r="U18" s="2"/>
@@ -2543,13 +2541,13 @@
       <c r="H19" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="I19" s="5">
+      <c r="I19" s="2">
         <v>60</v>
       </c>
-      <c r="J19" s="5">
+      <c r="J19" s="2">
         <v>4</v>
       </c>
-      <c r="K19" s="5">
+      <c r="K19" s="2">
         <v>5</v>
       </c>
       <c r="L19" s="1">
@@ -2615,13 +2613,13 @@
       <c r="H20" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="I20" s="5">
+      <c r="I20" s="2">
         <v>60</v>
       </c>
-      <c r="J20" s="5">
+      <c r="J20" s="2">
         <v>4</v>
       </c>
-      <c r="K20" s="5">
+      <c r="K20" s="2">
         <v>5</v>
       </c>
       <c r="L20" s="1">
@@ -2687,13 +2685,13 @@
       <c r="H21" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="I21" s="5">
+      <c r="I21" s="2">
         <v>60</v>
       </c>
-      <c r="J21" s="5">
+      <c r="J21" s="2">
         <v>4</v>
       </c>
-      <c r="K21" s="5">
+      <c r="K21" s="2">
         <v>5</v>
       </c>
       <c r="L21" s="1">
@@ -2759,13 +2757,13 @@
       <c r="H22" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="I22" s="5">
+      <c r="I22" s="2">
         <v>60</v>
       </c>
-      <c r="J22" s="5">
+      <c r="J22" s="2">
         <v>4</v>
       </c>
-      <c r="K22" s="5">
+      <c r="K22" s="2">
         <v>5</v>
       </c>
       <c r="L22" s="1">
@@ -2819,9 +2817,9 @@
       <c r="F23" s="2"/>
       <c r="G23" s="1"/>
       <c r="H23" s="1"/>
-      <c r="I23" s="5"/>
-      <c r="J23" s="5"/>
-      <c r="K23" s="5"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="2"/>
+      <c r="K23" s="2"/>
       <c r="L23" s="1"/>
       <c r="M23" s="1"/>
       <c r="N23" s="1"/>
@@ -2859,13 +2857,13 @@
       <c r="H24" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="I24" s="6">
+      <c r="I24" s="2">
         <v>20</v>
       </c>
-      <c r="J24" s="6">
-        <v>5</v>
-      </c>
-      <c r="K24" s="6">
+      <c r="J24" s="2">
+        <v>5</v>
+      </c>
+      <c r="K24" s="2">
         <v>5</v>
       </c>
       <c r="L24" s="1">
@@ -2931,13 +2929,13 @@
       <c r="H25" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="I25" s="6">
+      <c r="I25" s="2">
         <v>20</v>
       </c>
-      <c r="J25" s="6">
-        <v>5</v>
-      </c>
-      <c r="K25" s="6">
+      <c r="J25" s="2">
+        <v>5</v>
+      </c>
+      <c r="K25" s="2">
         <v>5</v>
       </c>
       <c r="L25" s="1">
@@ -3003,13 +3001,13 @@
       <c r="H26" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="I26" s="6">
+      <c r="I26" s="2">
         <v>20</v>
       </c>
-      <c r="J26" s="6">
-        <v>5</v>
-      </c>
-      <c r="K26" s="6">
+      <c r="J26" s="2">
+        <v>5</v>
+      </c>
+      <c r="K26" s="2">
         <v>5</v>
       </c>
       <c r="L26" s="1">
@@ -3075,13 +3073,13 @@
       <c r="H27" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="I27" s="6">
+      <c r="I27" s="2">
         <v>20</v>
       </c>
-      <c r="J27" s="6">
-        <v>5</v>
-      </c>
-      <c r="K27" s="6">
+      <c r="J27" s="2">
+        <v>5</v>
+      </c>
+      <c r="K27" s="2">
         <v>5</v>
       </c>
       <c r="L27" s="1">
@@ -3125,22 +3123,22 @@
       </c>
     </row>
     <row r="28" customHeight="1" spans="3:29">
-      <c r="I28" s="5"/>
-      <c r="J28" s="5"/>
-      <c r="K28" s="5"/>
+      <c r="I28" s="2"/>
+      <c r="J28" s="2"/>
+      <c r="K28" s="2"/>
     </row>
     <row r="29" s="3" customFormat="1" customHeight="1"/>
     <row r="30" customHeight="1" spans="3:29">
-      <c r="I30" s="5"/>
-      <c r="J30" s="5"/>
-      <c r="K30" s="5"/>
+      <c r="I30" s="2"/>
+      <c r="J30" s="2"/>
+      <c r="K30" s="2"/>
     </row>
     <row r="31" s="1" customFormat="1" customHeight="1" spans="3:29">
       <c r="C31" s="1">
         <v>20011</v>
       </c>
       <c r="D31" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E31" s="2">
         <v>2001</v>
@@ -3154,13 +3152,13 @@
       <c r="H31" s="1" t="s">
         <v>74</v>
       </c>
-      <c r="I31" s="5">
+      <c r="I31" s="2">
         <v>100</v>
       </c>
-      <c r="J31" s="5">
+      <c r="J31" s="2">
         <v>1</v>
       </c>
-      <c r="K31" s="5">
+      <c r="K31" s="2">
         <v>5</v>
       </c>
       <c r="L31" s="1">
@@ -3208,7 +3206,7 @@
         <v>20021</v>
       </c>
       <c r="D32" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E32" s="2">
         <v>2002</v>
@@ -3222,13 +3220,13 @@
       <c r="H32" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="I32" s="5">
+      <c r="I32" s="2">
         <v>100</v>
       </c>
-      <c r="J32" s="5">
+      <c r="J32" s="2">
         <v>1</v>
       </c>
-      <c r="K32" s="5">
+      <c r="K32" s="2">
         <v>5</v>
       </c>
       <c r="L32" s="1">
@@ -3279,7 +3277,7 @@
         <v>20031</v>
       </c>
       <c r="D33" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E33" s="2">
         <v>2003</v>
@@ -3293,13 +3291,13 @@
       <c r="H33" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="I33" s="5">
+      <c r="I33" s="2">
         <v>100</v>
       </c>
-      <c r="J33" s="5">
+      <c r="J33" s="2">
         <v>1</v>
       </c>
-      <c r="K33" s="5">
+      <c r="K33" s="2">
         <v>5</v>
       </c>
       <c r="L33" s="1">
@@ -3350,7 +3348,7 @@
         <v>20041</v>
       </c>
       <c r="D34" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E34" s="2">
         <v>2004</v>
@@ -3364,13 +3362,13 @@
       <c r="H34" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="I34" s="5">
+      <c r="I34" s="2">
         <v>100</v>
       </c>
-      <c r="J34" s="5">
+      <c r="J34" s="2">
         <v>1</v>
       </c>
-      <c r="K34" s="5">
+      <c r="K34" s="2">
         <v>5</v>
       </c>
       <c r="L34" s="1">
@@ -3421,7 +3419,7 @@
         <v>20051</v>
       </c>
       <c r="D35" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E35" s="2">
         <v>2005</v>
@@ -3435,13 +3433,13 @@
       <c r="H35" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="I35" s="5">
+      <c r="I35" s="2">
         <v>100</v>
       </c>
-      <c r="J35" s="5">
+      <c r="J35" s="2">
         <v>1</v>
       </c>
-      <c r="K35" s="5">
+      <c r="K35" s="2">
         <v>5</v>
       </c>
       <c r="L35" s="1">
@@ -3492,7 +3490,7 @@
         <v>20061</v>
       </c>
       <c r="D36" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E36" s="2">
         <v>2006</v>
@@ -3506,13 +3504,13 @@
       <c r="H36" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="I36" s="5">
+      <c r="I36" s="2">
         <v>100</v>
       </c>
-      <c r="J36" s="5">
+      <c r="J36" s="2">
         <v>1</v>
       </c>
-      <c r="K36" s="5">
+      <c r="K36" s="2">
         <v>5</v>
       </c>
       <c r="L36" s="1">
@@ -3563,7 +3561,7 @@
         <v>20071</v>
       </c>
       <c r="D37" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E37" s="2">
         <v>2007</v>
@@ -3577,13 +3575,13 @@
       <c r="H37" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="I37" s="5">
+      <c r="I37" s="2">
         <v>100</v>
       </c>
-      <c r="J37" s="5">
+      <c r="J37" s="2">
         <v>1</v>
       </c>
-      <c r="K37" s="5">
+      <c r="K37" s="2">
         <v>5</v>
       </c>
       <c r="L37" s="1">
@@ -3631,9 +3629,9 @@
     </row>
     <row r="38" s="1" customFormat="1" customHeight="1" spans="3:29">
       <c r="F38" s="2"/>
-      <c r="I38" s="5"/>
-      <c r="J38" s="5"/>
-      <c r="K38" s="5"/>
+      <c r="I38" s="2"/>
+      <c r="J38" s="2"/>
+      <c r="K38" s="2"/>
       <c r="Z38" s="2"/>
     </row>
     <row r="39" s="1" customFormat="1" customHeight="1" spans="3:29">
@@ -3641,7 +3639,7 @@
         <v>20022</v>
       </c>
       <c r="D39" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E39" s="2">
         <v>2002</v>
@@ -3655,13 +3653,13 @@
       <c r="H39" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="I39" s="5">
+      <c r="I39" s="2">
         <v>40</v>
       </c>
-      <c r="J39" s="5">
+      <c r="J39" s="2">
         <v>4</v>
       </c>
-      <c r="K39" s="5">
+      <c r="K39" s="2">
         <v>5</v>
       </c>
       <c r="L39" s="1">
@@ -3709,7 +3707,7 @@
         <v>20032</v>
       </c>
       <c r="D40" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E40" s="2">
         <v>2003</v>
@@ -3723,13 +3721,13 @@
       <c r="H40" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="I40" s="5">
+      <c r="I40" s="2">
         <v>40</v>
       </c>
-      <c r="J40" s="5">
+      <c r="J40" s="2">
         <v>4</v>
       </c>
-      <c r="K40" s="5">
+      <c r="K40" s="2">
         <v>5</v>
       </c>
       <c r="L40" s="1">
@@ -3777,7 +3775,7 @@
         <v>20042</v>
       </c>
       <c r="D41" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E41" s="2">
         <v>2004</v>
@@ -3791,13 +3789,13 @@
       <c r="H41" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="I41" s="5">
+      <c r="I41" s="2">
         <v>40</v>
       </c>
-      <c r="J41" s="5">
+      <c r="J41" s="2">
         <v>4</v>
       </c>
-      <c r="K41" s="5">
+      <c r="K41" s="2">
         <v>5</v>
       </c>
       <c r="L41" s="1">
@@ -3845,7 +3843,7 @@
         <v>20072</v>
       </c>
       <c r="D42" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E42" s="2">
         <v>2007</v>
@@ -3859,13 +3857,13 @@
       <c r="H42" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="I42" s="5">
+      <c r="I42" s="2">
         <v>40</v>
       </c>
-      <c r="J42" s="5">
+      <c r="J42" s="2">
         <v>4</v>
       </c>
-      <c r="K42" s="5">
+      <c r="K42" s="2">
         <v>5</v>
       </c>
       <c r="L42" s="1">
@@ -3911,9 +3909,9 @@
     <row r="43" s="1" customFormat="1" customHeight="1" spans="3:29">
       <c r="E43" s="2"/>
       <c r="F43" s="2"/>
-      <c r="I43" s="5"/>
-      <c r="J43" s="5"/>
-      <c r="K43" s="5"/>
+      <c r="I43" s="2"/>
+      <c r="J43" s="2"/>
+      <c r="K43" s="2"/>
       <c r="S43" s="2"/>
       <c r="T43" s="2"/>
       <c r="U43" s="2"/>
@@ -3924,7 +3922,7 @@
         <v>20023</v>
       </c>
       <c r="D44" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E44" s="2">
         <v>2002</v>
@@ -3938,13 +3936,13 @@
       <c r="H44" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="I44" s="5">
+      <c r="I44" s="2">
         <v>60</v>
       </c>
-      <c r="J44" s="5">
+      <c r="J44" s="2">
         <v>4</v>
       </c>
-      <c r="K44" s="5">
+      <c r="K44" s="2">
         <v>5</v>
       </c>
       <c r="L44" s="1">
@@ -3996,7 +3994,7 @@
         <v>20033</v>
       </c>
       <c r="D45" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E45" s="2">
         <v>2003</v>
@@ -4010,13 +4008,13 @@
       <c r="H45" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="I45" s="5">
+      <c r="I45" s="2">
         <v>60</v>
       </c>
-      <c r="J45" s="5">
+      <c r="J45" s="2">
         <v>4</v>
       </c>
-      <c r="K45" s="5">
+      <c r="K45" s="2">
         <v>5</v>
       </c>
       <c r="L45" s="1">
@@ -4068,7 +4066,7 @@
         <v>20043</v>
       </c>
       <c r="D46" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E46" s="2">
         <v>2004</v>
@@ -4082,13 +4080,13 @@
       <c r="H46" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="I46" s="5">
+      <c r="I46" s="2">
         <v>60</v>
       </c>
-      <c r="J46" s="5">
+      <c r="J46" s="2">
         <v>4</v>
       </c>
-      <c r="K46" s="5">
+      <c r="K46" s="2">
         <v>5</v>
       </c>
       <c r="L46" s="1">
@@ -4140,7 +4138,7 @@
         <v>20073</v>
       </c>
       <c r="D47" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E47" s="2">
         <v>2007</v>
@@ -4154,13 +4152,13 @@
       <c r="H47" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="I47" s="5">
+      <c r="I47" s="2">
         <v>60</v>
       </c>
-      <c r="J47" s="5">
+      <c r="J47" s="2">
         <v>4</v>
       </c>
-      <c r="K47" s="5">
+      <c r="K47" s="2">
         <v>5</v>
       </c>
       <c r="L47" s="1">
@@ -4212,9 +4210,9 @@
       <c r="D48" s="1"/>
       <c r="G48" s="1"/>
       <c r="H48" s="1"/>
-      <c r="I48" s="5"/>
-      <c r="J48" s="5"/>
-      <c r="K48" s="5"/>
+      <c r="I48" s="2"/>
+      <c r="J48" s="2"/>
+      <c r="K48" s="2"/>
       <c r="L48" s="1"/>
       <c r="M48" s="1"/>
       <c r="N48" s="1"/>
@@ -4238,7 +4236,7 @@
         <v>20024</v>
       </c>
       <c r="D49" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E49" s="2">
         <v>2002</v>
@@ -4252,13 +4250,13 @@
       <c r="H49" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="I49" s="6">
+      <c r="I49" s="2">
         <v>20</v>
       </c>
-      <c r="J49" s="6">
-        <v>5</v>
-      </c>
-      <c r="K49" s="6">
+      <c r="J49" s="2">
+        <v>5</v>
+      </c>
+      <c r="K49" s="2">
         <v>5</v>
       </c>
       <c r="L49" s="1">
@@ -4310,7 +4308,7 @@
         <v>20034</v>
       </c>
       <c r="D50" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E50" s="2">
         <v>2003</v>
@@ -4324,13 +4322,13 @@
       <c r="H50" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="I50" s="6">
+      <c r="I50" s="2">
         <v>20</v>
       </c>
-      <c r="J50" s="6">
-        <v>5</v>
-      </c>
-      <c r="K50" s="6">
+      <c r="J50" s="2">
+        <v>5</v>
+      </c>
+      <c r="K50" s="2">
         <v>5</v>
       </c>
       <c r="L50" s="1">
@@ -4382,7 +4380,7 @@
         <v>20044</v>
       </c>
       <c r="D51" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E51" s="2">
         <v>2004</v>
@@ -4396,13 +4394,13 @@
       <c r="H51" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="I51" s="6">
+      <c r="I51" s="2">
         <v>20</v>
       </c>
-      <c r="J51" s="6">
-        <v>5</v>
-      </c>
-      <c r="K51" s="6">
+      <c r="J51" s="2">
+        <v>5</v>
+      </c>
+      <c r="K51" s="2">
         <v>5</v>
       </c>
       <c r="L51" s="1">
@@ -4454,7 +4452,7 @@
         <v>20074</v>
       </c>
       <c r="D52" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E52" s="2">
         <v>2007</v>
@@ -4468,13 +4466,13 @@
       <c r="H52" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="I52" s="6">
+      <c r="I52" s="2">
         <v>20</v>
       </c>
-      <c r="J52" s="6">
-        <v>5</v>
-      </c>
-      <c r="K52" s="6">
+      <c r="J52" s="2">
+        <v>5</v>
+      </c>
+      <c r="K52" s="2">
         <v>5</v>
       </c>
       <c r="L52" s="1">
@@ -4518,22 +4516,22 @@
       </c>
     </row>
     <row r="53" customHeight="1" spans="3:29">
-      <c r="I53" s="5"/>
-      <c r="J53" s="5"/>
-      <c r="K53" s="5"/>
+      <c r="I53" s="2"/>
+      <c r="J53" s="2"/>
+      <c r="K53" s="2"/>
     </row>
     <row r="54" s="3" customFormat="1" customHeight="1"/>
     <row r="55" customHeight="1" spans="3:29">
-      <c r="I55" s="5"/>
-      <c r="J55" s="5"/>
-      <c r="K55" s="5"/>
+      <c r="I55" s="2"/>
+      <c r="J55" s="2"/>
+      <c r="K55" s="2"/>
     </row>
     <row r="56" s="1" customFormat="1" customHeight="1" spans="3:29">
       <c r="C56" s="1">
         <v>30011</v>
       </c>
       <c r="D56" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E56" s="2">
         <v>3001</v>
@@ -4547,13 +4545,13 @@
       <c r="H56" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="I56" s="5">
+      <c r="I56" s="2">
         <v>100</v>
       </c>
-      <c r="J56" s="5">
+      <c r="J56" s="2">
         <v>1</v>
       </c>
-      <c r="K56" s="5">
+      <c r="K56" s="2">
         <v>5</v>
       </c>
       <c r="L56" s="1">
@@ -4601,7 +4599,7 @@
         <v>30021</v>
       </c>
       <c r="D57" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E57" s="2">
         <v>3002</v>
@@ -4615,13 +4613,13 @@
       <c r="H57" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="I57" s="5">
+      <c r="I57" s="2">
         <v>100</v>
       </c>
-      <c r="J57" s="5">
+      <c r="J57" s="2">
         <v>1</v>
       </c>
-      <c r="K57" s="5">
+      <c r="K57" s="2">
         <v>5</v>
       </c>
       <c r="L57" s="1">
@@ -4672,7 +4670,7 @@
         <v>30031</v>
       </c>
       <c r="D58" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E58" s="2">
         <v>3003</v>
@@ -4686,13 +4684,13 @@
       <c r="H58" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="I58" s="5">
+      <c r="I58" s="2">
         <v>100</v>
       </c>
-      <c r="J58" s="5">
+      <c r="J58" s="2">
         <v>1</v>
       </c>
-      <c r="K58" s="5">
+      <c r="K58" s="2">
         <v>5</v>
       </c>
       <c r="L58" s="1">
@@ -4743,7 +4741,7 @@
         <v>30041</v>
       </c>
       <c r="D59" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E59" s="2">
         <v>3004</v>
@@ -4757,13 +4755,13 @@
       <c r="H59" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="I59" s="5">
+      <c r="I59" s="2">
         <v>100</v>
       </c>
-      <c r="J59" s="5">
+      <c r="J59" s="2">
         <v>1</v>
       </c>
-      <c r="K59" s="5">
+      <c r="K59" s="2">
         <v>5</v>
       </c>
       <c r="L59" s="1">
@@ -4814,7 +4812,7 @@
         <v>30051</v>
       </c>
       <c r="D60" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E60" s="2">
         <v>3005</v>
@@ -4828,13 +4826,13 @@
       <c r="H60" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="I60" s="5">
+      <c r="I60" s="2">
         <v>100</v>
       </c>
-      <c r="J60" s="5">
+      <c r="J60" s="2">
         <v>1</v>
       </c>
-      <c r="K60" s="5">
+      <c r="K60" s="2">
         <v>5</v>
       </c>
       <c r="L60" s="1">
@@ -4885,7 +4883,7 @@
         <v>30061</v>
       </c>
       <c r="D61" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E61" s="2">
         <v>3006</v>
@@ -4899,13 +4897,13 @@
       <c r="H61" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="I61" s="5">
+      <c r="I61" s="2">
         <v>100</v>
       </c>
-      <c r="J61" s="5">
+      <c r="J61" s="2">
         <v>1</v>
       </c>
-      <c r="K61" s="5">
+      <c r="K61" s="2">
         <v>5</v>
       </c>
       <c r="L61" s="1">
@@ -4956,7 +4954,7 @@
         <v>30071</v>
       </c>
       <c r="D62" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E62" s="2">
         <v>3007</v>
@@ -4970,13 +4968,13 @@
       <c r="H62" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="I62" s="5">
+      <c r="I62" s="2">
         <v>100</v>
       </c>
-      <c r="J62" s="5">
+      <c r="J62" s="2">
         <v>1</v>
       </c>
-      <c r="K62" s="5">
+      <c r="K62" s="2">
         <v>5</v>
       </c>
       <c r="L62" s="1">
@@ -5024,9 +5022,9 @@
     </row>
     <row r="63" s="1" customFormat="1" customHeight="1" spans="3:29">
       <c r="F63" s="2"/>
-      <c r="I63" s="5"/>
-      <c r="J63" s="5"/>
-      <c r="K63" s="5"/>
+      <c r="I63" s="2"/>
+      <c r="J63" s="2"/>
+      <c r="K63" s="2"/>
       <c r="Z63" s="2"/>
     </row>
     <row r="64" s="1" customFormat="1" customHeight="1" spans="3:29">
@@ -5034,7 +5032,7 @@
         <v>30022</v>
       </c>
       <c r="D64" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E64" s="2">
         <v>3002</v>
@@ -5048,13 +5046,13 @@
       <c r="H64" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="I64" s="5">
+      <c r="I64" s="2">
         <v>40</v>
       </c>
-      <c r="J64" s="5">
+      <c r="J64" s="2">
         <v>4</v>
       </c>
-      <c r="K64" s="5">
+      <c r="K64" s="2">
         <v>5</v>
       </c>
       <c r="L64" s="1">
@@ -5102,7 +5100,7 @@
         <v>30032</v>
       </c>
       <c r="D65" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E65" s="2">
         <v>3003</v>
@@ -5116,13 +5114,13 @@
       <c r="H65" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="I65" s="5">
+      <c r="I65" s="2">
         <v>40</v>
       </c>
-      <c r="J65" s="5">
+      <c r="J65" s="2">
         <v>4</v>
       </c>
-      <c r="K65" s="5">
+      <c r="K65" s="2">
         <v>5</v>
       </c>
       <c r="L65" s="1">
@@ -5170,7 +5168,7 @@
         <v>30042</v>
       </c>
       <c r="D66" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E66" s="2">
         <v>3004</v>
@@ -5184,13 +5182,13 @@
       <c r="H66" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="I66" s="5">
+      <c r="I66" s="2">
         <v>40</v>
       </c>
-      <c r="J66" s="5">
+      <c r="J66" s="2">
         <v>4</v>
       </c>
-      <c r="K66" s="5">
+      <c r="K66" s="2">
         <v>5</v>
       </c>
       <c r="L66" s="1">
@@ -5238,7 +5236,7 @@
         <v>30072</v>
       </c>
       <c r="D67" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E67" s="2">
         <v>3007</v>
@@ -5252,13 +5250,13 @@
       <c r="H67" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="I67" s="5">
+      <c r="I67" s="2">
         <v>40</v>
       </c>
-      <c r="J67" s="5">
+      <c r="J67" s="2">
         <v>4</v>
       </c>
-      <c r="K67" s="5">
+      <c r="K67" s="2">
         <v>5</v>
       </c>
       <c r="L67" s="1">
@@ -5304,9 +5302,9 @@
     <row r="68" s="1" customFormat="1" customHeight="1" spans="3:29">
       <c r="E68" s="2"/>
       <c r="F68" s="2"/>
-      <c r="I68" s="5"/>
-      <c r="J68" s="5"/>
-      <c r="K68" s="5"/>
+      <c r="I68" s="2"/>
+      <c r="J68" s="2"/>
+      <c r="K68" s="2"/>
       <c r="S68" s="2"/>
       <c r="T68" s="2"/>
       <c r="U68" s="2"/>
@@ -5317,7 +5315,7 @@
         <v>30023</v>
       </c>
       <c r="D69" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E69" s="2">
         <v>3002</v>
@@ -5331,13 +5329,13 @@
       <c r="H69" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="I69" s="5">
+      <c r="I69" s="2">
         <v>60</v>
       </c>
-      <c r="J69" s="5">
+      <c r="J69" s="2">
         <v>4</v>
       </c>
-      <c r="K69" s="5">
+      <c r="K69" s="2">
         <v>5</v>
       </c>
       <c r="L69" s="1">
@@ -5389,7 +5387,7 @@
         <v>30033</v>
       </c>
       <c r="D70" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E70" s="2">
         <v>3003</v>
@@ -5403,13 +5401,13 @@
       <c r="H70" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="I70" s="5">
+      <c r="I70" s="2">
         <v>60</v>
       </c>
-      <c r="J70" s="5">
+      <c r="J70" s="2">
         <v>4</v>
       </c>
-      <c r="K70" s="5">
+      <c r="K70" s="2">
         <v>5</v>
       </c>
       <c r="L70" s="1">
@@ -5461,7 +5459,7 @@
         <v>30043</v>
       </c>
       <c r="D71" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E71" s="2">
         <v>3004</v>
@@ -5475,13 +5473,13 @@
       <c r="H71" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="I71" s="5">
+      <c r="I71" s="2">
         <v>60</v>
       </c>
-      <c r="J71" s="5">
+      <c r="J71" s="2">
         <v>4</v>
       </c>
-      <c r="K71" s="5">
+      <c r="K71" s="2">
         <v>5</v>
       </c>
       <c r="L71" s="1">
@@ -5533,7 +5531,7 @@
         <v>30073</v>
       </c>
       <c r="D72" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E72" s="2">
         <v>3007</v>
@@ -5547,13 +5545,13 @@
       <c r="H72" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="I72" s="5">
+      <c r="I72" s="2">
         <v>60</v>
       </c>
-      <c r="J72" s="5">
+      <c r="J72" s="2">
         <v>4</v>
       </c>
-      <c r="K72" s="5">
+      <c r="K72" s="2">
         <v>5</v>
       </c>
       <c r="L72" s="1">
@@ -5605,9 +5603,9 @@
       <c r="D73" s="1"/>
       <c r="G73" s="1"/>
       <c r="H73" s="1"/>
-      <c r="I73" s="5"/>
-      <c r="J73" s="5"/>
-      <c r="K73" s="5"/>
+      <c r="I73" s="2"/>
+      <c r="J73" s="2"/>
+      <c r="K73" s="2"/>
       <c r="L73" s="1"/>
       <c r="M73" s="1"/>
       <c r="N73" s="1"/>
@@ -5631,7 +5629,7 @@
         <v>30024</v>
       </c>
       <c r="D74" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E74" s="2">
         <v>3002</v>
@@ -5645,13 +5643,13 @@
       <c r="H74" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="I74" s="6">
+      <c r="I74" s="2">
         <v>20</v>
       </c>
-      <c r="J74" s="6">
-        <v>5</v>
-      </c>
-      <c r="K74" s="6">
+      <c r="J74" s="2">
+        <v>5</v>
+      </c>
+      <c r="K74" s="2">
         <v>5</v>
       </c>
       <c r="L74" s="1">
@@ -5703,7 +5701,7 @@
         <v>30034</v>
       </c>
       <c r="D75" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E75" s="2">
         <v>3003</v>
@@ -5717,13 +5715,13 @@
       <c r="H75" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="I75" s="6">
+      <c r="I75" s="2">
         <v>20</v>
       </c>
-      <c r="J75" s="6">
-        <v>5</v>
-      </c>
-      <c r="K75" s="6">
+      <c r="J75" s="2">
+        <v>5</v>
+      </c>
+      <c r="K75" s="2">
         <v>5</v>
       </c>
       <c r="L75" s="1">
@@ -5775,7 +5773,7 @@
         <v>30044</v>
       </c>
       <c r="D76" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E76" s="2">
         <v>3004</v>
@@ -5789,13 +5787,13 @@
       <c r="H76" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="I76" s="6">
+      <c r="I76" s="2">
         <v>20</v>
       </c>
-      <c r="J76" s="6">
-        <v>5</v>
-      </c>
-      <c r="K76" s="6">
+      <c r="J76" s="2">
+        <v>5</v>
+      </c>
+      <c r="K76" s="2">
         <v>5</v>
       </c>
       <c r="L76" s="1">
@@ -5847,7 +5845,7 @@
         <v>30074</v>
       </c>
       <c r="D77" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E77" s="2">
         <v>3007</v>
@@ -5861,13 +5859,13 @@
       <c r="H77" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="I77" s="6">
+      <c r="I77" s="2">
         <v>20</v>
       </c>
-      <c r="J77" s="6">
-        <v>5</v>
-      </c>
-      <c r="K77" s="6">
+      <c r="J77" s="2">
+        <v>5</v>
+      </c>
+      <c r="K77" s="2">
         <v>5</v>
       </c>
       <c r="L77" s="1">
@@ -5912,7 +5910,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="L3:L5 C3:H5 I3:K5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:L5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/SkillSuitConfig.xlsx
+++ b/Excel/SkillSuitConfig.xlsx
@@ -145,7 +145,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AH4" authorId="1">
+    <comment ref="AI4" authorId="1">
       <text>
         <r>
           <rPr>
@@ -174,7 +174,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="92">
   <si>
     <t>_ID</t>
   </si>
@@ -261,6 +261,9 @@
   </si>
   <si>
     <t>附带效果</t>
+  </si>
+  <si>
+    <t>EffectDuration</t>
   </si>
   <si>
     <t>Id</t>
@@ -1423,7 +1426,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:AH77"/>
+  <dimension ref="C3:AI77"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="6" width="9" style="1"/>
@@ -1443,12 +1446,12 @@
     <col min="26" max="26" width="12.625" style="1" customWidth="1"/>
     <col min="27" max="27" width="9" style="1" customWidth="1"/>
     <col min="29" max="29" width="9.75" style="1" customWidth="1"/>
-    <col min="30" max="35" width="9" style="1"/>
-    <col min="36" max="36" width="19.25" style="1" customWidth="1"/>
-    <col min="37" max="16384" width="9" style="1"/>
+    <col min="30" max="36" width="9" style="1"/>
+    <col min="37" max="37" width="19.25" style="1" customWidth="1"/>
+    <col min="38" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:34">
+    <row r="3" s="1" customFormat="1" customHeight="1" spans="3:35">
       <c r="C3" s="4" t="s">
         <v>0</v>
       </c>
@@ -1538,24 +1541,27 @@
         <v>28</v>
       </c>
       <c r="AG3" s="4"/>
-      <c r="AH3" s="4"/>
-    </row>
-    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:34">
+      <c r="AH3" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="AI3" s="4"/>
+    </row>
+    <row r="4" s="1" customFormat="1" customHeight="1" spans="3:35">
       <c r="C4" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>1</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F4" s="4"/>
       <c r="G4" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I4" s="4" t="s">
         <v>5</v>
@@ -1567,52 +1573,52 @@
         <v>7</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M4" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N4" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="O4" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="P4" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="R4" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="S4" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="U4" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="V4" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="W4" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="X4" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="Y4" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="Z4" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="AA4" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="AB4" s="4" t="s">
         <v>24</v>
@@ -1621,118 +1627,124 @@
         <v>25</v>
       </c>
       <c r="AD4" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AE4" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AF4" s="4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="AG4" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="AH4" s="4" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:34">
+        <v>29</v>
+      </c>
+      <c r="AI4" s="4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" customHeight="1" spans="3:35">
       <c r="C5" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F5" s="4"/>
       <c r="G5" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="I5" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="J5" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="I5" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>54</v>
-      </c>
       <c r="K5" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="L5" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="M5" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="N5" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="O5" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="P5" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="R5" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="S5" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="U5" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="V5" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="W5" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="X5" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="Y5" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="Z5" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AA5" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AB5" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AC5" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AD5" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AE5" s="4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AF5" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AG5" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AH5" s="4" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:34">
+        <v>55</v>
+      </c>
+      <c r="AI5" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" customHeight="1" spans="3:35">
       <c r="C6" s="1">
         <v>10011</v>
       </c>
@@ -1743,13 +1755,13 @@
         <v>1001</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I6" s="2">
         <v>100</v>
@@ -1800,7 +1812,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:34">
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="3:35">
       <c r="C7" s="1">
         <v>10021</v>
       </c>
@@ -1811,13 +1823,13 @@
         <v>1002</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I7" s="2">
         <v>100</v>
@@ -1871,7 +1883,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:34">
+    <row r="8" s="1" customFormat="1" customHeight="1" spans="3:35">
       <c r="C8" s="1">
         <v>10031</v>
       </c>
@@ -1882,13 +1894,13 @@
         <v>1003</v>
       </c>
       <c r="F8" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="H8" s="1" t="s">
         <v>62</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>61</v>
       </c>
       <c r="I8" s="2">
         <v>100</v>
@@ -1942,7 +1954,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:34">
+    <row r="9" s="1" customFormat="1" customHeight="1" spans="3:35">
       <c r="C9" s="1">
         <v>10041</v>
       </c>
@@ -1953,13 +1965,13 @@
         <v>1004</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I9" s="2">
         <v>100</v>
@@ -2013,7 +2025,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:34">
+    <row r="10" s="1" customFormat="1" customHeight="1" spans="3:35">
       <c r="C10" s="1">
         <v>10051</v>
       </c>
@@ -2024,13 +2036,13 @@
         <v>1005</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I10" s="2">
         <v>100</v>
@@ -2084,7 +2096,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:34">
+    <row r="11" s="1" customFormat="1" customHeight="1" spans="3:35">
       <c r="C11" s="1">
         <v>10061</v>
       </c>
@@ -2095,13 +2107,13 @@
         <v>1006</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I11" s="2">
         <v>100</v>
@@ -2155,7 +2167,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:34">
+    <row r="12" s="1" customFormat="1" customHeight="1" spans="3:35">
       <c r="C12" s="1">
         <v>10071</v>
       </c>
@@ -2166,13 +2178,13 @@
         <v>1007</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I12" s="2">
         <v>100</v>
@@ -2226,7 +2238,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:34">
+    <row r="13" s="1" customFormat="1" customHeight="1" spans="3:35">
       <c r="F13" s="2"/>
       <c r="G13" s="1"/>
       <c r="H13" s="1"/>
@@ -2239,7 +2251,7 @@
       <c r="O13" s="1"/>
       <c r="Z13" s="2"/>
     </row>
-    <row r="14" s="1" customFormat="1" customHeight="1" spans="3:34">
+    <row r="14" s="1" customFormat="1" customHeight="1" spans="3:35">
       <c r="C14" s="1">
         <v>10022</v>
       </c>
@@ -2250,13 +2262,13 @@
         <v>1002</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I14" s="2">
         <v>40</v>
@@ -2307,7 +2319,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" s="1" customFormat="1" customHeight="1" spans="3:34">
+    <row r="15" s="1" customFormat="1" customHeight="1" spans="3:35">
       <c r="C15" s="1">
         <v>10032</v>
       </c>
@@ -2318,13 +2330,13 @@
         <v>1003</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I15" s="2">
         <v>40</v>
@@ -2375,7 +2387,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" s="1" customFormat="1" customHeight="1" spans="3:34">
+    <row r="16" s="1" customFormat="1" customHeight="1" spans="3:35">
       <c r="C16" s="1">
         <v>10042</v>
       </c>
@@ -2386,13 +2398,13 @@
         <v>1004</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I16" s="2">
         <v>40</v>
@@ -2454,13 +2466,13 @@
         <v>1007</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I17" s="2">
         <v>40</v>
@@ -2533,13 +2545,13 @@
         <v>1002</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I19" s="2">
         <v>60</v>
@@ -2605,13 +2617,13 @@
         <v>1003</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I20" s="2">
         <v>60</v>
@@ -2677,13 +2689,13 @@
         <v>1004</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I21" s="2">
         <v>60</v>
@@ -2749,13 +2761,13 @@
         <v>1007</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I22" s="2">
         <v>60</v>
@@ -2849,13 +2861,13 @@
         <v>1002</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I24" s="2">
         <v>20</v>
@@ -2921,13 +2933,13 @@
         <v>1003</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I25" s="2">
         <v>20</v>
@@ -2993,13 +3005,13 @@
         <v>1004</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I26" s="2">
         <v>20</v>
@@ -3065,13 +3077,13 @@
         <v>1007</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I27" s="2">
         <v>20</v>
@@ -3144,13 +3156,13 @@
         <v>2001</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I31" s="2">
         <v>100</v>
@@ -3212,13 +3224,13 @@
         <v>2002</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I32" s="2">
         <v>100</v>
@@ -3283,13 +3295,13 @@
         <v>2003</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I33" s="2">
         <v>100</v>
@@ -3354,13 +3366,13 @@
         <v>2004</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I34" s="2">
         <v>100</v>
@@ -3425,13 +3437,13 @@
         <v>2005</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I35" s="2">
         <v>100</v>
@@ -3496,13 +3508,13 @@
         <v>2006</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I36" s="2">
         <v>100</v>
@@ -3567,13 +3579,13 @@
         <v>2007</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I37" s="2">
         <v>100</v>
@@ -3645,13 +3657,13 @@
         <v>2002</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I39" s="2">
         <v>40</v>
@@ -3713,13 +3725,13 @@
         <v>2003</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I40" s="2">
         <v>40</v>
@@ -3781,13 +3793,13 @@
         <v>2004</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I41" s="2">
         <v>40</v>
@@ -3849,13 +3861,13 @@
         <v>2007</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I42" s="2">
         <v>40</v>
@@ -3928,13 +3940,13 @@
         <v>2002</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I44" s="2">
         <v>60</v>
@@ -4000,13 +4012,13 @@
         <v>2003</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I45" s="2">
         <v>60</v>
@@ -4072,13 +4084,13 @@
         <v>2004</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I46" s="2">
         <v>60</v>
@@ -4144,13 +4156,13 @@
         <v>2007</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I47" s="2">
         <v>60</v>
@@ -4242,13 +4254,13 @@
         <v>2002</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I49" s="2">
         <v>20</v>
@@ -4314,13 +4326,13 @@
         <v>2003</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I50" s="2">
         <v>20</v>
@@ -4386,13 +4398,13 @@
         <v>2004</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I51" s="2">
         <v>20</v>
@@ -4458,13 +4470,13 @@
         <v>2007</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I52" s="2">
         <v>20</v>
@@ -4537,13 +4549,13 @@
         <v>3001</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="I56" s="2">
         <v>100</v>
@@ -4605,13 +4617,13 @@
         <v>3002</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I57" s="2">
         <v>100</v>
@@ -4676,13 +4688,13 @@
         <v>3003</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I58" s="2">
         <v>100</v>
@@ -4747,13 +4759,13 @@
         <v>3004</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I59" s="2">
         <v>100</v>
@@ -4818,13 +4830,13 @@
         <v>3005</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I60" s="2">
         <v>100</v>
@@ -4889,13 +4901,13 @@
         <v>3006</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I61" s="2">
         <v>100</v>
@@ -4960,13 +4972,13 @@
         <v>3007</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="I62" s="2">
         <v>100</v>
@@ -5038,13 +5050,13 @@
         <v>3002</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I64" s="2">
         <v>40</v>
@@ -5106,13 +5118,13 @@
         <v>3003</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I65" s="2">
         <v>40</v>
@@ -5174,13 +5186,13 @@
         <v>3004</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H66" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I66" s="2">
         <v>40</v>
@@ -5242,13 +5254,13 @@
         <v>3007</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="I67" s="2">
         <v>40</v>
@@ -5321,13 +5333,13 @@
         <v>3002</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I69" s="2">
         <v>60</v>
@@ -5393,13 +5405,13 @@
         <v>3003</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I70" s="2">
         <v>60</v>
@@ -5465,13 +5477,13 @@
         <v>3004</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="I71" s="2">
         <v>60</v>
@@ -5537,13 +5549,13 @@
         <v>3007</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H72" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I72" s="2">
         <v>60</v>
@@ -5635,13 +5647,13 @@
         <v>3002</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H74" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I74" s="2">
         <v>20</v>
@@ -5707,13 +5719,13 @@
         <v>3003</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H75" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I75" s="2">
         <v>20</v>
@@ -5779,13 +5791,13 @@
         <v>3004</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I76" s="2">
         <v>20</v>
@@ -5851,13 +5863,13 @@
         <v>3007</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H77" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="I77" s="2">
         <v>20</v>

--- a/Excel/SkillSuitConfig.xlsx
+++ b/Excel/SkillSuitConfig.xlsx
@@ -174,7 +174,10 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="97">
+  <si>
+    <t>#</t>
+  </si>
   <si>
     <t>_ID</t>
   </si>
@@ -362,7 +365,7 @@
     <t>流光剑诀</t>
   </si>
   <si>
-    <t>增加{1}点技能系数</t>
+    <t>增加{1}%技能系数</t>
   </si>
   <si>
     <t>四方剑阵</t>
@@ -371,7 +374,13 @@
     <t>重击剑术</t>
   </si>
   <si>
-    <t>武神盾</t>
+    <t>龙魂护体</t>
+  </si>
+  <si>
+    <t>·千重</t>
+  </si>
+  <si>
+    <t>增加{1}%的护盾值</t>
   </si>
   <si>
     <t>无求易决</t>
@@ -386,6 +395,12 @@
     <t>增加{5}%技能攻击</t>
   </si>
   <si>
+    <t>·壁垒</t>
+  </si>
+  <si>
+    <t>增加{5}%的护盾最终血量</t>
+  </si>
+  <si>
     <t>·终伤</t>
   </si>
   <si>
@@ -413,7 +428,7 @@
     <t>烈焰术</t>
   </si>
   <si>
-    <t>念力盾</t>
+    <t>炎凰法盾</t>
   </si>
   <si>
     <t>冰心诀</t>
@@ -437,7 +452,7 @@
     <t>疗伤术</t>
   </si>
   <si>
-    <t>护魂盾</t>
+    <t>太虚麟盾</t>
   </si>
   <si>
     <t>圣心诀</t>
@@ -1426,7 +1441,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:AI77"/>
+  <dimension ref="C1:AI81"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="6" width="9" style="1"/>
@@ -1451,297 +1466,307 @@
     <col min="38" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
+    <row r="1" customHeight="1" spans="3:35">
+      <c r="F1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" customHeight="1" spans="3:35">
+      <c r="F2" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
     <row r="3" s="1" customFormat="1" customHeight="1" spans="3:35">
       <c r="C3" s="4" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F3" s="4"/>
       <c r="G3" s="4" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L3" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M3" s="4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N3" s="4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O3" s="4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="P3" s="4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R3" s="4" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="S3" s="4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="T3" s="4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="U3" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="V3" s="4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="W3" s="4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="X3" s="4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="Y3" s="4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="Z3" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AA3" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AB3" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AC3" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AD3" s="4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AE3" s="4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AF3" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AG3" s="4"/>
       <c r="AH3" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AI3" s="4"/>
     </row>
     <row r="4" s="1" customFormat="1" customHeight="1" spans="3:35">
       <c r="C4" s="4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F4" s="4"/>
       <c r="G4" s="4" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M4" s="4" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="N4" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="O4" s="4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="P4" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="R4" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="S4" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="U4" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="V4" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="W4" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="X4" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="Y4" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="Z4" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="AA4" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="AB4" s="4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AC4" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AD4" s="4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="AE4" s="4" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="AF4" s="4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="AG4" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="AH4" s="4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AI4" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" customHeight="1" spans="3:35">
       <c r="C5" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F5" s="4"/>
       <c r="G5" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="I5" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="J5" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="I5" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="J5" s="4" t="s">
-        <v>55</v>
-      </c>
       <c r="K5" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L5" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="M5" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="N5" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="O5" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="P5" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="R5" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="S5" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="U5" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="V5" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="W5" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="X5" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="Y5" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="Z5" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AA5" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AB5" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AC5" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AD5" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AE5" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="AF5" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AG5" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AH5" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AI5" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6" s="1" customFormat="1" customHeight="1" spans="3:35">
@@ -1755,13 +1780,13 @@
         <v>1001</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="I6" s="2">
         <v>100</v>
@@ -1823,13 +1848,13 @@
         <v>1002</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I7" s="2">
         <v>100</v>
@@ -1894,13 +1919,13 @@
         <v>1003</v>
       </c>
       <c r="F8" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="H8" s="1" t="s">
         <v>63</v>
-      </c>
-      <c r="G8" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>62</v>
       </c>
       <c r="I8" s="2">
         <v>100</v>
@@ -1965,13 +1990,13 @@
         <v>1004</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I9" s="2">
         <v>100</v>
@@ -2036,13 +2061,13 @@
         <v>1005</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="I10" s="2">
         <v>100</v>
@@ -2075,7 +2100,7 @@
         <v>0</v>
       </c>
       <c r="S10" s="2">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" s="2"/>
       <c r="U10" s="2"/>
@@ -2107,13 +2132,13 @@
         <v>1006</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I11" s="2">
         <v>100</v>
@@ -2178,13 +2203,13 @@
         <v>1007</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I12" s="2">
         <v>100</v>
@@ -2252,91 +2277,30 @@
       <c r="Z13" s="2"/>
     </row>
     <row r="14" s="1" customFormat="1" customHeight="1" spans="3:35">
-      <c r="C14" s="1">
-        <v>10022</v>
-      </c>
-      <c r="D14" s="1">
-        <v>1</v>
-      </c>
-      <c r="E14" s="2">
-        <v>1002</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="G14" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="H14" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="I14" s="2">
-        <v>40</v>
-      </c>
-      <c r="J14" s="2">
-        <v>4</v>
-      </c>
-      <c r="K14" s="2">
-        <v>5</v>
-      </c>
-      <c r="L14" s="1">
-        <v>0</v>
-      </c>
-      <c r="M14" s="1">
-        <v>0</v>
-      </c>
-      <c r="N14" s="1">
-        <v>0</v>
-      </c>
-      <c r="O14" s="1">
-        <v>0</v>
-      </c>
-      <c r="P14" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="1">
-        <v>0</v>
-      </c>
-      <c r="R14" s="1">
-        <v>0</v>
-      </c>
-      <c r="S14" s="1">
-        <v>0</v>
-      </c>
-      <c r="W14" s="1">
-        <v>0</v>
-      </c>
-      <c r="X14" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y14" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z14" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA14" s="1">
-        <v>0</v>
-      </c>
+      <c r="F14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
+      <c r="K14" s="2"/>
+      <c r="Z14" s="2"/>
     </row>
     <row r="15" s="1" customFormat="1" customHeight="1" spans="3:35">
       <c r="C15" s="1">
-        <v>10032</v>
+        <v>10022</v>
       </c>
       <c r="D15" s="1">
         <v>1</v>
       </c>
       <c r="E15" s="2">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="I15" s="2">
         <v>40</v>
@@ -2389,22 +2353,22 @@
     </row>
     <row r="16" s="1" customFormat="1" customHeight="1" spans="3:35">
       <c r="C16" s="1">
-        <v>10042</v>
+        <v>10032</v>
       </c>
       <c r="D16" s="1">
         <v>1</v>
       </c>
       <c r="E16" s="2">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>64</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="I16" s="2">
         <v>40</v>
@@ -2457,104 +2421,164 @@
     </row>
     <row r="17" s="1" customFormat="1" customHeight="1" spans="3:29">
       <c r="C17" s="1">
-        <v>10072</v>
+        <v>10052</v>
       </c>
       <c r="D17" s="1">
         <v>1</v>
       </c>
       <c r="E17" s="2">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="I17" s="2">
+        <v>100</v>
+      </c>
+      <c r="J17" s="2">
+        <v>1</v>
+      </c>
+      <c r="K17" s="2">
+        <v>5</v>
+      </c>
+      <c r="L17" s="1">
+        <v>0</v>
+      </c>
+      <c r="M17" s="1">
+        <v>0</v>
+      </c>
+      <c r="N17" s="1">
+        <v>0</v>
+      </c>
+      <c r="O17" s="1">
+        <v>0</v>
+      </c>
+      <c r="P17" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="1">
+        <v>0</v>
+      </c>
+      <c r="R17" s="1">
+        <v>0</v>
+      </c>
+      <c r="S17" s="2">
+        <v>0</v>
+      </c>
+      <c r="T17" s="2"/>
+      <c r="U17" s="2"/>
+      <c r="V17" s="2"/>
+      <c r="W17" s="1">
+        <v>0</v>
+      </c>
+      <c r="X17" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y17" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z17" s="1">
+        <v>20</v>
+      </c>
+      <c r="AA17" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" s="1" customFormat="1" customHeight="1" spans="3:29">
+      <c r="C18" s="1">
+        <v>10042</v>
+      </c>
+      <c r="D18" s="1">
+        <v>1</v>
+      </c>
+      <c r="E18" s="2">
+        <v>1004</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="I18" s="2">
         <v>40</v>
       </c>
-      <c r="J17" s="2">
+      <c r="J18" s="2">
         <v>4</v>
       </c>
-      <c r="K17" s="2">
-        <v>5</v>
-      </c>
-      <c r="L17" s="1">
-        <v>0</v>
-      </c>
-      <c r="M17" s="1">
-        <v>0</v>
-      </c>
-      <c r="N17" s="1">
-        <v>0</v>
-      </c>
-      <c r="O17" s="1">
-        <v>0</v>
-      </c>
-      <c r="P17" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q17" s="1">
-        <v>0</v>
-      </c>
-      <c r="R17" s="1">
-        <v>0</v>
-      </c>
-      <c r="S17" s="1">
-        <v>0</v>
-      </c>
-      <c r="W17" s="1">
-        <v>0</v>
-      </c>
-      <c r="X17" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y17" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z17" s="2">
+      <c r="K18" s="2">
+        <v>5</v>
+      </c>
+      <c r="L18" s="1">
+        <v>0</v>
+      </c>
+      <c r="M18" s="1">
+        <v>0</v>
+      </c>
+      <c r="N18" s="1">
+        <v>0</v>
+      </c>
+      <c r="O18" s="1">
+        <v>0</v>
+      </c>
+      <c r="P18" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="1">
+        <v>0</v>
+      </c>
+      <c r="R18" s="1">
+        <v>0</v>
+      </c>
+      <c r="S18" s="1">
+        <v>0</v>
+      </c>
+      <c r="W18" s="1">
+        <v>0</v>
+      </c>
+      <c r="X18" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y18" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z18" s="2">
         <v>20</v>
       </c>
-      <c r="AA17" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" s="1" customFormat="1" customHeight="1" spans="3:29">
-      <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
-      <c r="I18" s="2"/>
-      <c r="J18" s="2"/>
-      <c r="K18" s="2"/>
-      <c r="S18" s="2"/>
-      <c r="T18" s="2"/>
-      <c r="U18" s="2"/>
-      <c r="V18" s="2"/>
-    </row>
-    <row r="19" s="2" customFormat="1" customHeight="1" spans="3:29">
+      <c r="AA18" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" s="1" customFormat="1" customHeight="1" spans="3:29">
       <c r="C19" s="1">
-        <v>10023</v>
+        <v>10072</v>
       </c>
       <c r="D19" s="1">
         <v>1</v>
       </c>
       <c r="E19" s="2">
-        <v>1002</v>
+        <v>1007</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I19" s="2">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="J19" s="2">
         <v>4</v>
@@ -2586,9 +2610,6 @@
       <c r="S19" s="1">
         <v>0</v>
       </c>
-      <c r="T19" s="1"/>
-      <c r="U19" s="1"/>
-      <c r="V19" s="1"/>
       <c r="W19" s="1">
         <v>0</v>
       </c>
@@ -2598,104 +2619,42 @@
       <c r="Y19" s="1">
         <v>0</v>
       </c>
-      <c r="Z19" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA19" s="2">
+      <c r="Z19" s="2">
         <v>20</v>
       </c>
-      <c r="AC19" s="1"/>
-    </row>
-    <row r="20" s="2" customFormat="1" customHeight="1" spans="3:29">
-      <c r="C20" s="1">
-        <v>10033</v>
-      </c>
-      <c r="D20" s="1">
-        <v>1</v>
-      </c>
-      <c r="E20" s="2">
-        <v>1003</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="G20" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="H20" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="I20" s="2">
-        <v>60</v>
-      </c>
-      <c r="J20" s="2">
-        <v>4</v>
-      </c>
-      <c r="K20" s="2">
-        <v>5</v>
-      </c>
-      <c r="L20" s="1">
-        <v>0</v>
-      </c>
-      <c r="M20" s="1">
-        <v>0</v>
-      </c>
-      <c r="N20" s="1">
-        <v>0</v>
-      </c>
-      <c r="O20" s="1">
-        <v>0</v>
-      </c>
-      <c r="P20" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q20" s="1">
-        <v>0</v>
-      </c>
-      <c r="R20" s="1">
-        <v>0</v>
-      </c>
-      <c r="S20" s="1">
-        <v>0</v>
-      </c>
-      <c r="T20" s="1"/>
-      <c r="U20" s="1"/>
-      <c r="V20" s="1"/>
-      <c r="W20" s="1">
-        <v>0</v>
-      </c>
-      <c r="X20" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y20" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z20" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA20" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC20" s="1"/>
+      <c r="AA19" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" s="1" customFormat="1" customHeight="1" spans="3:29">
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="2"/>
+      <c r="K20" s="2"/>
+      <c r="S20" s="2"/>
+      <c r="T20" s="2"/>
+      <c r="U20" s="2"/>
+      <c r="V20" s="2"/>
     </row>
     <row r="21" s="2" customFormat="1" customHeight="1" spans="3:29">
       <c r="C21" s="1">
-        <v>10043</v>
+        <v>10023</v>
       </c>
       <c r="D21" s="1">
         <v>1</v>
       </c>
       <c r="E21" s="2">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="I21" s="2">
         <v>60</v>
@@ -2752,22 +2711,22 @@
     </row>
     <row r="22" s="2" customFormat="1" customHeight="1" spans="3:29">
       <c r="C22" s="1">
-        <v>10073</v>
+        <v>10033</v>
       </c>
       <c r="D22" s="1">
         <v>1</v>
       </c>
       <c r="E22" s="2">
-        <v>1007</v>
+        <v>1003</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="I22" s="2">
         <v>60</v>
@@ -2823,57 +2782,101 @@
       <c r="AC22" s="1"/>
     </row>
     <row r="23" s="2" customFormat="1" customHeight="1" spans="3:29">
-      <c r="C23" s="1"/>
-      <c r="D23" s="1"/>
-      <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
-      <c r="G23" s="1"/>
-      <c r="H23" s="1"/>
-      <c r="I23" s="2"/>
-      <c r="J23" s="2"/>
-      <c r="K23" s="2"/>
-      <c r="L23" s="1"/>
-      <c r="M23" s="1"/>
-      <c r="N23" s="1"/>
-      <c r="O23" s="1"/>
-      <c r="P23" s="1"/>
-      <c r="Q23" s="1"/>
-      <c r="R23" s="1"/>
-      <c r="S23" s="1"/>
+      <c r="C23" s="1">
+        <v>10043</v>
+      </c>
+      <c r="D23" s="1">
+        <v>1</v>
+      </c>
+      <c r="E23" s="2">
+        <v>1004</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="I23" s="2">
+        <v>60</v>
+      </c>
+      <c r="J23" s="2">
+        <v>4</v>
+      </c>
+      <c r="K23" s="2">
+        <v>5</v>
+      </c>
+      <c r="L23" s="1">
+        <v>0</v>
+      </c>
+      <c r="M23" s="1">
+        <v>0</v>
+      </c>
+      <c r="N23" s="1">
+        <v>0</v>
+      </c>
+      <c r="O23" s="1">
+        <v>0</v>
+      </c>
+      <c r="P23" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="1">
+        <v>0</v>
+      </c>
+      <c r="R23" s="1">
+        <v>0</v>
+      </c>
+      <c r="S23" s="1">
+        <v>0</v>
+      </c>
       <c r="T23" s="1"/>
       <c r="U23" s="1"/>
       <c r="V23" s="1"/>
-      <c r="W23" s="1"/>
-      <c r="X23" s="1"/>
-      <c r="Y23" s="1"/>
-      <c r="Z23" s="1"/>
-      <c r="AA23" s="1"/>
+      <c r="W23" s="1">
+        <v>0</v>
+      </c>
+      <c r="X23" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y23" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z23" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA23" s="2">
+        <v>20</v>
+      </c>
       <c r="AC23" s="1"/>
     </row>
     <row r="24" s="2" customFormat="1" customHeight="1" spans="3:29">
       <c r="C24" s="1">
-        <v>10024</v>
+        <v>10073</v>
       </c>
       <c r="D24" s="1">
         <v>1</v>
       </c>
       <c r="E24" s="2">
-        <v>1002</v>
+        <v>1007</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="I24" s="2">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="J24" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K24" s="2">
         <v>5</v>
@@ -2909,7 +2912,7 @@
         <v>0</v>
       </c>
       <c r="X24" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y24" s="1">
         <v>0</v>
@@ -2917,101 +2920,57 @@
       <c r="Z24" s="1">
         <v>0</v>
       </c>
-      <c r="AA24" s="1">
-        <v>0</v>
+      <c r="AA24" s="2">
+        <v>20</v>
       </c>
       <c r="AC24" s="1"/>
     </row>
     <row r="25" s="2" customFormat="1" customHeight="1" spans="3:29">
-      <c r="C25" s="1">
-        <v>10034</v>
-      </c>
-      <c r="D25" s="1">
-        <v>1</v>
-      </c>
-      <c r="E25" s="2">
-        <v>1003</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="G25" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="H25" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="I25" s="2">
-        <v>20</v>
-      </c>
-      <c r="J25" s="2">
-        <v>5</v>
-      </c>
-      <c r="K25" s="2">
-        <v>5</v>
-      </c>
-      <c r="L25" s="1">
-        <v>0</v>
-      </c>
-      <c r="M25" s="1">
-        <v>0</v>
-      </c>
-      <c r="N25" s="1">
-        <v>0</v>
-      </c>
-      <c r="O25" s="1">
-        <v>0</v>
-      </c>
-      <c r="P25" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q25" s="1">
-        <v>0</v>
-      </c>
-      <c r="R25" s="1">
-        <v>0</v>
-      </c>
-      <c r="S25" s="1">
-        <v>0</v>
-      </c>
+      <c r="C25" s="1"/>
+      <c r="D25" s="1"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="2"/>
+      <c r="G25" s="1"/>
+      <c r="H25" s="1"/>
+      <c r="I25" s="2"/>
+      <c r="J25" s="2"/>
+      <c r="K25" s="2"/>
+      <c r="L25" s="1"/>
+      <c r="M25" s="1"/>
+      <c r="N25" s="1"/>
+      <c r="O25" s="1"/>
+      <c r="P25" s="1"/>
+      <c r="Q25" s="1"/>
+      <c r="R25" s="1"/>
+      <c r="S25" s="1"/>
       <c r="T25" s="1"/>
       <c r="U25" s="1"/>
       <c r="V25" s="1"/>
-      <c r="W25" s="1">
-        <v>0</v>
-      </c>
-      <c r="X25" s="1">
-        <v>100</v>
-      </c>
-      <c r="Y25" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z25" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA25" s="1">
-        <v>0</v>
-      </c>
+      <c r="W25" s="1"/>
+      <c r="X25" s="1"/>
+      <c r="Y25" s="1"/>
+      <c r="Z25" s="1"/>
+      <c r="AA25" s="1"/>
       <c r="AC25" s="1"/>
     </row>
     <row r="26" s="2" customFormat="1" customHeight="1" spans="3:29">
       <c r="C26" s="1">
-        <v>10044</v>
+        <v>10024</v>
       </c>
       <c r="D26" s="1">
         <v>1</v>
       </c>
       <c r="E26" s="2">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="I26" s="2">
         <v>20</v>
@@ -3066,24 +3025,24 @@
       </c>
       <c r="AC26" s="1"/>
     </row>
-    <row r="27" s="1" customFormat="1" customHeight="1" spans="3:29">
+    <row r="27" s="2" customFormat="1" customHeight="1" spans="3:29">
       <c r="C27" s="1">
-        <v>10074</v>
+        <v>10034</v>
       </c>
       <c r="D27" s="1">
         <v>1</v>
       </c>
       <c r="E27" s="2">
-        <v>1007</v>
+        <v>1003</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="I27" s="2">
         <v>20</v>
@@ -3118,6 +3077,9 @@
       <c r="S27" s="1">
         <v>0</v>
       </c>
+      <c r="T27" s="1"/>
+      <c r="U27" s="1"/>
+      <c r="V27" s="1"/>
       <c r="W27" s="1">
         <v>0</v>
       </c>
@@ -3133,175 +3095,177 @@
       <c r="AA27" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" customHeight="1" spans="3:29">
-      <c r="I28" s="2"/>
-      <c r="J28" s="2"/>
-      <c r="K28" s="2"/>
-    </row>
-    <row r="29" s="3" customFormat="1" customHeight="1"/>
+      <c r="AC27" s="1"/>
+    </row>
+    <row r="28" s="2" customFormat="1" customHeight="1" spans="3:29">
+      <c r="C28" s="1">
+        <v>10044</v>
+      </c>
+      <c r="D28" s="1">
+        <v>1</v>
+      </c>
+      <c r="E28" s="2">
+        <v>1004</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="I28" s="2">
+        <v>20</v>
+      </c>
+      <c r="J28" s="2">
+        <v>5</v>
+      </c>
+      <c r="K28" s="2">
+        <v>5</v>
+      </c>
+      <c r="L28" s="1">
+        <v>0</v>
+      </c>
+      <c r="M28" s="1">
+        <v>0</v>
+      </c>
+      <c r="N28" s="1">
+        <v>0</v>
+      </c>
+      <c r="O28" s="1">
+        <v>0</v>
+      </c>
+      <c r="P28" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="1">
+        <v>0</v>
+      </c>
+      <c r="R28" s="1">
+        <v>0</v>
+      </c>
+      <c r="S28" s="1">
+        <v>0</v>
+      </c>
+      <c r="T28" s="1"/>
+      <c r="U28" s="1"/>
+      <c r="V28" s="1"/>
+      <c r="W28" s="1">
+        <v>0</v>
+      </c>
+      <c r="X28" s="1">
+        <v>100</v>
+      </c>
+      <c r="Y28" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z28" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA28" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC28" s="1"/>
+    </row>
+    <row r="29" s="1" customFormat="1" customHeight="1" spans="3:29">
+      <c r="C29" s="1">
+        <v>10074</v>
+      </c>
+      <c r="D29" s="1">
+        <v>1</v>
+      </c>
+      <c r="E29" s="2">
+        <v>1007</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="I29" s="2">
+        <v>20</v>
+      </c>
+      <c r="J29" s="2">
+        <v>5</v>
+      </c>
+      <c r="K29" s="2">
+        <v>5</v>
+      </c>
+      <c r="L29" s="1">
+        <v>0</v>
+      </c>
+      <c r="M29" s="1">
+        <v>0</v>
+      </c>
+      <c r="N29" s="1">
+        <v>0</v>
+      </c>
+      <c r="O29" s="1">
+        <v>0</v>
+      </c>
+      <c r="P29" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="1">
+        <v>0</v>
+      </c>
+      <c r="R29" s="1">
+        <v>0</v>
+      </c>
+      <c r="S29" s="1">
+        <v>0</v>
+      </c>
+      <c r="W29" s="1">
+        <v>0</v>
+      </c>
+      <c r="X29" s="1">
+        <v>100</v>
+      </c>
+      <c r="Y29" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA29" s="1">
+        <v>0</v>
+      </c>
+    </row>
     <row r="30" customHeight="1" spans="3:29">
       <c r="I30" s="2"/>
       <c r="J30" s="2"/>
       <c r="K30" s="2"/>
     </row>
-    <row r="31" s="1" customFormat="1" customHeight="1" spans="3:29">
-      <c r="C31" s="1">
-        <v>20011</v>
-      </c>
-      <c r="D31" s="1">
-        <v>2</v>
-      </c>
-      <c r="E31" s="2">
-        <v>2001</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="G31" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="H31" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="I31" s="2">
-        <v>100</v>
-      </c>
-      <c r="J31" s="2">
-        <v>1</v>
-      </c>
-      <c r="K31" s="2">
-        <v>5</v>
-      </c>
-      <c r="L31" s="1">
-        <v>0</v>
-      </c>
-      <c r="M31" s="1">
-        <v>0</v>
-      </c>
-      <c r="N31" s="1">
-        <v>0</v>
-      </c>
-      <c r="O31" s="1">
-        <v>0</v>
-      </c>
-      <c r="P31" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q31" s="1">
-        <v>0</v>
-      </c>
-      <c r="R31" s="1">
-        <v>0</v>
-      </c>
-      <c r="S31" s="1">
-        <v>5</v>
-      </c>
-      <c r="W31" s="1">
-        <v>0</v>
-      </c>
-      <c r="X31" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y31" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z31" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA31" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" s="1" customFormat="1" customHeight="1" spans="3:29">
-      <c r="C32" s="1">
-        <v>20021</v>
-      </c>
-      <c r="D32" s="1">
-        <v>2</v>
-      </c>
-      <c r="E32" s="2">
-        <v>2002</v>
-      </c>
-      <c r="F32" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G32" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="H32" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="I32" s="2">
-        <v>100</v>
-      </c>
-      <c r="J32" s="2">
-        <v>1</v>
-      </c>
-      <c r="K32" s="2">
-        <v>5</v>
-      </c>
-      <c r="L32" s="1">
-        <v>0</v>
-      </c>
-      <c r="M32" s="1">
-        <v>0</v>
-      </c>
-      <c r="N32" s="1">
-        <v>0</v>
-      </c>
-      <c r="O32" s="1">
-        <v>0</v>
-      </c>
-      <c r="P32" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q32" s="1">
-        <v>0</v>
-      </c>
-      <c r="R32" s="1">
-        <v>0</v>
-      </c>
-      <c r="S32" s="2">
-        <v>20</v>
-      </c>
-      <c r="T32" s="2"/>
-      <c r="U32" s="2"/>
-      <c r="V32" s="2"/>
-      <c r="W32" s="1">
-        <v>0</v>
-      </c>
-      <c r="X32" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y32" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z32" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA32" s="1">
-        <v>0</v>
-      </c>
+    <row r="31" s="3" customFormat="1" customHeight="1"/>
+    <row r="32" customHeight="1" spans="3:29">
+      <c r="I32" s="2"/>
+      <c r="J32" s="2"/>
+      <c r="K32" s="2"/>
     </row>
     <row r="33" s="1" customFormat="1" customHeight="1" spans="3:29">
       <c r="C33" s="1">
-        <v>20031</v>
+        <v>20011</v>
       </c>
       <c r="D33" s="1">
         <v>2</v>
       </c>
       <c r="E33" s="2">
-        <v>2003</v>
+        <v>2001</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="I33" s="2">
         <v>100</v>
@@ -3333,12 +3297,9 @@
       <c r="R33" s="1">
         <v>0</v>
       </c>
-      <c r="S33" s="2">
-        <v>20</v>
-      </c>
-      <c r="T33" s="2"/>
-      <c r="U33" s="2"/>
-      <c r="V33" s="2"/>
+      <c r="S33" s="1">
+        <v>5</v>
+      </c>
       <c r="W33" s="1">
         <v>0</v>
       </c>
@@ -3357,22 +3318,22 @@
     </row>
     <row r="34" s="1" customFormat="1" customHeight="1" spans="3:29">
       <c r="C34" s="1">
-        <v>20041</v>
+        <v>20021</v>
       </c>
       <c r="D34" s="1">
         <v>2</v>
       </c>
       <c r="E34" s="2">
-        <v>2004</v>
+        <v>2002</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I34" s="2">
         <v>100</v>
@@ -3428,22 +3389,22 @@
     </row>
     <row r="35" s="1" customFormat="1" customHeight="1" spans="3:29">
       <c r="C35" s="1">
-        <v>20051</v>
+        <v>20031</v>
       </c>
       <c r="D35" s="1">
         <v>2</v>
       </c>
       <c r="E35" s="2">
-        <v>2005</v>
+        <v>2003</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I35" s="2">
         <v>100</v>
@@ -3476,7 +3437,7 @@
         <v>0</v>
       </c>
       <c r="S35" s="2">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T35" s="2"/>
       <c r="U35" s="2"/>
@@ -3499,22 +3460,22 @@
     </row>
     <row r="36" s="1" customFormat="1" customHeight="1" spans="3:29">
       <c r="C36" s="1">
-        <v>20061</v>
+        <v>20041</v>
       </c>
       <c r="D36" s="1">
         <v>2</v>
       </c>
       <c r="E36" s="2">
-        <v>2006</v>
+        <v>2004</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I36" s="2">
         <v>100</v>
@@ -3547,7 +3508,7 @@
         <v>0</v>
       </c>
       <c r="S36" s="2">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T36" s="2"/>
       <c r="U36" s="2"/>
@@ -3570,22 +3531,22 @@
     </row>
     <row r="37" s="1" customFormat="1" customHeight="1" spans="3:29">
       <c r="C37" s="1">
-        <v>20071</v>
+        <v>20051</v>
       </c>
       <c r="D37" s="1">
         <v>2</v>
       </c>
       <c r="E37" s="2">
-        <v>2007</v>
+        <v>2005</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="I37" s="2">
         <v>100</v>
@@ -3618,7 +3579,7 @@
         <v>0</v>
       </c>
       <c r="S37" s="2">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T37" s="2"/>
       <c r="U37" s="2"/>
@@ -3640,36 +3601,100 @@
       </c>
     </row>
     <row r="38" s="1" customFormat="1" customHeight="1" spans="3:29">
-      <c r="F38" s="2"/>
-      <c r="I38" s="2"/>
-      <c r="J38" s="2"/>
-      <c r="K38" s="2"/>
-      <c r="Z38" s="2"/>
+      <c r="C38" s="1">
+        <v>20061</v>
+      </c>
+      <c r="D38" s="1">
+        <v>2</v>
+      </c>
+      <c r="E38" s="2">
+        <v>2006</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="I38" s="2">
+        <v>100</v>
+      </c>
+      <c r="J38" s="2">
+        <v>1</v>
+      </c>
+      <c r="K38" s="2">
+        <v>5</v>
+      </c>
+      <c r="L38" s="1">
+        <v>0</v>
+      </c>
+      <c r="M38" s="1">
+        <v>0</v>
+      </c>
+      <c r="N38" s="1">
+        <v>0</v>
+      </c>
+      <c r="O38" s="1">
+        <v>0</v>
+      </c>
+      <c r="P38" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q38" s="1">
+        <v>0</v>
+      </c>
+      <c r="R38" s="1">
+        <v>0</v>
+      </c>
+      <c r="S38" s="2">
+        <v>5</v>
+      </c>
+      <c r="T38" s="2"/>
+      <c r="U38" s="2"/>
+      <c r="V38" s="2"/>
+      <c r="W38" s="1">
+        <v>0</v>
+      </c>
+      <c r="X38" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y38" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z38" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA38" s="1">
+        <v>0</v>
+      </c>
     </row>
     <row r="39" s="1" customFormat="1" customHeight="1" spans="3:29">
       <c r="C39" s="1">
-        <v>20022</v>
+        <v>20071</v>
       </c>
       <c r="D39" s="1">
         <v>2</v>
       </c>
       <c r="E39" s="2">
-        <v>2002</v>
+        <v>2007</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="I39" s="2">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="J39" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K39" s="2">
         <v>5</v>
@@ -3695,9 +3720,12 @@
       <c r="R39" s="1">
         <v>0</v>
       </c>
-      <c r="S39" s="1">
-        <v>0</v>
-      </c>
+      <c r="S39" s="2">
+        <v>20</v>
+      </c>
+      <c r="T39" s="2"/>
+      <c r="U39" s="2"/>
+      <c r="V39" s="2"/>
       <c r="W39" s="1">
         <v>0</v>
       </c>
@@ -3707,99 +3735,38 @@
       <c r="Y39" s="1">
         <v>0</v>
       </c>
-      <c r="Z39" s="2">
-        <v>20</v>
+      <c r="Z39" s="1">
+        <v>0</v>
       </c>
       <c r="AA39" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="40" s="1" customFormat="1" customHeight="1" spans="3:29">
-      <c r="C40" s="1">
-        <v>20032</v>
-      </c>
-      <c r="D40" s="1">
-        <v>2</v>
-      </c>
-      <c r="E40" s="2">
-        <v>2003</v>
-      </c>
-      <c r="F40" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G40" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="H40" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="I40" s="2">
-        <v>40</v>
-      </c>
-      <c r="J40" s="2">
-        <v>4</v>
-      </c>
-      <c r="K40" s="2">
-        <v>5</v>
-      </c>
-      <c r="L40" s="1">
-        <v>0</v>
-      </c>
-      <c r="M40" s="1">
-        <v>0</v>
-      </c>
-      <c r="N40" s="1">
-        <v>0</v>
-      </c>
-      <c r="O40" s="1">
-        <v>0</v>
-      </c>
-      <c r="P40" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q40" s="1">
-        <v>0</v>
-      </c>
-      <c r="R40" s="1">
-        <v>0</v>
-      </c>
-      <c r="S40" s="1">
-        <v>0</v>
-      </c>
-      <c r="W40" s="1">
-        <v>0</v>
-      </c>
-      <c r="X40" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y40" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z40" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA40" s="1">
-        <v>0</v>
-      </c>
+      <c r="F40" s="2"/>
+      <c r="I40" s="2"/>
+      <c r="J40" s="2"/>
+      <c r="K40" s="2"/>
+      <c r="Z40" s="2"/>
     </row>
     <row r="41" s="1" customFormat="1" customHeight="1" spans="3:29">
       <c r="C41" s="1">
-        <v>20042</v>
+        <v>20022</v>
       </c>
       <c r="D41" s="1">
         <v>2</v>
       </c>
       <c r="E41" s="2">
-        <v>2004</v>
+        <v>2002</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="I41" s="2">
         <v>40</v>
@@ -3852,22 +3819,22 @@
     </row>
     <row r="42" s="1" customFormat="1" customHeight="1" spans="3:29">
       <c r="C42" s="1">
-        <v>20072</v>
+        <v>20032</v>
       </c>
       <c r="D42" s="1">
         <v>2</v>
       </c>
       <c r="E42" s="2">
-        <v>2007</v>
+        <v>2003</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="I42" s="2">
         <v>40</v>
@@ -3919,37 +3886,97 @@
       </c>
     </row>
     <row r="43" s="1" customFormat="1" customHeight="1" spans="3:29">
-      <c r="E43" s="2"/>
-      <c r="F43" s="2"/>
-      <c r="I43" s="2"/>
-      <c r="J43" s="2"/>
-      <c r="K43" s="2"/>
-      <c r="S43" s="2"/>
+      <c r="C43" s="1">
+        <v>20052</v>
+      </c>
+      <c r="D43" s="1">
+        <v>1</v>
+      </c>
+      <c r="E43" s="2">
+        <v>2005</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="H43" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="I43" s="2">
+        <v>100</v>
+      </c>
+      <c r="J43" s="2">
+        <v>1</v>
+      </c>
+      <c r="K43" s="2">
+        <v>5</v>
+      </c>
+      <c r="L43" s="1">
+        <v>0</v>
+      </c>
+      <c r="M43" s="1">
+        <v>0</v>
+      </c>
+      <c r="N43" s="1">
+        <v>0</v>
+      </c>
+      <c r="O43" s="1">
+        <v>0</v>
+      </c>
+      <c r="P43" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="1">
+        <v>0</v>
+      </c>
+      <c r="R43" s="1">
+        <v>0</v>
+      </c>
+      <c r="S43" s="2">
+        <v>0</v>
+      </c>
       <c r="T43" s="2"/>
       <c r="U43" s="2"/>
       <c r="V43" s="2"/>
-    </row>
-    <row r="44" s="2" customFormat="1" customHeight="1" spans="3:29">
+      <c r="W43" s="1">
+        <v>0</v>
+      </c>
+      <c r="X43" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y43" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z43" s="1">
+        <v>20</v>
+      </c>
+      <c r="AA43" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" s="1" customFormat="1" customHeight="1" spans="3:29">
       <c r="C44" s="1">
-        <v>20023</v>
+        <v>20042</v>
       </c>
       <c r="D44" s="1">
         <v>2</v>
       </c>
       <c r="E44" s="2">
-        <v>2002</v>
+        <v>2004</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I44" s="2">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="J44" s="2">
         <v>4</v>
@@ -3981,9 +4008,6 @@
       <c r="S44" s="1">
         <v>0</v>
       </c>
-      <c r="T44" s="1"/>
-      <c r="U44" s="1"/>
-      <c r="V44" s="1"/>
       <c r="W44" s="1">
         <v>0</v>
       </c>
@@ -3993,35 +4017,34 @@
       <c r="Y44" s="1">
         <v>0</v>
       </c>
-      <c r="Z44" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA44" s="2">
+      <c r="Z44" s="2">
         <v>20</v>
       </c>
-      <c r="AC44" s="1"/>
-    </row>
-    <row r="45" s="2" customFormat="1" customHeight="1" spans="3:29">
+      <c r="AA44" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" s="1" customFormat="1" customHeight="1" spans="3:29">
       <c r="C45" s="1">
-        <v>20033</v>
+        <v>20072</v>
       </c>
       <c r="D45" s="1">
         <v>2</v>
       </c>
       <c r="E45" s="2">
-        <v>2003</v>
+        <v>2007</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I45" s="2">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="J45" s="2">
         <v>4</v>
@@ -4053,9 +4076,6 @@
       <c r="S45" s="1">
         <v>0</v>
       </c>
-      <c r="T45" s="1"/>
-      <c r="U45" s="1"/>
-      <c r="V45" s="1"/>
       <c r="W45" s="1">
         <v>0</v>
       </c>
@@ -4065,104 +4085,42 @@
       <c r="Y45" s="1">
         <v>0</v>
       </c>
-      <c r="Z45" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA45" s="2">
+      <c r="Z45" s="2">
         <v>20</v>
       </c>
-      <c r="AC45" s="1"/>
-    </row>
-    <row r="46" s="2" customFormat="1" customHeight="1" spans="3:29">
-      <c r="C46" s="1">
-        <v>20043</v>
-      </c>
-      <c r="D46" s="1">
-        <v>2</v>
-      </c>
-      <c r="E46" s="2">
-        <v>2004</v>
-      </c>
-      <c r="F46" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G46" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="H46" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="I46" s="2">
-        <v>60</v>
-      </c>
-      <c r="J46" s="2">
-        <v>4</v>
-      </c>
-      <c r="K46" s="2">
-        <v>5</v>
-      </c>
-      <c r="L46" s="1">
-        <v>0</v>
-      </c>
-      <c r="M46" s="1">
-        <v>0</v>
-      </c>
-      <c r="N46" s="1">
-        <v>0</v>
-      </c>
-      <c r="O46" s="1">
-        <v>0</v>
-      </c>
-      <c r="P46" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q46" s="1">
-        <v>0</v>
-      </c>
-      <c r="R46" s="1">
-        <v>0</v>
-      </c>
-      <c r="S46" s="1">
-        <v>0</v>
-      </c>
-      <c r="T46" s="1"/>
-      <c r="U46" s="1"/>
-      <c r="V46" s="1"/>
-      <c r="W46" s="1">
-        <v>0</v>
-      </c>
-      <c r="X46" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y46" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z46" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA46" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC46" s="1"/>
+      <c r="AA45" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" s="1" customFormat="1" customHeight="1" spans="3:29">
+      <c r="E46" s="2"/>
+      <c r="F46" s="2"/>
+      <c r="I46" s="2"/>
+      <c r="J46" s="2"/>
+      <c r="K46" s="2"/>
+      <c r="S46" s="2"/>
+      <c r="T46" s="2"/>
+      <c r="U46" s="2"/>
+      <c r="V46" s="2"/>
     </row>
     <row r="47" s="2" customFormat="1" customHeight="1" spans="3:29">
       <c r="C47" s="1">
-        <v>20073</v>
+        <v>20023</v>
       </c>
       <c r="D47" s="1">
         <v>2</v>
       </c>
       <c r="E47" s="2">
-        <v>2007</v>
+        <v>2002</v>
       </c>
       <c r="F47" s="2" t="s">
         <v>81</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="I47" s="2">
         <v>60</v>
@@ -4218,55 +4176,101 @@
       <c r="AC47" s="1"/>
     </row>
     <row r="48" s="2" customFormat="1" customHeight="1" spans="3:29">
-      <c r="C48" s="1"/>
-      <c r="D48" s="1"/>
-      <c r="G48" s="1"/>
-      <c r="H48" s="1"/>
-      <c r="I48" s="2"/>
-      <c r="J48" s="2"/>
-      <c r="K48" s="2"/>
-      <c r="L48" s="1"/>
-      <c r="M48" s="1"/>
-      <c r="N48" s="1"/>
-      <c r="O48" s="1"/>
-      <c r="P48" s="1"/>
-      <c r="Q48" s="1"/>
-      <c r="R48" s="1"/>
-      <c r="S48" s="1"/>
+      <c r="C48" s="1">
+        <v>20033</v>
+      </c>
+      <c r="D48" s="1">
+        <v>2</v>
+      </c>
+      <c r="E48" s="2">
+        <v>2003</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G48" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="H48" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="I48" s="2">
+        <v>60</v>
+      </c>
+      <c r="J48" s="2">
+        <v>4</v>
+      </c>
+      <c r="K48" s="2">
+        <v>5</v>
+      </c>
+      <c r="L48" s="1">
+        <v>0</v>
+      </c>
+      <c r="M48" s="1">
+        <v>0</v>
+      </c>
+      <c r="N48" s="1">
+        <v>0</v>
+      </c>
+      <c r="O48" s="1">
+        <v>0</v>
+      </c>
+      <c r="P48" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q48" s="1">
+        <v>0</v>
+      </c>
+      <c r="R48" s="1">
+        <v>0</v>
+      </c>
+      <c r="S48" s="1">
+        <v>0</v>
+      </c>
       <c r="T48" s="1"/>
       <c r="U48" s="1"/>
       <c r="V48" s="1"/>
-      <c r="W48" s="1"/>
-      <c r="X48" s="1"/>
-      <c r="Y48" s="1"/>
-      <c r="Z48" s="1"/>
-      <c r="AA48" s="1"/>
+      <c r="W48" s="1">
+        <v>0</v>
+      </c>
+      <c r="X48" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y48" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z48" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA48" s="2">
+        <v>20</v>
+      </c>
       <c r="AC48" s="1"/>
     </row>
     <row r="49" s="2" customFormat="1" customHeight="1" spans="3:29">
       <c r="C49" s="1">
-        <v>20024</v>
+        <v>20043</v>
       </c>
       <c r="D49" s="1">
         <v>2</v>
       </c>
       <c r="E49" s="2">
-        <v>2002</v>
+        <v>2004</v>
       </c>
       <c r="F49" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="G49" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="H49" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="G49" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="H49" s="1" t="s">
-        <v>73</v>
-      </c>
       <c r="I49" s="2">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="J49" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K49" s="2">
         <v>5</v>
@@ -4302,7 +4306,7 @@
         <v>0</v>
       </c>
       <c r="X49" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y49" s="1">
         <v>0</v>
@@ -4310,35 +4314,35 @@
       <c r="Z49" s="1">
         <v>0</v>
       </c>
-      <c r="AA49" s="1">
-        <v>0</v>
+      <c r="AA49" s="2">
+        <v>20</v>
       </c>
       <c r="AC49" s="1"/>
     </row>
     <row r="50" s="2" customFormat="1" customHeight="1" spans="3:29">
       <c r="C50" s="1">
-        <v>20034</v>
+        <v>20073</v>
       </c>
       <c r="D50" s="1">
         <v>2</v>
       </c>
       <c r="E50" s="2">
-        <v>2003</v>
+        <v>2007</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="I50" s="2">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="J50" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K50" s="2">
         <v>5</v>
@@ -4374,7 +4378,7 @@
         <v>0</v>
       </c>
       <c r="X50" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y50" s="1">
         <v>0</v>
@@ -4382,101 +4386,55 @@
       <c r="Z50" s="1">
         <v>0</v>
       </c>
-      <c r="AA50" s="1">
-        <v>0</v>
+      <c r="AA50" s="2">
+        <v>20</v>
       </c>
       <c r="AC50" s="1"/>
     </row>
     <row r="51" s="2" customFormat="1" customHeight="1" spans="3:29">
-      <c r="C51" s="1">
-        <v>20044</v>
-      </c>
-      <c r="D51" s="1">
-        <v>2</v>
-      </c>
-      <c r="E51" s="2">
-        <v>2004</v>
-      </c>
-      <c r="F51" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G51" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="H51" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="I51" s="2">
-        <v>20</v>
-      </c>
-      <c r="J51" s="2">
-        <v>5</v>
-      </c>
-      <c r="K51" s="2">
-        <v>5</v>
-      </c>
-      <c r="L51" s="1">
-        <v>0</v>
-      </c>
-      <c r="M51" s="1">
-        <v>0</v>
-      </c>
-      <c r="N51" s="1">
-        <v>0</v>
-      </c>
-      <c r="O51" s="1">
-        <v>0</v>
-      </c>
-      <c r="P51" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q51" s="1">
-        <v>0</v>
-      </c>
-      <c r="R51" s="1">
-        <v>0</v>
-      </c>
-      <c r="S51" s="1">
-        <v>0</v>
-      </c>
+      <c r="C51" s="1"/>
+      <c r="D51" s="1"/>
+      <c r="G51" s="1"/>
+      <c r="H51" s="1"/>
+      <c r="I51" s="2"/>
+      <c r="J51" s="2"/>
+      <c r="K51" s="2"/>
+      <c r="L51" s="1"/>
+      <c r="M51" s="1"/>
+      <c r="N51" s="1"/>
+      <c r="O51" s="1"/>
+      <c r="P51" s="1"/>
+      <c r="Q51" s="1"/>
+      <c r="R51" s="1"/>
+      <c r="S51" s="1"/>
       <c r="T51" s="1"/>
       <c r="U51" s="1"/>
       <c r="V51" s="1"/>
-      <c r="W51" s="1">
-        <v>0</v>
-      </c>
-      <c r="X51" s="1">
-        <v>100</v>
-      </c>
-      <c r="Y51" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z51" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA51" s="1">
-        <v>0</v>
-      </c>
+      <c r="W51" s="1"/>
+      <c r="X51" s="1"/>
+      <c r="Y51" s="1"/>
+      <c r="Z51" s="1"/>
+      <c r="AA51" s="1"/>
       <c r="AC51" s="1"/>
     </row>
-    <row r="52" s="1" customFormat="1" customHeight="1" spans="3:29">
+    <row r="52" s="2" customFormat="1" customHeight="1" spans="3:29">
       <c r="C52" s="1">
-        <v>20074</v>
+        <v>20024</v>
       </c>
       <c r="D52" s="1">
         <v>2</v>
       </c>
       <c r="E52" s="2">
-        <v>2007</v>
+        <v>2002</v>
       </c>
       <c r="F52" s="2" t="s">
         <v>81</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="I52" s="2">
         <v>20</v>
@@ -4511,6 +4469,9 @@
       <c r="S52" s="1">
         <v>0</v>
       </c>
+      <c r="T52" s="1"/>
+      <c r="U52" s="1"/>
+      <c r="V52" s="1"/>
       <c r="W52" s="1">
         <v>0</v>
       </c>
@@ -4526,246 +4487,249 @@
       <c r="AA52" s="1">
         <v>0</v>
       </c>
-    </row>
-    <row r="53" customHeight="1" spans="3:29">
-      <c r="I53" s="2"/>
-      <c r="J53" s="2"/>
-      <c r="K53" s="2"/>
-    </row>
-    <row r="54" s="3" customFormat="1" customHeight="1"/>
-    <row r="55" customHeight="1" spans="3:29">
-      <c r="I55" s="2"/>
-      <c r="J55" s="2"/>
-      <c r="K55" s="2"/>
-    </row>
-    <row r="56" s="1" customFormat="1" customHeight="1" spans="3:29">
-      <c r="C56" s="1">
-        <v>30011</v>
-      </c>
-      <c r="D56" s="1">
-        <v>3</v>
-      </c>
-      <c r="E56" s="2">
-        <v>3001</v>
-      </c>
-      <c r="F56" s="2" t="s">
+      <c r="AC52" s="1"/>
+    </row>
+    <row r="53" s="2" customFormat="1" customHeight="1" spans="3:29">
+      <c r="C53" s="1">
+        <v>20034</v>
+      </c>
+      <c r="D53" s="1">
+        <v>2</v>
+      </c>
+      <c r="E53" s="2">
+        <v>2003</v>
+      </c>
+      <c r="F53" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="G56" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="H56" s="1" t="s">
+      <c r="G53" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="H53" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="I53" s="2">
+        <v>20</v>
+      </c>
+      <c r="J53" s="2">
+        <v>5</v>
+      </c>
+      <c r="K53" s="2">
+        <v>5</v>
+      </c>
+      <c r="L53" s="1">
+        <v>0</v>
+      </c>
+      <c r="M53" s="1">
+        <v>0</v>
+      </c>
+      <c r="N53" s="1">
+        <v>0</v>
+      </c>
+      <c r="O53" s="1">
+        <v>0</v>
+      </c>
+      <c r="P53" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="1">
+        <v>0</v>
+      </c>
+      <c r="R53" s="1">
+        <v>0</v>
+      </c>
+      <c r="S53" s="1">
+        <v>0</v>
+      </c>
+      <c r="T53" s="1"/>
+      <c r="U53" s="1"/>
+      <c r="V53" s="1"/>
+      <c r="W53" s="1">
+        <v>0</v>
+      </c>
+      <c r="X53" s="1">
+        <v>100</v>
+      </c>
+      <c r="Y53" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z53" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA53" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC53" s="1"/>
+    </row>
+    <row r="54" s="2" customFormat="1" customHeight="1" spans="3:29">
+      <c r="C54" s="1">
+        <v>20044</v>
+      </c>
+      <c r="D54" s="1">
+        <v>2</v>
+      </c>
+      <c r="E54" s="2">
+        <v>2004</v>
+      </c>
+      <c r="F54" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="I56" s="2">
+      <c r="G54" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="H54" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="I54" s="2">
+        <v>20</v>
+      </c>
+      <c r="J54" s="2">
+        <v>5</v>
+      </c>
+      <c r="K54" s="2">
+        <v>5</v>
+      </c>
+      <c r="L54" s="1">
+        <v>0</v>
+      </c>
+      <c r="M54" s="1">
+        <v>0</v>
+      </c>
+      <c r="N54" s="1">
+        <v>0</v>
+      </c>
+      <c r="O54" s="1">
+        <v>0</v>
+      </c>
+      <c r="P54" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q54" s="1">
+        <v>0</v>
+      </c>
+      <c r="R54" s="1">
+        <v>0</v>
+      </c>
+      <c r="S54" s="1">
+        <v>0</v>
+      </c>
+      <c r="T54" s="1"/>
+      <c r="U54" s="1"/>
+      <c r="V54" s="1"/>
+      <c r="W54" s="1">
+        <v>0</v>
+      </c>
+      <c r="X54" s="1">
         <v>100</v>
       </c>
-      <c r="J56" s="2">
-        <v>1</v>
-      </c>
-      <c r="K56" s="2">
-        <v>5</v>
-      </c>
-      <c r="L56" s="1">
-        <v>0</v>
-      </c>
-      <c r="M56" s="1">
-        <v>0</v>
-      </c>
-      <c r="N56" s="1">
-        <v>0</v>
-      </c>
-      <c r="O56" s="1">
-        <v>0</v>
-      </c>
-      <c r="P56" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q56" s="1">
-        <v>0</v>
-      </c>
-      <c r="R56" s="1">
-        <v>0</v>
-      </c>
-      <c r="S56" s="1">
-        <v>5</v>
-      </c>
-      <c r="W56" s="1">
-        <v>0</v>
-      </c>
-      <c r="X56" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y56" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z56" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA56" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" s="1" customFormat="1" customHeight="1" spans="3:29">
-      <c r="C57" s="1">
-        <v>30021</v>
-      </c>
-      <c r="D57" s="1">
-        <v>3</v>
-      </c>
-      <c r="E57" s="2">
-        <v>3002</v>
-      </c>
-      <c r="F57" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="G57" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="H57" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="I57" s="2">
+      <c r="Y54" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z54" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA54" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC54" s="1"/>
+    </row>
+    <row r="55" s="1" customFormat="1" customHeight="1" spans="3:29">
+      <c r="C55" s="1">
+        <v>20074</v>
+      </c>
+      <c r="D55" s="1">
+        <v>2</v>
+      </c>
+      <c r="E55" s="2">
+        <v>2007</v>
+      </c>
+      <c r="F55" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="G55" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="H55" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="I55" s="2">
+        <v>20</v>
+      </c>
+      <c r="J55" s="2">
+        <v>5</v>
+      </c>
+      <c r="K55" s="2">
+        <v>5</v>
+      </c>
+      <c r="L55" s="1">
+        <v>0</v>
+      </c>
+      <c r="M55" s="1">
+        <v>0</v>
+      </c>
+      <c r="N55" s="1">
+        <v>0</v>
+      </c>
+      <c r="O55" s="1">
+        <v>0</v>
+      </c>
+      <c r="P55" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q55" s="1">
+        <v>0</v>
+      </c>
+      <c r="R55" s="1">
+        <v>0</v>
+      </c>
+      <c r="S55" s="1">
+        <v>0</v>
+      </c>
+      <c r="W55" s="1">
+        <v>0</v>
+      </c>
+      <c r="X55" s="1">
         <v>100</v>
       </c>
-      <c r="J57" s="2">
-        <v>1</v>
-      </c>
-      <c r="K57" s="2">
-        <v>5</v>
-      </c>
-      <c r="L57" s="1">
-        <v>0</v>
-      </c>
-      <c r="M57" s="1">
-        <v>0</v>
-      </c>
-      <c r="N57" s="1">
-        <v>0</v>
-      </c>
-      <c r="O57" s="1">
-        <v>0</v>
-      </c>
-      <c r="P57" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q57" s="1">
-        <v>0</v>
-      </c>
-      <c r="R57" s="1">
-        <v>0</v>
-      </c>
-      <c r="S57" s="2">
-        <v>20</v>
-      </c>
-      <c r="T57" s="2"/>
-      <c r="U57" s="2"/>
-      <c r="V57" s="2"/>
-      <c r="W57" s="1">
-        <v>0</v>
-      </c>
-      <c r="X57" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y57" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z57" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA57" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" s="1" customFormat="1" customHeight="1" spans="3:29">
-      <c r="C58" s="1">
-        <v>30031</v>
-      </c>
-      <c r="D58" s="1">
-        <v>3</v>
-      </c>
-      <c r="E58" s="2">
-        <v>3003</v>
-      </c>
-      <c r="F58" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="G58" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="H58" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="I58" s="2">
-        <v>100</v>
-      </c>
-      <c r="J58" s="2">
-        <v>1</v>
-      </c>
-      <c r="K58" s="2">
-        <v>5</v>
-      </c>
-      <c r="L58" s="1">
-        <v>0</v>
-      </c>
-      <c r="M58" s="1">
-        <v>0</v>
-      </c>
-      <c r="N58" s="1">
-        <v>0</v>
-      </c>
-      <c r="O58" s="1">
-        <v>0</v>
-      </c>
-      <c r="P58" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q58" s="1">
-        <v>0</v>
-      </c>
-      <c r="R58" s="1">
-        <v>0</v>
-      </c>
-      <c r="S58" s="2">
-        <v>20</v>
-      </c>
-      <c r="T58" s="2"/>
-      <c r="U58" s="2"/>
-      <c r="V58" s="2"/>
-      <c r="W58" s="1">
-        <v>0</v>
-      </c>
-      <c r="X58" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y58" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z58" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA58" s="1">
-        <v>0</v>
-      </c>
+      <c r="Y55" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z55" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA55" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" customHeight="1" spans="3:29">
+      <c r="I56" s="2"/>
+      <c r="J56" s="2"/>
+      <c r="K56" s="2"/>
+    </row>
+    <row r="57" s="3" customFormat="1" customHeight="1"/>
+    <row r="58" customHeight="1" spans="3:29">
+      <c r="I58" s="2"/>
+      <c r="J58" s="2"/>
+      <c r="K58" s="2"/>
     </row>
     <row r="59" s="1" customFormat="1" customHeight="1" spans="3:29">
       <c r="C59" s="1">
-        <v>30041</v>
+        <v>30011</v>
       </c>
       <c r="D59" s="1">
         <v>3</v>
       </c>
       <c r="E59" s="2">
-        <v>3004</v>
+        <v>3001</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>62</v>
+        <v>88</v>
       </c>
       <c r="I59" s="2">
         <v>100</v>
@@ -4797,12 +4761,9 @@
       <c r="R59" s="1">
         <v>0</v>
       </c>
-      <c r="S59" s="2">
-        <v>20</v>
-      </c>
-      <c r="T59" s="2"/>
-      <c r="U59" s="2"/>
-      <c r="V59" s="2"/>
+      <c r="S59" s="1">
+        <v>5</v>
+      </c>
       <c r="W59" s="1">
         <v>0</v>
       </c>
@@ -4821,22 +4782,22 @@
     </row>
     <row r="60" s="1" customFormat="1" customHeight="1" spans="3:29">
       <c r="C60" s="1">
-        <v>30051</v>
+        <v>30021</v>
       </c>
       <c r="D60" s="1">
         <v>3</v>
       </c>
       <c r="E60" s="2">
-        <v>3005</v>
+        <v>3002</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I60" s="2">
         <v>100</v>
@@ -4869,7 +4830,7 @@
         <v>0</v>
       </c>
       <c r="S60" s="2">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T60" s="2"/>
       <c r="U60" s="2"/>
@@ -4892,22 +4853,22 @@
     </row>
     <row r="61" s="1" customFormat="1" customHeight="1" spans="3:29">
       <c r="C61" s="1">
-        <v>30061</v>
+        <v>30031</v>
       </c>
       <c r="D61" s="1">
         <v>3</v>
       </c>
       <c r="E61" s="2">
-        <v>3006</v>
+        <v>3003</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I61" s="2">
         <v>100</v>
@@ -4940,7 +4901,7 @@
         <v>0</v>
       </c>
       <c r="S61" s="2">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T61" s="2"/>
       <c r="U61" s="2"/>
@@ -4963,22 +4924,22 @@
     </row>
     <row r="62" s="1" customFormat="1" customHeight="1" spans="3:29">
       <c r="C62" s="1">
-        <v>30071</v>
+        <v>30041</v>
       </c>
       <c r="D62" s="1">
         <v>3</v>
       </c>
       <c r="E62" s="2">
-        <v>3007</v>
+        <v>3004</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="I62" s="2">
         <v>100</v>
@@ -5033,36 +4994,100 @@
       </c>
     </row>
     <row r="63" s="1" customFormat="1" customHeight="1" spans="3:29">
-      <c r="F63" s="2"/>
-      <c r="I63" s="2"/>
-      <c r="J63" s="2"/>
-      <c r="K63" s="2"/>
-      <c r="Z63" s="2"/>
+      <c r="C63" s="1">
+        <v>30051</v>
+      </c>
+      <c r="D63" s="1">
+        <v>3</v>
+      </c>
+      <c r="E63" s="2">
+        <v>3005</v>
+      </c>
+      <c r="F63" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="G63" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="H63" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="I63" s="2">
+        <v>100</v>
+      </c>
+      <c r="J63" s="2">
+        <v>1</v>
+      </c>
+      <c r="K63" s="2">
+        <v>5</v>
+      </c>
+      <c r="L63" s="1">
+        <v>0</v>
+      </c>
+      <c r="M63" s="1">
+        <v>0</v>
+      </c>
+      <c r="N63" s="1">
+        <v>0</v>
+      </c>
+      <c r="O63" s="1">
+        <v>0</v>
+      </c>
+      <c r="P63" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="1">
+        <v>0</v>
+      </c>
+      <c r="R63" s="1">
+        <v>0</v>
+      </c>
+      <c r="S63" s="2">
+        <v>10</v>
+      </c>
+      <c r="T63" s="2"/>
+      <c r="U63" s="2"/>
+      <c r="V63" s="2"/>
+      <c r="W63" s="1">
+        <v>0</v>
+      </c>
+      <c r="X63" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y63" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z63" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA63" s="1">
+        <v>0</v>
+      </c>
     </row>
     <row r="64" s="1" customFormat="1" customHeight="1" spans="3:29">
       <c r="C64" s="1">
-        <v>30022</v>
+        <v>30061</v>
       </c>
       <c r="D64" s="1">
         <v>3</v>
       </c>
       <c r="E64" s="2">
-        <v>3002</v>
+        <v>3006</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="H64" s="1" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="I64" s="2">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="J64" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K64" s="2">
         <v>5</v>
@@ -5088,9 +5113,12 @@
       <c r="R64" s="1">
         <v>0</v>
       </c>
-      <c r="S64" s="1">
-        <v>0</v>
-      </c>
+      <c r="S64" s="2">
+        <v>5</v>
+      </c>
+      <c r="T64" s="2"/>
+      <c r="U64" s="2"/>
+      <c r="V64" s="2"/>
       <c r="W64" s="1">
         <v>0</v>
       </c>
@@ -5100,8 +5128,8 @@
       <c r="Y64" s="1">
         <v>0</v>
       </c>
-      <c r="Z64" s="2">
-        <v>20</v>
+      <c r="Z64" s="1">
+        <v>0</v>
       </c>
       <c r="AA64" s="1">
         <v>0</v>
@@ -5109,28 +5137,28 @@
     </row>
     <row r="65" s="1" customFormat="1" customHeight="1" spans="3:29">
       <c r="C65" s="1">
-        <v>30032</v>
+        <v>30071</v>
       </c>
       <c r="D65" s="1">
         <v>3</v>
       </c>
       <c r="E65" s="2">
-        <v>3003</v>
+        <v>3007</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="H65" s="1" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="I65" s="2">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="J65" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K65" s="2">
         <v>5</v>
@@ -5156,9 +5184,12 @@
       <c r="R65" s="1">
         <v>0</v>
       </c>
-      <c r="S65" s="1">
-        <v>0</v>
-      </c>
+      <c r="S65" s="2">
+        <v>20</v>
+      </c>
+      <c r="T65" s="2"/>
+      <c r="U65" s="2"/>
+      <c r="V65" s="2"/>
       <c r="W65" s="1">
         <v>0</v>
       </c>
@@ -5168,99 +5199,38 @@
       <c r="Y65" s="1">
         <v>0</v>
       </c>
-      <c r="Z65" s="2">
-        <v>20</v>
+      <c r="Z65" s="1">
+        <v>0</v>
       </c>
       <c r="AA65" s="1">
         <v>0</v>
       </c>
     </row>
     <row r="66" s="1" customFormat="1" customHeight="1" spans="3:29">
-      <c r="C66" s="1">
-        <v>30042</v>
-      </c>
-      <c r="D66" s="1">
-        <v>3</v>
-      </c>
-      <c r="E66" s="2">
-        <v>3004</v>
-      </c>
-      <c r="F66" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="G66" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="H66" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="I66" s="2">
-        <v>40</v>
-      </c>
-      <c r="J66" s="2">
-        <v>4</v>
-      </c>
-      <c r="K66" s="2">
-        <v>5</v>
-      </c>
-      <c r="L66" s="1">
-        <v>0</v>
-      </c>
-      <c r="M66" s="1">
-        <v>0</v>
-      </c>
-      <c r="N66" s="1">
-        <v>0</v>
-      </c>
-      <c r="O66" s="1">
-        <v>0</v>
-      </c>
-      <c r="P66" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q66" s="1">
-        <v>0</v>
-      </c>
-      <c r="R66" s="1">
-        <v>0</v>
-      </c>
-      <c r="S66" s="1">
-        <v>0</v>
-      </c>
-      <c r="W66" s="1">
-        <v>0</v>
-      </c>
-      <c r="X66" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y66" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z66" s="2">
-        <v>20</v>
-      </c>
-      <c r="AA66" s="1">
-        <v>0</v>
-      </c>
+      <c r="F66" s="2"/>
+      <c r="I66" s="2"/>
+      <c r="J66" s="2"/>
+      <c r="K66" s="2"/>
+      <c r="Z66" s="2"/>
     </row>
     <row r="67" s="1" customFormat="1" customHeight="1" spans="3:29">
       <c r="C67" s="1">
-        <v>30072</v>
+        <v>30022</v>
       </c>
       <c r="D67" s="1">
         <v>3</v>
       </c>
       <c r="E67" s="2">
-        <v>3007</v>
+        <v>3002</v>
       </c>
       <c r="F67" s="2" t="s">
         <v>89</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="H67" s="1" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="I67" s="2">
         <v>40</v>
@@ -5312,40 +5282,97 @@
       </c>
     </row>
     <row r="68" s="1" customFormat="1" customHeight="1" spans="3:29">
-      <c r="E68" s="2"/>
-      <c r="F68" s="2"/>
-      <c r="I68" s="2"/>
-      <c r="J68" s="2"/>
-      <c r="K68" s="2"/>
-      <c r="S68" s="2"/>
-      <c r="T68" s="2"/>
-      <c r="U68" s="2"/>
-      <c r="V68" s="2"/>
-    </row>
-    <row r="69" s="2" customFormat="1" customHeight="1" spans="3:29">
+      <c r="C68" s="1">
+        <v>30032</v>
+      </c>
+      <c r="D68" s="1">
+        <v>3</v>
+      </c>
+      <c r="E68" s="2">
+        <v>3003</v>
+      </c>
+      <c r="F68" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G68" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="H68" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="I68" s="2">
+        <v>40</v>
+      </c>
+      <c r="J68" s="2">
+        <v>4</v>
+      </c>
+      <c r="K68" s="2">
+        <v>5</v>
+      </c>
+      <c r="L68" s="1">
+        <v>0</v>
+      </c>
+      <c r="M68" s="1">
+        <v>0</v>
+      </c>
+      <c r="N68" s="1">
+        <v>0</v>
+      </c>
+      <c r="O68" s="1">
+        <v>0</v>
+      </c>
+      <c r="P68" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="1">
+        <v>0</v>
+      </c>
+      <c r="R68" s="1">
+        <v>0</v>
+      </c>
+      <c r="S68" s="1">
+        <v>0</v>
+      </c>
+      <c r="W68" s="1">
+        <v>0</v>
+      </c>
+      <c r="X68" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y68" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z68" s="2">
+        <v>20</v>
+      </c>
+      <c r="AA68" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" s="1" customFormat="1" customHeight="1" spans="3:29">
       <c r="C69" s="1">
-        <v>30023</v>
+        <v>30052</v>
       </c>
       <c r="D69" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E69" s="2">
-        <v>3002</v>
+        <v>3005</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="I69" s="2">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="J69" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K69" s="2">
         <v>5</v>
@@ -5371,12 +5398,12 @@
       <c r="R69" s="1">
         <v>0</v>
       </c>
-      <c r="S69" s="1">
-        <v>0</v>
-      </c>
-      <c r="T69" s="1"/>
-      <c r="U69" s="1"/>
-      <c r="V69" s="1"/>
+      <c r="S69" s="2">
+        <v>0</v>
+      </c>
+      <c r="T69" s="2"/>
+      <c r="U69" s="2"/>
+      <c r="V69" s="2"/>
       <c r="W69" s="1">
         <v>0</v>
       </c>
@@ -5387,34 +5414,33 @@
         <v>0</v>
       </c>
       <c r="Z69" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA69" s="2">
         <v>20</v>
       </c>
-      <c r="AC69" s="1"/>
-    </row>
-    <row r="70" s="2" customFormat="1" customHeight="1" spans="3:29">
+      <c r="AA69" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" s="1" customFormat="1" customHeight="1" spans="3:29">
       <c r="C70" s="1">
-        <v>30033</v>
+        <v>30042</v>
       </c>
       <c r="D70" s="1">
         <v>3</v>
       </c>
       <c r="E70" s="2">
-        <v>3003</v>
+        <v>3004</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H70" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I70" s="2">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="J70" s="2">
         <v>4</v>
@@ -5446,9 +5472,6 @@
       <c r="S70" s="1">
         <v>0</v>
       </c>
-      <c r="T70" s="1"/>
-      <c r="U70" s="1"/>
-      <c r="V70" s="1"/>
       <c r="W70" s="1">
         <v>0</v>
       </c>
@@ -5458,35 +5481,34 @@
       <c r="Y70" s="1">
         <v>0</v>
       </c>
-      <c r="Z70" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA70" s="2">
+      <c r="Z70" s="2">
         <v>20</v>
       </c>
-      <c r="AC70" s="1"/>
-    </row>
-    <row r="71" s="2" customFormat="1" customHeight="1" spans="3:29">
+      <c r="AA70" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" s="1" customFormat="1" customHeight="1" spans="3:29">
       <c r="C71" s="1">
-        <v>30043</v>
+        <v>30072</v>
       </c>
       <c r="D71" s="1">
         <v>3</v>
       </c>
       <c r="E71" s="2">
-        <v>3004</v>
+        <v>3007</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H71" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I71" s="2">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="J71" s="2">
         <v>4</v>
@@ -5518,9 +5540,6 @@
       <c r="S71" s="1">
         <v>0</v>
       </c>
-      <c r="T71" s="1"/>
-      <c r="U71" s="1"/>
-      <c r="V71" s="1"/>
       <c r="W71" s="1">
         <v>0</v>
       </c>
@@ -5530,136 +5549,120 @@
       <c r="Y71" s="1">
         <v>0</v>
       </c>
-      <c r="Z71" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA71" s="2">
+      <c r="Z71" s="2">
         <v>20</v>
       </c>
-      <c r="AC71" s="1"/>
-    </row>
-    <row r="72" s="2" customFormat="1" customHeight="1" spans="3:29">
-      <c r="C72" s="1">
-        <v>30073</v>
-      </c>
-      <c r="D72" s="1">
+      <c r="AA71" s="1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" s="1" customFormat="1" customHeight="1" spans="3:29">
+      <c r="E72" s="2"/>
+      <c r="F72" s="2"/>
+      <c r="I72" s="2"/>
+      <c r="J72" s="2"/>
+      <c r="K72" s="2"/>
+      <c r="S72" s="2"/>
+      <c r="T72" s="2"/>
+      <c r="U72" s="2"/>
+      <c r="V72" s="2"/>
+    </row>
+    <row r="73" s="2" customFormat="1" customHeight="1" spans="3:29">
+      <c r="C73" s="1">
+        <v>30023</v>
+      </c>
+      <c r="D73" s="1">
         <v>3</v>
       </c>
-      <c r="E72" s="2">
-        <v>3007</v>
-      </c>
-      <c r="F72" s="2" t="s">
+      <c r="E73" s="2">
+        <v>3002</v>
+      </c>
+      <c r="F73" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="G72" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="H72" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="I72" s="2">
+      <c r="G73" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="H73" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="I73" s="2">
         <v>60</v>
       </c>
-      <c r="J72" s="2">
+      <c r="J73" s="2">
         <v>4</v>
       </c>
-      <c r="K72" s="2">
-        <v>5</v>
-      </c>
-      <c r="L72" s="1">
-        <v>0</v>
-      </c>
-      <c r="M72" s="1">
-        <v>0</v>
-      </c>
-      <c r="N72" s="1">
-        <v>0</v>
-      </c>
-      <c r="O72" s="1">
-        <v>0</v>
-      </c>
-      <c r="P72" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q72" s="1">
-        <v>0</v>
-      </c>
-      <c r="R72" s="1">
-        <v>0</v>
-      </c>
-      <c r="S72" s="1">
-        <v>0</v>
-      </c>
-      <c r="T72" s="1"/>
-      <c r="U72" s="1"/>
-      <c r="V72" s="1"/>
-      <c r="W72" s="1">
-        <v>0</v>
-      </c>
-      <c r="X72" s="1">
-        <v>0</v>
-      </c>
-      <c r="Y72" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z72" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA72" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC72" s="1"/>
-    </row>
-    <row r="73" s="2" customFormat="1" customHeight="1" spans="3:29">
-      <c r="C73" s="1"/>
-      <c r="D73" s="1"/>
-      <c r="G73" s="1"/>
-      <c r="H73" s="1"/>
-      <c r="I73" s="2"/>
-      <c r="J73" s="2"/>
-      <c r="K73" s="2"/>
-      <c r="L73" s="1"/>
-      <c r="M73" s="1"/>
-      <c r="N73" s="1"/>
-      <c r="O73" s="1"/>
-      <c r="P73" s="1"/>
-      <c r="Q73" s="1"/>
-      <c r="R73" s="1"/>
-      <c r="S73" s="1"/>
+      <c r="K73" s="2">
+        <v>5</v>
+      </c>
+      <c r="L73" s="1">
+        <v>0</v>
+      </c>
+      <c r="M73" s="1">
+        <v>0</v>
+      </c>
+      <c r="N73" s="1">
+        <v>0</v>
+      </c>
+      <c r="O73" s="1">
+        <v>0</v>
+      </c>
+      <c r="P73" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="1">
+        <v>0</v>
+      </c>
+      <c r="R73" s="1">
+        <v>0</v>
+      </c>
+      <c r="S73" s="1">
+        <v>0</v>
+      </c>
       <c r="T73" s="1"/>
       <c r="U73" s="1"/>
       <c r="V73" s="1"/>
-      <c r="W73" s="1"/>
-      <c r="X73" s="1"/>
-      <c r="Y73" s="1"/>
-      <c r="Z73" s="1"/>
-      <c r="AA73" s="1"/>
+      <c r="W73" s="1">
+        <v>0</v>
+      </c>
+      <c r="X73" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y73" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z73" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA73" s="2">
+        <v>20</v>
+      </c>
       <c r="AC73" s="1"/>
     </row>
     <row r="74" s="2" customFormat="1" customHeight="1" spans="3:29">
       <c r="C74" s="1">
-        <v>30024</v>
+        <v>30033</v>
       </c>
       <c r="D74" s="1">
         <v>3</v>
       </c>
       <c r="E74" s="2">
-        <v>3002</v>
+        <v>3003</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="H74" s="1" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="I74" s="2">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="J74" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K74" s="2">
         <v>5</v>
@@ -5695,7 +5698,7 @@
         <v>0</v>
       </c>
       <c r="X74" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y74" s="1">
         <v>0</v>
@@ -5703,35 +5706,35 @@
       <c r="Z74" s="1">
         <v>0</v>
       </c>
-      <c r="AA74" s="1">
-        <v>0</v>
+      <c r="AA74" s="2">
+        <v>20</v>
       </c>
       <c r="AC74" s="1"/>
     </row>
     <row r="75" s="2" customFormat="1" customHeight="1" spans="3:29">
       <c r="C75" s="1">
-        <v>30034</v>
+        <v>30043</v>
       </c>
       <c r="D75" s="1">
         <v>3</v>
       </c>
       <c r="E75" s="2">
-        <v>3003</v>
+        <v>3004</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="H75" s="1" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="I75" s="2">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="J75" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K75" s="2">
         <v>5</v>
@@ -5767,7 +5770,7 @@
         <v>0</v>
       </c>
       <c r="X75" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="Y75" s="1">
         <v>0</v>
@@ -5775,35 +5778,35 @@
       <c r="Z75" s="1">
         <v>0</v>
       </c>
-      <c r="AA75" s="1">
-        <v>0</v>
+      <c r="AA75" s="2">
+        <v>20</v>
       </c>
       <c r="AC75" s="1"/>
     </row>
     <row r="76" s="2" customFormat="1" customHeight="1" spans="3:29">
       <c r="C76" s="1">
-        <v>30044</v>
+        <v>30073</v>
       </c>
       <c r="D76" s="1">
         <v>3</v>
       </c>
       <c r="E76" s="2">
-        <v>3004</v>
+        <v>3007</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="I76" s="2">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="J76" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K76" s="2">
         <v>5</v>
@@ -5839,84 +5842,326 @@
         <v>0</v>
       </c>
       <c r="X76" s="1">
+        <v>0</v>
+      </c>
+      <c r="Y76" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z76" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA76" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC76" s="1"/>
+    </row>
+    <row r="77" s="2" customFormat="1" customHeight="1" spans="3:29">
+      <c r="C77" s="1"/>
+      <c r="D77" s="1"/>
+      <c r="G77" s="1"/>
+      <c r="H77" s="1"/>
+      <c r="I77" s="2"/>
+      <c r="J77" s="2"/>
+      <c r="K77" s="2"/>
+      <c r="L77" s="1"/>
+      <c r="M77" s="1"/>
+      <c r="N77" s="1"/>
+      <c r="O77" s="1"/>
+      <c r="P77" s="1"/>
+      <c r="Q77" s="1"/>
+      <c r="R77" s="1"/>
+      <c r="S77" s="1"/>
+      <c r="T77" s="1"/>
+      <c r="U77" s="1"/>
+      <c r="V77" s="1"/>
+      <c r="W77" s="1"/>
+      <c r="X77" s="1"/>
+      <c r="Y77" s="1"/>
+      <c r="Z77" s="1"/>
+      <c r="AA77" s="1"/>
+      <c r="AC77" s="1"/>
+    </row>
+    <row r="78" s="2" customFormat="1" customHeight="1" spans="3:29">
+      <c r="C78" s="1">
+        <v>30024</v>
+      </c>
+      <c r="D78" s="1">
+        <v>3</v>
+      </c>
+      <c r="E78" s="2">
+        <v>3002</v>
+      </c>
+      <c r="F78" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="G78" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="H78" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="I78" s="2">
+        <v>20</v>
+      </c>
+      <c r="J78" s="2">
+        <v>5</v>
+      </c>
+      <c r="K78" s="2">
+        <v>5</v>
+      </c>
+      <c r="L78" s="1">
+        <v>0</v>
+      </c>
+      <c r="M78" s="1">
+        <v>0</v>
+      </c>
+      <c r="N78" s="1">
+        <v>0</v>
+      </c>
+      <c r="O78" s="1">
+        <v>0</v>
+      </c>
+      <c r="P78" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q78" s="1">
+        <v>0</v>
+      </c>
+      <c r="R78" s="1">
+        <v>0</v>
+      </c>
+      <c r="S78" s="1">
+        <v>0</v>
+      </c>
+      <c r="T78" s="1"/>
+      <c r="U78" s="1"/>
+      <c r="V78" s="1"/>
+      <c r="W78" s="1">
+        <v>0</v>
+      </c>
+      <c r="X78" s="1">
         <v>100</v>
       </c>
-      <c r="Y76" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z76" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA76" s="1">
-        <v>0</v>
-      </c>
-      <c r="AC76" s="1"/>
-    </row>
-    <row r="77" s="1" customFormat="1" customHeight="1" spans="3:29">
-      <c r="C77" s="1">
+      <c r="Y78" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z78" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA78" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC78" s="1"/>
+    </row>
+    <row r="79" s="2" customFormat="1" customHeight="1" spans="3:29">
+      <c r="C79" s="1">
+        <v>30034</v>
+      </c>
+      <c r="D79" s="1">
+        <v>3</v>
+      </c>
+      <c r="E79" s="2">
+        <v>3003</v>
+      </c>
+      <c r="F79" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="G79" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="H79" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="I79" s="2">
+        <v>20</v>
+      </c>
+      <c r="J79" s="2">
+        <v>5</v>
+      </c>
+      <c r="K79" s="2">
+        <v>5</v>
+      </c>
+      <c r="L79" s="1">
+        <v>0</v>
+      </c>
+      <c r="M79" s="1">
+        <v>0</v>
+      </c>
+      <c r="N79" s="1">
+        <v>0</v>
+      </c>
+      <c r="O79" s="1">
+        <v>0</v>
+      </c>
+      <c r="P79" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q79" s="1">
+        <v>0</v>
+      </c>
+      <c r="R79" s="1">
+        <v>0</v>
+      </c>
+      <c r="S79" s="1">
+        <v>0</v>
+      </c>
+      <c r="T79" s="1"/>
+      <c r="U79" s="1"/>
+      <c r="V79" s="1"/>
+      <c r="W79" s="1">
+        <v>0</v>
+      </c>
+      <c r="X79" s="1">
+        <v>100</v>
+      </c>
+      <c r="Y79" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z79" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA79" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC79" s="1"/>
+    </row>
+    <row r="80" s="2" customFormat="1" customHeight="1" spans="3:29">
+      <c r="C80" s="1">
+        <v>30044</v>
+      </c>
+      <c r="D80" s="1">
+        <v>3</v>
+      </c>
+      <c r="E80" s="2">
+        <v>3004</v>
+      </c>
+      <c r="F80" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="G80" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="H80" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="I80" s="2">
+        <v>20</v>
+      </c>
+      <c r="J80" s="2">
+        <v>5</v>
+      </c>
+      <c r="K80" s="2">
+        <v>5</v>
+      </c>
+      <c r="L80" s="1">
+        <v>0</v>
+      </c>
+      <c r="M80" s="1">
+        <v>0</v>
+      </c>
+      <c r="N80" s="1">
+        <v>0</v>
+      </c>
+      <c r="O80" s="1">
+        <v>0</v>
+      </c>
+      <c r="P80" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q80" s="1">
+        <v>0</v>
+      </c>
+      <c r="R80" s="1">
+        <v>0</v>
+      </c>
+      <c r="S80" s="1">
+        <v>0</v>
+      </c>
+      <c r="T80" s="1"/>
+      <c r="U80" s="1"/>
+      <c r="V80" s="1"/>
+      <c r="W80" s="1">
+        <v>0</v>
+      </c>
+      <c r="X80" s="1">
+        <v>100</v>
+      </c>
+      <c r="Y80" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z80" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA80" s="1">
+        <v>0</v>
+      </c>
+      <c r="AC80" s="1"/>
+    </row>
+    <row r="81" s="1" customFormat="1" customHeight="1" spans="3:27">
+      <c r="C81" s="1">
         <v>30074</v>
       </c>
-      <c r="D77" s="1">
+      <c r="D81" s="1">
         <v>3</v>
       </c>
-      <c r="E77" s="2">
+      <c r="E81" s="2">
         <v>3007</v>
       </c>
-      <c r="F77" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="G77" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="H77" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="I77" s="2">
+      <c r="F81" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="G81" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="H81" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="I81" s="2">
         <v>20</v>
       </c>
-      <c r="J77" s="2">
-        <v>5</v>
-      </c>
-      <c r="K77" s="2">
-        <v>5</v>
-      </c>
-      <c r="L77" s="1">
-        <v>0</v>
-      </c>
-      <c r="M77" s="1">
-        <v>0</v>
-      </c>
-      <c r="N77" s="1">
-        <v>0</v>
-      </c>
-      <c r="O77" s="1">
-        <v>0</v>
-      </c>
-      <c r="P77" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q77" s="1">
-        <v>0</v>
-      </c>
-      <c r="R77" s="1">
-        <v>0</v>
-      </c>
-      <c r="S77" s="1">
-        <v>0</v>
-      </c>
-      <c r="W77" s="1">
-        <v>0</v>
-      </c>
-      <c r="X77" s="1">
+      <c r="J81" s="2">
+        <v>5</v>
+      </c>
+      <c r="K81" s="2">
+        <v>5</v>
+      </c>
+      <c r="L81" s="1">
+        <v>0</v>
+      </c>
+      <c r="M81" s="1">
+        <v>0</v>
+      </c>
+      <c r="N81" s="1">
+        <v>0</v>
+      </c>
+      <c r="O81" s="1">
+        <v>0</v>
+      </c>
+      <c r="P81" s="1">
+        <v>0</v>
+      </c>
+      <c r="Q81" s="1">
+        <v>0</v>
+      </c>
+      <c r="R81" s="1">
+        <v>0</v>
+      </c>
+      <c r="S81" s="1">
+        <v>0</v>
+      </c>
+      <c r="W81" s="1">
+        <v>0</v>
+      </c>
+      <c r="X81" s="1">
         <v>100</v>
       </c>
-      <c r="Y77" s="1">
-        <v>0</v>
-      </c>
-      <c r="Z77" s="1">
-        <v>0</v>
-      </c>
-      <c r="AA77" s="1">
+      <c r="Y81" s="1">
+        <v>0</v>
+      </c>
+      <c r="Z81" s="1">
+        <v>0</v>
+      </c>
+      <c r="AA81" s="1">
         <v>0</v>
       </c>
     </row>

--- a/Excel/SkillSuitConfig.xlsx
+++ b/Excel/SkillSuitConfig.xlsx
@@ -174,7 +174,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="98">
   <si>
     <t>#</t>
   </si>
@@ -359,7 +359,7 @@
     <t>·跃升</t>
   </si>
   <si>
-    <t>增加{1}%物攻倍率</t>
+    <t>增加{1}%物攻加成</t>
   </si>
   <si>
     <t>流光剑诀</t>
@@ -368,33 +368,36 @@
     <t>增加{1}%技能系数</t>
   </si>
   <si>
+    <t>月华剑阵</t>
+  </si>
+  <si>
+    <t>蛮牛冲撞</t>
+  </si>
+  <si>
+    <t>龙魂护体</t>
+  </si>
+  <si>
+    <t>·千重</t>
+  </si>
+  <si>
+    <t>增加{1}%的护盾值</t>
+  </si>
+  <si>
+    <t>无求易决</t>
+  </si>
+  <si>
+    <t>火麟剑诀</t>
+  </si>
+  <si>
+    <t>·祝福</t>
+  </si>
+  <si>
+    <t>增加{5}%技能攻击</t>
+  </si>
+  <si>
     <t>四方剑阵</t>
   </si>
   <si>
-    <t>重击剑术</t>
-  </si>
-  <si>
-    <t>龙魂护体</t>
-  </si>
-  <si>
-    <t>·千重</t>
-  </si>
-  <si>
-    <t>增加{1}%的护盾值</t>
-  </si>
-  <si>
-    <t>无求易决</t>
-  </si>
-  <si>
-    <t>火麟剑诀</t>
-  </si>
-  <si>
-    <t>·祝福</t>
-  </si>
-  <si>
-    <t>增加{5}%技能攻击</t>
-  </si>
-  <si>
     <t>·壁垒</t>
   </si>
   <si>
@@ -416,7 +419,7 @@
     <t>冥想心法</t>
   </si>
   <si>
-    <t>增加{1}%魔攻倍率</t>
+    <t>增加{1}%魔攻加成</t>
   </si>
   <si>
     <t>神雷术</t>
@@ -440,7 +443,7 @@
     <t>祈福心法</t>
   </si>
   <si>
-    <t>增加{1}%道攻倍率</t>
+    <t>增加{1}%道攻加成</t>
   </si>
   <si>
     <t>灭魔符</t>
@@ -1819,7 +1822,7 @@
         <v>0</v>
       </c>
       <c r="S6" s="1">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="W6" s="1">
         <v>0</v>
@@ -1887,7 +1890,7 @@
         <v>0</v>
       </c>
       <c r="S7" s="2">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="T7" s="2"/>
       <c r="U7" s="2"/>
@@ -1958,7 +1961,7 @@
         <v>0</v>
       </c>
       <c r="S8" s="2">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T8" s="2"/>
       <c r="U8" s="2"/>
@@ -2029,7 +2032,7 @@
         <v>0</v>
       </c>
       <c r="S9" s="2">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="T9" s="2"/>
       <c r="U9" s="2"/>
@@ -2100,7 +2103,7 @@
         <v>0</v>
       </c>
       <c r="S10" s="2">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T10" s="2"/>
       <c r="U10" s="2"/>
@@ -2171,7 +2174,7 @@
         <v>0</v>
       </c>
       <c r="S11" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T11" s="2"/>
       <c r="U11" s="2"/>
@@ -2242,7 +2245,7 @@
         <v>0</v>
       </c>
       <c r="S12" s="2">
-        <v>20</v>
+        <v>150</v>
       </c>
       <c r="T12" s="2"/>
       <c r="U12" s="2"/>
@@ -2362,7 +2365,7 @@
         <v>1003</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="G16" s="1" t="s">
         <v>71</v>
@@ -2433,10 +2436,10 @@
         <v>66</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I17" s="2">
         <v>100</v>
@@ -2651,10 +2654,10 @@
         <v>62</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I21" s="2">
         <v>60</v>
@@ -2720,13 +2723,13 @@
         <v>1003</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I22" s="2">
         <v>60</v>
@@ -2795,10 +2798,10 @@
         <v>65</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I23" s="2">
         <v>60</v>
@@ -2867,10 +2870,10 @@
         <v>70</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I24" s="2">
         <v>60</v>
@@ -2967,10 +2970,10 @@
         <v>62</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I26" s="2">
         <v>20</v>
@@ -3036,13 +3039,13 @@
         <v>1003</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I27" s="2">
         <v>20</v>
@@ -3111,10 +3114,10 @@
         <v>65</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I28" s="2">
         <v>20</v>
@@ -3183,10 +3186,10 @@
         <v>70</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I29" s="2">
         <v>20</v>
@@ -3259,13 +3262,13 @@
         <v>2001</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G33" s="1" t="s">
         <v>60</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="I33" s="2">
         <v>100</v>
@@ -3298,7 +3301,7 @@
         <v>0</v>
       </c>
       <c r="S33" s="1">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="W33" s="1">
         <v>0</v>
@@ -3327,7 +3330,7 @@
         <v>2002</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G34" s="1" t="s">
         <v>60</v>
@@ -3366,7 +3369,7 @@
         <v>0</v>
       </c>
       <c r="S34" s="2">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="T34" s="2"/>
       <c r="U34" s="2"/>
@@ -3398,7 +3401,7 @@
         <v>2003</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G35" s="1" t="s">
         <v>60</v>
@@ -3437,7 +3440,7 @@
         <v>0</v>
       </c>
       <c r="S35" s="2">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T35" s="2"/>
       <c r="U35" s="2"/>
@@ -3469,7 +3472,7 @@
         <v>2004</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G36" s="1" t="s">
         <v>60</v>
@@ -3508,7 +3511,7 @@
         <v>0</v>
       </c>
       <c r="S36" s="2">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="T36" s="2"/>
       <c r="U36" s="2"/>
@@ -3540,7 +3543,7 @@
         <v>2005</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G37" s="1" t="s">
         <v>67</v>
@@ -3579,7 +3582,7 @@
         <v>0</v>
       </c>
       <c r="S37" s="2">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T37" s="2"/>
       <c r="U37" s="2"/>
@@ -3611,7 +3614,7 @@
         <v>2006</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G38" s="1" t="s">
         <v>60</v>
@@ -3650,7 +3653,7 @@
         <v>0</v>
       </c>
       <c r="S38" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T38" s="2"/>
       <c r="U38" s="2"/>
@@ -3682,7 +3685,7 @@
         <v>2007</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G39" s="1" t="s">
         <v>60</v>
@@ -3721,7 +3724,7 @@
         <v>0</v>
       </c>
       <c r="S39" s="2">
-        <v>20</v>
+        <v>150</v>
       </c>
       <c r="T39" s="2"/>
       <c r="U39" s="2"/>
@@ -3760,7 +3763,7 @@
         <v>2002</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G41" s="1" t="s">
         <v>71</v>
@@ -3828,7 +3831,7 @@
         <v>2003</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G42" s="1" t="s">
         <v>71</v>
@@ -3896,13 +3899,13 @@
         <v>2005</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I43" s="2">
         <v>100</v>
@@ -3967,7 +3970,7 @@
         <v>2004</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G44" s="1" t="s">
         <v>71</v>
@@ -4035,7 +4038,7 @@
         <v>2007</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G45" s="1" t="s">
         <v>71</v>
@@ -4114,13 +4117,13 @@
         <v>2002</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I47" s="2">
         <v>60</v>
@@ -4186,13 +4189,13 @@
         <v>2003</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I48" s="2">
         <v>60</v>
@@ -4258,13 +4261,13 @@
         <v>2004</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I49" s="2">
         <v>60</v>
@@ -4330,13 +4333,13 @@
         <v>2007</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I50" s="2">
         <v>60</v>
@@ -4428,13 +4431,13 @@
         <v>2002</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I52" s="2">
         <v>20</v>
@@ -4500,13 +4503,13 @@
         <v>2003</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I53" s="2">
         <v>20</v>
@@ -4572,13 +4575,13 @@
         <v>2004</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I54" s="2">
         <v>20</v>
@@ -4644,13 +4647,13 @@
         <v>2007</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I55" s="2">
         <v>20</v>
@@ -4723,13 +4726,13 @@
         <v>3001</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G59" s="1" t="s">
         <v>60</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="I59" s="2">
         <v>100</v>
@@ -4762,7 +4765,7 @@
         <v>0</v>
       </c>
       <c r="S59" s="1">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="W59" s="1">
         <v>0</v>
@@ -4791,7 +4794,7 @@
         <v>3002</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G60" s="1" t="s">
         <v>60</v>
@@ -4830,7 +4833,7 @@
         <v>0</v>
       </c>
       <c r="S60" s="2">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="T60" s="2"/>
       <c r="U60" s="2"/>
@@ -4862,7 +4865,7 @@
         <v>3003</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G61" s="1" t="s">
         <v>60</v>
@@ -4901,7 +4904,7 @@
         <v>0</v>
       </c>
       <c r="S61" s="2">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T61" s="2"/>
       <c r="U61" s="2"/>
@@ -4933,7 +4936,7 @@
         <v>3004</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G62" s="1" t="s">
         <v>60</v>
@@ -4972,7 +4975,7 @@
         <v>0</v>
       </c>
       <c r="S62" s="2">
-        <v>20</v>
+        <v>300</v>
       </c>
       <c r="T62" s="2"/>
       <c r="U62" s="2"/>
@@ -5004,7 +5007,7 @@
         <v>3005</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G63" s="1" t="s">
         <v>67</v>
@@ -5043,7 +5046,7 @@
         <v>0</v>
       </c>
       <c r="S63" s="2">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T63" s="2"/>
       <c r="U63" s="2"/>
@@ -5075,7 +5078,7 @@
         <v>3006</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G64" s="1" t="s">
         <v>60</v>
@@ -5146,7 +5149,7 @@
         <v>3007</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G65" s="1" t="s">
         <v>60</v>
@@ -5185,7 +5188,7 @@
         <v>0</v>
       </c>
       <c r="S65" s="2">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="T65" s="2"/>
       <c r="U65" s="2"/>
@@ -5224,7 +5227,7 @@
         <v>3002</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G67" s="1" t="s">
         <v>71</v>
@@ -5292,7 +5295,7 @@
         <v>3003</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G68" s="1" t="s">
         <v>71</v>
@@ -5360,13 +5363,13 @@
         <v>3005</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H69" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="I69" s="2">
         <v>100</v>
@@ -5431,7 +5434,7 @@
         <v>3004</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G70" s="1" t="s">
         <v>71</v>
@@ -5499,7 +5502,7 @@
         <v>3007</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G71" s="1" t="s">
         <v>71</v>
@@ -5578,13 +5581,13 @@
         <v>3002</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H73" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I73" s="2">
         <v>60</v>
@@ -5650,13 +5653,13 @@
         <v>3003</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H74" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I74" s="2">
         <v>60</v>
@@ -5722,13 +5725,13 @@
         <v>3004</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H75" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I75" s="2">
         <v>60</v>
@@ -5794,13 +5797,13 @@
         <v>3007</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H76" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="I76" s="2">
         <v>60</v>
@@ -5892,13 +5895,13 @@
         <v>3002</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H78" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I78" s="2">
         <v>20</v>
@@ -5964,13 +5967,13 @@
         <v>3003</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H79" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I79" s="2">
         <v>20</v>
@@ -6036,13 +6039,13 @@
         <v>3004</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H80" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I80" s="2">
         <v>20</v>
@@ -6108,13 +6111,13 @@
         <v>3007</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G81" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H81" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I81" s="2">
         <v>20</v>

--- a/Excel/SkillSuitConfig.xlsx
+++ b/Excel/SkillSuitConfig.xlsx
@@ -1,8 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\legend2\Excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView windowHeight="17680"/>
   </bookViews>
@@ -5188,7 +5193,7 @@
         <v>0</v>
       </c>
       <c r="S65" s="2">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="T65" s="2"/>
       <c r="U65" s="2"/>
